--- a/src/migrations/ParentCompanies.xlsx
+++ b/src/migrations/ParentCompanies.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tsemachhadad/devemada/emda-dev/src/migrations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tsemachhadad/devemada/emda3/src/migrations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42563FB7-2BF9-4542-AD10-106C59F1C538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C0481B-BE0A-1C41-93AC-C3216B197A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="381">
   <si>
     <t xml:space="preserve">רום-רביד </t>
   </si>
@@ -1187,6 +1187,9 @@
   </si>
   <si>
     <t>אי.בי.אי קרנות נאמנות בע"מ- קרנות חו"ל</t>
+  </si>
+  <si>
+    <t>איילון חברה לביטוח - נוסטרו</t>
   </si>
 </sst>
 </file>
@@ -2207,7 +2210,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="287">
+  <cellXfs count="289">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2641,6 +2644,54 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
@@ -2650,14 +2701,281 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2671,324 +2989,18 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2997,11 +3009,8 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3339,28 +3348,28 @@
       <c r="B1" s="82" t="s">
         <v>199</v>
       </c>
-      <c r="C1" s="268" t="s">
+      <c r="C1" s="188" t="s">
         <v>200</v>
       </c>
-      <c r="D1" s="268"/>
+      <c r="D1" s="188"/>
       <c r="E1" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="F1" s="171" t="s">
+      <c r="F1" s="276" t="s">
         <v>378</v>
       </c>
-      <c r="G1" s="172"/>
-      <c r="H1" s="173" t="s">
+      <c r="G1" s="277"/>
+      <c r="H1" s="278" t="s">
         <v>375</v>
       </c>
-      <c r="I1" s="174"/>
-      <c r="J1" s="174"/>
-      <c r="K1" s="174"/>
-      <c r="L1" s="174"/>
-      <c r="M1" s="174"/>
-      <c r="N1" s="174"/>
-      <c r="O1" s="174"/>
-      <c r="P1" s="174"/>
+      <c r="I1" s="279"/>
+      <c r="J1" s="279"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="279"/>
+      <c r="M1" s="279"/>
+      <c r="N1" s="279"/>
+      <c r="O1" s="279"/>
+      <c r="P1" s="279"/>
       <c r="Q1" s="5" t="s">
         <v>184</v>
       </c>
@@ -3369,19 +3378,19 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="211" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="199" t="s">
+      <c r="B2" s="214" t="s">
         <v>197</v>
       </c>
-      <c r="C2" s="285" t="s">
+      <c r="C2" s="202" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="186">
+      <c r="D2" s="175">
         <v>17</v>
       </c>
-      <c r="E2" s="170">
+      <c r="E2" s="177">
         <v>513765339</v>
       </c>
       <c r="F2" s="87" t="s">
@@ -3390,103 +3399,103 @@
       <c r="G2" s="134">
         <v>101</v>
       </c>
-      <c r="H2" s="176" t="s">
+      <c r="H2" s="239" t="s">
         <v>347</v>
       </c>
-      <c r="I2" s="177"/>
-      <c r="J2" s="177"/>
-      <c r="K2" s="177"/>
-      <c r="L2" s="177"/>
-      <c r="M2" s="177"/>
-      <c r="N2" s="177"/>
-      <c r="O2" s="177"/>
-      <c r="P2" s="177"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
+      <c r="M2" s="240"/>
+      <c r="N2" s="240"/>
+      <c r="O2" s="240"/>
+      <c r="P2" s="240"/>
       <c r="Q2" s="88" t="s">
         <v>186</v>
       </c>
       <c r="R2" s="89"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="197"/>
-      <c r="B3" s="200"/>
-      <c r="C3" s="286"/>
-      <c r="D3" s="187"/>
-      <c r="E3" s="170"/>
+      <c r="A3" s="212"/>
+      <c r="B3" s="215"/>
+      <c r="C3" s="203"/>
+      <c r="D3" s="176"/>
+      <c r="E3" s="177"/>
       <c r="F3" s="76" t="s">
         <v>191</v>
       </c>
       <c r="G3" s="135">
         <v>102</v>
       </c>
-      <c r="H3" s="178"/>
-      <c r="I3" s="179"/>
-      <c r="J3" s="179"/>
-      <c r="K3" s="179"/>
-      <c r="L3" s="179"/>
-      <c r="M3" s="179"/>
-      <c r="N3" s="179"/>
-      <c r="O3" s="179"/>
-      <c r="P3" s="179"/>
+      <c r="H3" s="280"/>
+      <c r="I3" s="281"/>
+      <c r="J3" s="281"/>
+      <c r="K3" s="281"/>
+      <c r="L3" s="281"/>
+      <c r="M3" s="281"/>
+      <c r="N3" s="281"/>
+      <c r="O3" s="281"/>
+      <c r="P3" s="281"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="90"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="197"/>
-      <c r="B4" s="200"/>
-      <c r="C4" s="285" t="s">
+      <c r="A4" s="212"/>
+      <c r="B4" s="215"/>
+      <c r="C4" s="202" t="s">
         <v>379</v>
       </c>
-      <c r="D4" s="188">
+      <c r="D4" s="184">
         <v>110</v>
       </c>
-      <c r="E4" s="170"/>
+      <c r="E4" s="177"/>
       <c r="F4" s="77" t="s">
         <v>192</v>
       </c>
       <c r="G4" s="135">
         <v>301</v>
       </c>
-      <c r="H4" s="178"/>
-      <c r="I4" s="179"/>
-      <c r="J4" s="179"/>
-      <c r="K4" s="179"/>
-      <c r="L4" s="179"/>
-      <c r="M4" s="179"/>
-      <c r="N4" s="179"/>
-      <c r="O4" s="179"/>
-      <c r="P4" s="179"/>
+      <c r="H4" s="280"/>
+      <c r="I4" s="281"/>
+      <c r="J4" s="281"/>
+      <c r="K4" s="281"/>
+      <c r="L4" s="281"/>
+      <c r="M4" s="281"/>
+      <c r="N4" s="281"/>
+      <c r="O4" s="281"/>
+      <c r="P4" s="281"/>
       <c r="Q4" s="6" t="s">
         <v>187</v>
       </c>
       <c r="R4" s="90"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" s="197"/>
-      <c r="B5" s="200"/>
-      <c r="C5" s="286"/>
-      <c r="D5" s="187"/>
-      <c r="E5" s="182"/>
+      <c r="A5" s="212"/>
+      <c r="B5" s="215"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="176"/>
+      <c r="E5" s="178"/>
       <c r="F5" s="77" t="s">
         <v>193</v>
       </c>
       <c r="G5" s="135">
         <v>302</v>
       </c>
-      <c r="H5" s="180"/>
-      <c r="I5" s="181"/>
-      <c r="J5" s="181"/>
-      <c r="K5" s="181"/>
-      <c r="L5" s="181"/>
-      <c r="M5" s="181"/>
-      <c r="N5" s="181"/>
-      <c r="O5" s="181"/>
-      <c r="P5" s="181"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="243"/>
+      <c r="J5" s="243"/>
+      <c r="K5" s="243"/>
+      <c r="L5" s="243"/>
+      <c r="M5" s="243"/>
+      <c r="N5" s="243"/>
+      <c r="O5" s="243"/>
+      <c r="P5" s="243"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="90"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="197"/>
-      <c r="B6" s="209" t="s">
+      <c r="A6" s="212"/>
+      <c r="B6" s="275" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="79" t="s">
@@ -3504,23 +3513,23 @@
       <c r="G6" s="135">
         <v>8357</v>
       </c>
-      <c r="H6" s="165" t="s">
+      <c r="H6" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I6" s="166"/>
-      <c r="J6" s="166"/>
-      <c r="K6" s="166"/>
-      <c r="L6" s="166"/>
-      <c r="M6" s="166"/>
-      <c r="N6" s="166"/>
-      <c r="O6" s="166"/>
-      <c r="P6" s="166"/>
+      <c r="I6" s="182"/>
+      <c r="J6" s="182"/>
+      <c r="K6" s="182"/>
+      <c r="L6" s="182"/>
+      <c r="M6" s="182"/>
+      <c r="N6" s="182"/>
+      <c r="O6" s="182"/>
+      <c r="P6" s="182"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="90"/>
     </row>
     <row r="7" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A7" s="197"/>
-      <c r="B7" s="209"/>
+      <c r="A7" s="212"/>
+      <c r="B7" s="275"/>
       <c r="C7" s="79" t="s">
         <v>12</v>
       </c>
@@ -3554,8 +3563,8 @@
       <c r="R7" s="90"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A8" s="197"/>
-      <c r="B8" s="209"/>
+      <c r="A8" s="212"/>
+      <c r="B8" s="275"/>
       <c r="C8" s="79" t="s">
         <v>19</v>
       </c>
@@ -3571,30 +3580,30 @@
       <c r="G8" s="135">
         <v>14221</v>
       </c>
-      <c r="H8" s="165" t="s">
+      <c r="H8" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I8" s="166"/>
-      <c r="J8" s="166"/>
-      <c r="K8" s="166"/>
-      <c r="L8" s="166"/>
-      <c r="M8" s="166"/>
-      <c r="N8" s="166"/>
-      <c r="O8" s="166"/>
-      <c r="P8" s="166"/>
+      <c r="I8" s="182"/>
+      <c r="J8" s="182"/>
+      <c r="K8" s="182"/>
+      <c r="L8" s="182"/>
+      <c r="M8" s="182"/>
+      <c r="N8" s="182"/>
+      <c r="O8" s="182"/>
+      <c r="P8" s="182"/>
       <c r="Q8" s="22"/>
       <c r="R8" s="90"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="197"/>
-      <c r="B9" s="209"/>
-      <c r="C9" s="167" t="s">
+      <c r="A9" s="212"/>
+      <c r="B9" s="275"/>
+      <c r="C9" s="183" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="188">
+      <c r="D9" s="184">
         <v>1175</v>
       </c>
-      <c r="E9" s="169">
+      <c r="E9" s="185">
         <v>512008335</v>
       </c>
       <c r="F9" s="10" t="s">
@@ -3603,75 +3612,75 @@
       <c r="G9" s="135">
         <v>19815</v>
       </c>
-      <c r="H9" s="165" t="s">
+      <c r="H9" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I9" s="166"/>
-      <c r="J9" s="166"/>
-      <c r="K9" s="166"/>
-      <c r="L9" s="166"/>
-      <c r="M9" s="166"/>
-      <c r="N9" s="166"/>
-      <c r="O9" s="166"/>
-      <c r="P9" s="166"/>
+      <c r="I9" s="182"/>
+      <c r="J9" s="182"/>
+      <c r="K9" s="182"/>
+      <c r="L9" s="182"/>
+      <c r="M9" s="182"/>
+      <c r="N9" s="182"/>
+      <c r="O9" s="182"/>
+      <c r="P9" s="182"/>
       <c r="Q9" s="22"/>
       <c r="R9" s="90"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A10" s="197"/>
-      <c r="B10" s="209"/>
-      <c r="C10" s="168"/>
-      <c r="D10" s="186"/>
-      <c r="E10" s="170"/>
+      <c r="A10" s="212"/>
+      <c r="B10" s="275"/>
+      <c r="C10" s="173"/>
+      <c r="D10" s="175"/>
+      <c r="E10" s="177"/>
       <c r="F10" s="10" t="s">
         <v>195</v>
       </c>
       <c r="G10" s="135">
         <v>19816</v>
       </c>
-      <c r="H10" s="165" t="s">
+      <c r="H10" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I10" s="166"/>
-      <c r="J10" s="166"/>
-      <c r="K10" s="166"/>
-      <c r="L10" s="166"/>
-      <c r="M10" s="166"/>
-      <c r="N10" s="166"/>
-      <c r="O10" s="166"/>
-      <c r="P10" s="166"/>
+      <c r="I10" s="182"/>
+      <c r="J10" s="182"/>
+      <c r="K10" s="182"/>
+      <c r="L10" s="182"/>
+      <c r="M10" s="182"/>
+      <c r="N10" s="182"/>
+      <c r="O10" s="182"/>
+      <c r="P10" s="182"/>
       <c r="Q10" s="22"/>
       <c r="R10" s="90"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" s="197"/>
-      <c r="B11" s="209"/>
-      <c r="C11" s="168"/>
-      <c r="D11" s="186"/>
-      <c r="E11" s="170"/>
+      <c r="A11" s="212"/>
+      <c r="B11" s="275"/>
+      <c r="C11" s="173"/>
+      <c r="D11" s="175"/>
+      <c r="E11" s="177"/>
       <c r="F11" s="76" t="s">
         <v>196</v>
       </c>
       <c r="G11" s="136">
         <v>19817</v>
       </c>
-      <c r="H11" s="165" t="s">
+      <c r="H11" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I11" s="166"/>
-      <c r="J11" s="166"/>
-      <c r="K11" s="166"/>
-      <c r="L11" s="166"/>
-      <c r="M11" s="166"/>
-      <c r="N11" s="166"/>
-      <c r="O11" s="166"/>
-      <c r="P11" s="166"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="182"/>
+      <c r="L11" s="182"/>
+      <c r="M11" s="182"/>
+      <c r="N11" s="182"/>
+      <c r="O11" s="182"/>
+      <c r="P11" s="182"/>
       <c r="Q11" s="22"/>
       <c r="R11" s="90"/>
     </row>
     <row r="12" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A12" s="197"/>
-      <c r="B12" s="209"/>
+      <c r="A12" s="212"/>
+      <c r="B12" s="275"/>
       <c r="C12" s="146" t="s">
         <v>96</v>
       </c>
@@ -3687,30 +3696,30 @@
       <c r="G12" s="135">
         <v>12437</v>
       </c>
-      <c r="H12" s="165" t="s">
+      <c r="H12" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I12" s="166"/>
-      <c r="J12" s="166"/>
-      <c r="K12" s="166"/>
-      <c r="L12" s="166"/>
-      <c r="M12" s="166"/>
-      <c r="N12" s="166"/>
-      <c r="O12" s="166"/>
-      <c r="P12" s="166"/>
+      <c r="I12" s="182"/>
+      <c r="J12" s="182"/>
+      <c r="K12" s="182"/>
+      <c r="L12" s="182"/>
+      <c r="M12" s="182"/>
+      <c r="N12" s="182"/>
+      <c r="O12" s="182"/>
+      <c r="P12" s="182"/>
       <c r="Q12" s="22"/>
       <c r="R12" s="90"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A13" s="197"/>
-      <c r="B13" s="209"/>
-      <c r="C13" s="184" t="s">
+      <c r="A13" s="212"/>
+      <c r="B13" s="275"/>
+      <c r="C13" s="196" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="189">
+      <c r="D13" s="282">
         <v>22</v>
       </c>
-      <c r="E13" s="170">
+      <c r="E13" s="177">
         <v>520024985</v>
       </c>
       <c r="F13" s="147" t="s">
@@ -3719,155 +3728,155 @@
       <c r="G13" s="145">
         <v>7960</v>
       </c>
-      <c r="H13" s="165" t="s">
+      <c r="H13" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I13" s="166"/>
-      <c r="J13" s="166"/>
-      <c r="K13" s="166"/>
-      <c r="L13" s="166"/>
-      <c r="M13" s="166"/>
-      <c r="N13" s="166"/>
-      <c r="O13" s="166"/>
-      <c r="P13" s="166"/>
+      <c r="I13" s="182"/>
+      <c r="J13" s="182"/>
+      <c r="K13" s="182"/>
+      <c r="L13" s="182"/>
+      <c r="M13" s="182"/>
+      <c r="N13" s="182"/>
+      <c r="O13" s="182"/>
+      <c r="P13" s="182"/>
       <c r="Q13" s="74" t="s">
         <v>344</v>
       </c>
       <c r="R13" s="90"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A14" s="197"/>
-      <c r="B14" s="209"/>
-      <c r="C14" s="184"/>
-      <c r="D14" s="189"/>
-      <c r="E14" s="170"/>
+      <c r="A14" s="212"/>
+      <c r="B14" s="275"/>
+      <c r="C14" s="196"/>
+      <c r="D14" s="282"/>
+      <c r="E14" s="177"/>
       <c r="F14" s="78" t="s">
         <v>353</v>
       </c>
       <c r="G14" s="135">
         <v>9888</v>
       </c>
-      <c r="H14" s="165" t="s">
+      <c r="H14" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I14" s="166"/>
-      <c r="J14" s="166"/>
-      <c r="K14" s="166"/>
-      <c r="L14" s="166"/>
-      <c r="M14" s="166"/>
-      <c r="N14" s="166"/>
-      <c r="O14" s="166"/>
-      <c r="P14" s="166"/>
+      <c r="I14" s="182"/>
+      <c r="J14" s="182"/>
+      <c r="K14" s="182"/>
+      <c r="L14" s="182"/>
+      <c r="M14" s="182"/>
+      <c r="N14" s="182"/>
+      <c r="O14" s="182"/>
+      <c r="P14" s="182"/>
       <c r="Q14" s="74"/>
       <c r="R14" s="90"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A15" s="197"/>
-      <c r="B15" s="209"/>
-      <c r="C15" s="184"/>
-      <c r="D15" s="189"/>
-      <c r="E15" s="170"/>
+      <c r="A15" s="212"/>
+      <c r="B15" s="275"/>
+      <c r="C15" s="196"/>
+      <c r="D15" s="282"/>
+      <c r="E15" s="177"/>
       <c r="F15" s="78" t="s">
         <v>354</v>
       </c>
       <c r="G15" s="135">
         <v>9886</v>
       </c>
-      <c r="H15" s="165" t="s">
+      <c r="H15" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I15" s="166"/>
-      <c r="J15" s="166"/>
-      <c r="K15" s="166"/>
-      <c r="L15" s="166"/>
-      <c r="M15" s="166"/>
-      <c r="N15" s="166"/>
-      <c r="O15" s="166"/>
-      <c r="P15" s="166"/>
+      <c r="I15" s="182"/>
+      <c r="J15" s="182"/>
+      <c r="K15" s="182"/>
+      <c r="L15" s="182"/>
+      <c r="M15" s="182"/>
+      <c r="N15" s="182"/>
+      <c r="O15" s="182"/>
+      <c r="P15" s="182"/>
       <c r="Q15" s="74"/>
       <c r="R15" s="90"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A16" s="197"/>
-      <c r="B16" s="209"/>
-      <c r="C16" s="184"/>
-      <c r="D16" s="189"/>
-      <c r="E16" s="170"/>
+      <c r="A16" s="212"/>
+      <c r="B16" s="275"/>
+      <c r="C16" s="196"/>
+      <c r="D16" s="282"/>
+      <c r="E16" s="177"/>
       <c r="F16" s="78" t="s">
         <v>355</v>
       </c>
       <c r="G16" s="135">
         <v>7961</v>
       </c>
-      <c r="H16" s="165" t="s">
+      <c r="H16" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I16" s="166"/>
-      <c r="J16" s="166"/>
-      <c r="K16" s="166"/>
-      <c r="L16" s="166"/>
-      <c r="M16" s="166"/>
-      <c r="N16" s="166"/>
-      <c r="O16" s="166"/>
-      <c r="P16" s="166"/>
+      <c r="I16" s="182"/>
+      <c r="J16" s="182"/>
+      <c r="K16" s="182"/>
+      <c r="L16" s="182"/>
+      <c r="M16" s="182"/>
+      <c r="N16" s="182"/>
+      <c r="O16" s="182"/>
+      <c r="P16" s="182"/>
       <c r="Q16" s="22"/>
       <c r="R16" s="90"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" s="197"/>
-      <c r="B17" s="209"/>
-      <c r="C17" s="184"/>
-      <c r="D17" s="189"/>
-      <c r="E17" s="170"/>
+      <c r="A17" s="212"/>
+      <c r="B17" s="275"/>
+      <c r="C17" s="196"/>
+      <c r="D17" s="282"/>
+      <c r="E17" s="177"/>
       <c r="F17" s="78" t="s">
         <v>356</v>
       </c>
       <c r="G17" s="135">
         <v>9887</v>
       </c>
-      <c r="H17" s="165" t="s">
+      <c r="H17" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I17" s="166"/>
-      <c r="J17" s="166"/>
-      <c r="K17" s="166"/>
-      <c r="L17" s="166"/>
-      <c r="M17" s="166"/>
-      <c r="N17" s="166"/>
-      <c r="O17" s="166"/>
-      <c r="P17" s="166"/>
+      <c r="I17" s="182"/>
+      <c r="J17" s="182"/>
+      <c r="K17" s="182"/>
+      <c r="L17" s="182"/>
+      <c r="M17" s="182"/>
+      <c r="N17" s="182"/>
+      <c r="O17" s="182"/>
+      <c r="P17" s="182"/>
       <c r="Q17" s="22"/>
       <c r="R17" s="90"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A18" s="197"/>
-      <c r="B18" s="209"/>
-      <c r="C18" s="185"/>
-      <c r="D18" s="190"/>
-      <c r="E18" s="182"/>
+      <c r="A18" s="212"/>
+      <c r="B18" s="275"/>
+      <c r="C18" s="194"/>
+      <c r="D18" s="283"/>
+      <c r="E18" s="178"/>
       <c r="F18" s="78" t="s">
         <v>357</v>
       </c>
       <c r="G18" s="135">
         <v>9889</v>
       </c>
-      <c r="H18" s="165" t="s">
+      <c r="H18" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I18" s="166"/>
-      <c r="J18" s="166"/>
-      <c r="K18" s="166"/>
-      <c r="L18" s="166"/>
-      <c r="M18" s="166"/>
-      <c r="N18" s="166"/>
-      <c r="O18" s="166"/>
-      <c r="P18" s="166"/>
+      <c r="I18" s="182"/>
+      <c r="J18" s="182"/>
+      <c r="K18" s="182"/>
+      <c r="L18" s="182"/>
+      <c r="M18" s="182"/>
+      <c r="N18" s="182"/>
+      <c r="O18" s="182"/>
+      <c r="P18" s="182"/>
       <c r="Q18" s="22"/>
       <c r="R18" s="90"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A19" s="197"/>
-      <c r="B19" s="209"/>
+      <c r="A19" s="212"/>
+      <c r="B19" s="275"/>
       <c r="C19" s="79" t="s">
         <v>13</v>
       </c>
@@ -3906,8 +3915,8 @@
       <c r="R19" s="90"/>
     </row>
     <row r="20" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A20" s="197"/>
-      <c r="B20" s="209"/>
+      <c r="A20" s="212"/>
+      <c r="B20" s="275"/>
       <c r="C20" s="79" t="s">
         <v>11</v>
       </c>
@@ -3946,15 +3955,15 @@
       <c r="R20" s="90"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A21" s="197"/>
-      <c r="B21" s="209"/>
-      <c r="C21" s="167" t="s">
+      <c r="A21" s="212"/>
+      <c r="B21" s="275"/>
+      <c r="C21" s="183" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="188">
+      <c r="D21" s="184">
         <v>24</v>
       </c>
-      <c r="E21" s="169">
+      <c r="E21" s="185">
         <v>520031824</v>
       </c>
       <c r="F21" s="10" t="s">
@@ -3963,162 +3972,162 @@
       <c r="G21" s="135">
         <v>8067</v>
       </c>
-      <c r="H21" s="165" t="s">
+      <c r="H21" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I21" s="166"/>
-      <c r="J21" s="166"/>
-      <c r="K21" s="166"/>
-      <c r="L21" s="166"/>
-      <c r="M21" s="166"/>
-      <c r="N21" s="166"/>
-      <c r="O21" s="166"/>
-      <c r="P21" s="166"/>
+      <c r="I21" s="182"/>
+      <c r="J21" s="182"/>
+      <c r="K21" s="182"/>
+      <c r="L21" s="182"/>
+      <c r="M21" s="182"/>
+      <c r="N21" s="182"/>
+      <c r="O21" s="182"/>
+      <c r="P21" s="182"/>
       <c r="Q21" s="50" t="s">
         <v>345</v>
       </c>
       <c r="R21" s="90"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A22" s="197"/>
-      <c r="B22" s="209"/>
-      <c r="C22" s="168"/>
-      <c r="D22" s="186"/>
-      <c r="E22" s="170"/>
+      <c r="A22" s="212"/>
+      <c r="B22" s="275"/>
+      <c r="C22" s="173"/>
+      <c r="D22" s="175"/>
+      <c r="E22" s="177"/>
       <c r="F22" s="10" t="s">
         <v>359</v>
       </c>
       <c r="G22" s="135">
         <v>8062</v>
       </c>
-      <c r="H22" s="165" t="s">
+      <c r="H22" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I22" s="166"/>
-      <c r="J22" s="166"/>
-      <c r="K22" s="166"/>
-      <c r="L22" s="166"/>
-      <c r="M22" s="166"/>
-      <c r="N22" s="166"/>
-      <c r="O22" s="166"/>
-      <c r="P22" s="166"/>
+      <c r="I22" s="182"/>
+      <c r="J22" s="182"/>
+      <c r="K22" s="182"/>
+      <c r="L22" s="182"/>
+      <c r="M22" s="182"/>
+      <c r="N22" s="182"/>
+      <c r="O22" s="182"/>
+      <c r="P22" s="182"/>
       <c r="Q22" s="50"/>
       <c r="R22" s="90"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A23" s="197"/>
-      <c r="B23" s="209"/>
-      <c r="C23" s="168"/>
-      <c r="D23" s="186"/>
-      <c r="E23" s="170"/>
+      <c r="A23" s="212"/>
+      <c r="B23" s="275"/>
+      <c r="C23" s="173"/>
+      <c r="D23" s="175"/>
+      <c r="E23" s="177"/>
       <c r="F23" s="10" t="s">
         <v>0</v>
       </c>
       <c r="G23" s="135">
         <v>8068</v>
       </c>
-      <c r="H23" s="165" t="s">
+      <c r="H23" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I23" s="166"/>
-      <c r="J23" s="166"/>
-      <c r="K23" s="166"/>
-      <c r="L23" s="166"/>
-      <c r="M23" s="166"/>
-      <c r="N23" s="166"/>
-      <c r="O23" s="166"/>
-      <c r="P23" s="166"/>
+      <c r="I23" s="182"/>
+      <c r="J23" s="182"/>
+      <c r="K23" s="182"/>
+      <c r="L23" s="182"/>
+      <c r="M23" s="182"/>
+      <c r="N23" s="182"/>
+      <c r="O23" s="182"/>
+      <c r="P23" s="182"/>
       <c r="Q23" s="22"/>
       <c r="R23" s="90"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A24" s="197"/>
-      <c r="B24" s="209"/>
-      <c r="C24" s="168"/>
-      <c r="D24" s="186"/>
-      <c r="E24" s="170"/>
+      <c r="A24" s="212"/>
+      <c r="B24" s="275"/>
+      <c r="C24" s="173"/>
+      <c r="D24" s="175"/>
+      <c r="E24" s="177"/>
       <c r="F24" s="10" t="s">
         <v>1</v>
       </c>
       <c r="G24" s="135">
         <v>8061</v>
       </c>
-      <c r="H24" s="165" t="s">
+      <c r="H24" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I24" s="166"/>
-      <c r="J24" s="166"/>
-      <c r="K24" s="166"/>
-      <c r="L24" s="166"/>
-      <c r="M24" s="166"/>
-      <c r="N24" s="166"/>
-      <c r="O24" s="166"/>
-      <c r="P24" s="166"/>
+      <c r="I24" s="182"/>
+      <c r="J24" s="182"/>
+      <c r="K24" s="182"/>
+      <c r="L24" s="182"/>
+      <c r="M24" s="182"/>
+      <c r="N24" s="182"/>
+      <c r="O24" s="182"/>
+      <c r="P24" s="182"/>
       <c r="Q24" s="22"/>
       <c r="R24" s="90"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A25" s="197"/>
-      <c r="B25" s="209"/>
-      <c r="C25" s="168"/>
-      <c r="D25" s="186"/>
-      <c r="E25" s="170"/>
+      <c r="A25" s="212"/>
+      <c r="B25" s="275"/>
+      <c r="C25" s="173"/>
+      <c r="D25" s="175"/>
+      <c r="E25" s="177"/>
       <c r="F25" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G25" s="135">
         <v>14627</v>
       </c>
-      <c r="H25" s="165" t="s">
+      <c r="H25" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I25" s="166"/>
-      <c r="J25" s="166"/>
-      <c r="K25" s="166"/>
-      <c r="L25" s="166"/>
-      <c r="M25" s="166"/>
-      <c r="N25" s="166"/>
-      <c r="O25" s="166"/>
-      <c r="P25" s="166"/>
+      <c r="I25" s="182"/>
+      <c r="J25" s="182"/>
+      <c r="K25" s="182"/>
+      <c r="L25" s="182"/>
+      <c r="M25" s="182"/>
+      <c r="N25" s="182"/>
+      <c r="O25" s="182"/>
+      <c r="P25" s="182"/>
       <c r="Q25" s="22"/>
       <c r="R25" s="90"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A26" s="197"/>
-      <c r="B26" s="209"/>
-      <c r="C26" s="183"/>
-      <c r="D26" s="187"/>
-      <c r="E26" s="182"/>
+      <c r="A26" s="212"/>
+      <c r="B26" s="275"/>
+      <c r="C26" s="174"/>
+      <c r="D26" s="176"/>
+      <c r="E26" s="178"/>
       <c r="F26" s="75" t="s">
         <v>16</v>
       </c>
       <c r="G26" s="135">
         <v>20640</v>
       </c>
-      <c r="H26" s="165" t="s">
+      <c r="H26" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I26" s="166"/>
-      <c r="J26" s="166"/>
-      <c r="K26" s="166"/>
-      <c r="L26" s="166"/>
-      <c r="M26" s="166"/>
-      <c r="N26" s="166"/>
-      <c r="O26" s="166"/>
-      <c r="P26" s="166"/>
+      <c r="I26" s="182"/>
+      <c r="J26" s="182"/>
+      <c r="K26" s="182"/>
+      <c r="L26" s="182"/>
+      <c r="M26" s="182"/>
+      <c r="N26" s="182"/>
+      <c r="O26" s="182"/>
+      <c r="P26" s="182"/>
       <c r="Q26" s="22"/>
       <c r="R26" s="90"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A27" s="197"/>
-      <c r="B27" s="209"/>
-      <c r="C27" s="192" t="s">
+      <c r="A27" s="212"/>
+      <c r="B27" s="275"/>
+      <c r="C27" s="218" t="s">
         <v>5</v>
       </c>
-      <c r="D27" s="191">
+      <c r="D27" s="200">
         <v>26</v>
       </c>
-      <c r="E27" s="193">
+      <c r="E27" s="221">
         <v>520032269</v>
       </c>
       <c r="F27" s="75" t="s">
@@ -4127,155 +4136,155 @@
       <c r="G27" s="135">
         <v>7089</v>
       </c>
-      <c r="H27" s="165" t="s">
+      <c r="H27" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I27" s="166"/>
-      <c r="J27" s="166"/>
-      <c r="K27" s="166"/>
-      <c r="L27" s="166"/>
-      <c r="M27" s="166"/>
-      <c r="N27" s="166"/>
-      <c r="O27" s="166"/>
-      <c r="P27" s="166"/>
+      <c r="I27" s="182"/>
+      <c r="J27" s="182"/>
+      <c r="K27" s="182"/>
+      <c r="L27" s="182"/>
+      <c r="M27" s="182"/>
+      <c r="N27" s="182"/>
+      <c r="O27" s="182"/>
+      <c r="P27" s="182"/>
       <c r="Q27" s="50" t="s">
         <v>346</v>
       </c>
       <c r="R27" s="90"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A28" s="197"/>
-      <c r="B28" s="209"/>
-      <c r="C28" s="192"/>
-      <c r="D28" s="191"/>
-      <c r="E28" s="193"/>
+      <c r="A28" s="212"/>
+      <c r="B28" s="275"/>
+      <c r="C28" s="218"/>
+      <c r="D28" s="200"/>
+      <c r="E28" s="221"/>
       <c r="F28" s="75" t="s">
         <v>349</v>
       </c>
       <c r="G28" s="135">
         <v>7090</v>
       </c>
-      <c r="H28" s="165" t="s">
+      <c r="H28" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I28" s="166"/>
-      <c r="J28" s="166"/>
-      <c r="K28" s="166"/>
-      <c r="L28" s="166"/>
-      <c r="M28" s="166"/>
-      <c r="N28" s="166"/>
-      <c r="O28" s="166"/>
-      <c r="P28" s="166"/>
+      <c r="I28" s="182"/>
+      <c r="J28" s="182"/>
+      <c r="K28" s="182"/>
+      <c r="L28" s="182"/>
+      <c r="M28" s="182"/>
+      <c r="N28" s="182"/>
+      <c r="O28" s="182"/>
+      <c r="P28" s="182"/>
       <c r="Q28" s="22"/>
       <c r="R28" s="90"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A29" s="197"/>
-      <c r="B29" s="209"/>
-      <c r="C29" s="192"/>
-      <c r="D29" s="191"/>
-      <c r="E29" s="193"/>
+      <c r="A29" s="212"/>
+      <c r="B29" s="275"/>
+      <c r="C29" s="218"/>
+      <c r="D29" s="200"/>
+      <c r="E29" s="221"/>
       <c r="F29" s="75" t="s">
         <v>350</v>
       </c>
       <c r="G29" s="135">
         <v>12333</v>
       </c>
-      <c r="H29" s="165" t="s">
+      <c r="H29" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I29" s="166"/>
-      <c r="J29" s="166"/>
-      <c r="K29" s="166"/>
-      <c r="L29" s="166"/>
-      <c r="M29" s="166"/>
-      <c r="N29" s="166"/>
-      <c r="O29" s="166"/>
-      <c r="P29" s="166"/>
+      <c r="I29" s="182"/>
+      <c r="J29" s="182"/>
+      <c r="K29" s="182"/>
+      <c r="L29" s="182"/>
+      <c r="M29" s="182"/>
+      <c r="N29" s="182"/>
+      <c r="O29" s="182"/>
+      <c r="P29" s="182"/>
       <c r="Q29" s="22"/>
       <c r="R29" s="90"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A30" s="197"/>
-      <c r="B30" s="209"/>
-      <c r="C30" s="192"/>
-      <c r="D30" s="191"/>
-      <c r="E30" s="193"/>
+      <c r="A30" s="212"/>
+      <c r="B30" s="275"/>
+      <c r="C30" s="218"/>
+      <c r="D30" s="200"/>
+      <c r="E30" s="221"/>
       <c r="F30" s="75" t="s">
         <v>351</v>
       </c>
       <c r="G30" s="135">
         <v>12334</v>
       </c>
-      <c r="H30" s="165" t="s">
+      <c r="H30" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I30" s="166"/>
-      <c r="J30" s="166"/>
-      <c r="K30" s="166"/>
-      <c r="L30" s="166"/>
-      <c r="M30" s="166"/>
-      <c r="N30" s="166"/>
-      <c r="O30" s="166"/>
-      <c r="P30" s="166"/>
+      <c r="I30" s="182"/>
+      <c r="J30" s="182"/>
+      <c r="K30" s="182"/>
+      <c r="L30" s="182"/>
+      <c r="M30" s="182"/>
+      <c r="N30" s="182"/>
+      <c r="O30" s="182"/>
+      <c r="P30" s="182"/>
       <c r="Q30" s="22"/>
       <c r="R30" s="90"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A31" s="197"/>
-      <c r="B31" s="209"/>
-      <c r="C31" s="192"/>
-      <c r="D31" s="191"/>
-      <c r="E31" s="193"/>
+      <c r="A31" s="212"/>
+      <c r="B31" s="275"/>
+      <c r="C31" s="218"/>
+      <c r="D31" s="200"/>
+      <c r="E31" s="221"/>
       <c r="F31" s="75" t="s">
         <v>208</v>
       </c>
       <c r="G31" s="135">
         <v>13985</v>
       </c>
-      <c r="H31" s="165" t="s">
+      <c r="H31" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I31" s="166"/>
-      <c r="J31" s="166"/>
-      <c r="K31" s="166"/>
-      <c r="L31" s="166"/>
-      <c r="M31" s="166"/>
-      <c r="N31" s="166"/>
-      <c r="O31" s="166"/>
-      <c r="P31" s="166"/>
+      <c r="I31" s="182"/>
+      <c r="J31" s="182"/>
+      <c r="K31" s="182"/>
+      <c r="L31" s="182"/>
+      <c r="M31" s="182"/>
+      <c r="N31" s="182"/>
+      <c r="O31" s="182"/>
+      <c r="P31" s="182"/>
       <c r="Q31" s="22"/>
       <c r="R31" s="90"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A32" s="197"/>
-      <c r="B32" s="209"/>
-      <c r="C32" s="192"/>
-      <c r="D32" s="191"/>
-      <c r="E32" s="193"/>
+      <c r="A32" s="212"/>
+      <c r="B32" s="275"/>
+      <c r="C32" s="218"/>
+      <c r="D32" s="200"/>
+      <c r="E32" s="221"/>
       <c r="F32" s="75" t="s">
         <v>209</v>
       </c>
       <c r="G32" s="135">
         <v>21032</v>
       </c>
-      <c r="H32" s="165" t="s">
+      <c r="H32" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I32" s="166"/>
-      <c r="J32" s="166"/>
-      <c r="K32" s="166"/>
-      <c r="L32" s="166"/>
-      <c r="M32" s="166"/>
-      <c r="N32" s="166"/>
-      <c r="O32" s="166"/>
-      <c r="P32" s="166"/>
+      <c r="I32" s="182"/>
+      <c r="J32" s="182"/>
+      <c r="K32" s="182"/>
+      <c r="L32" s="182"/>
+      <c r="M32" s="182"/>
+      <c r="N32" s="182"/>
+      <c r="O32" s="182"/>
+      <c r="P32" s="182"/>
       <c r="Q32" s="22"/>
       <c r="R32" s="90"/>
     </row>
     <row r="33" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A33" s="197"/>
-      <c r="B33" s="209"/>
+      <c r="A33" s="212"/>
+      <c r="B33" s="275"/>
       <c r="C33" s="79" t="s">
         <v>15</v>
       </c>
@@ -4291,30 +4300,30 @@
       <c r="G33" s="135">
         <v>20532</v>
       </c>
-      <c r="H33" s="165" t="s">
+      <c r="H33" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I33" s="166"/>
-      <c r="J33" s="166"/>
-      <c r="K33" s="166"/>
-      <c r="L33" s="166"/>
-      <c r="M33" s="166"/>
-      <c r="N33" s="166"/>
-      <c r="O33" s="166"/>
-      <c r="P33" s="166"/>
+      <c r="I33" s="182"/>
+      <c r="J33" s="182"/>
+      <c r="K33" s="182"/>
+      <c r="L33" s="182"/>
+      <c r="M33" s="182"/>
+      <c r="N33" s="182"/>
+      <c r="O33" s="182"/>
+      <c r="P33" s="182"/>
       <c r="Q33" s="22"/>
       <c r="R33" s="90"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A34" s="197"/>
-      <c r="B34" s="209"/>
-      <c r="C34" s="167" t="s">
+      <c r="A34" s="212"/>
+      <c r="B34" s="275"/>
+      <c r="C34" s="183" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="188">
+      <c r="D34" s="184">
         <v>1157</v>
       </c>
-      <c r="E34" s="169">
+      <c r="E34" s="185">
         <v>520042581</v>
       </c>
       <c r="F34" s="10" t="s">
@@ -4323,335 +4332,335 @@
       <c r="G34" s="135">
         <v>14647</v>
       </c>
-      <c r="H34" s="165" t="s">
+      <c r="H34" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I34" s="166"/>
-      <c r="J34" s="166"/>
-      <c r="K34" s="166"/>
-      <c r="L34" s="166"/>
-      <c r="M34" s="166"/>
-      <c r="N34" s="166"/>
-      <c r="O34" s="166"/>
-      <c r="P34" s="166"/>
+      <c r="I34" s="182"/>
+      <c r="J34" s="182"/>
+      <c r="K34" s="182"/>
+      <c r="L34" s="182"/>
+      <c r="M34" s="182"/>
+      <c r="N34" s="182"/>
+      <c r="O34" s="182"/>
+      <c r="P34" s="182"/>
       <c r="Q34" s="22"/>
       <c r="R34" s="90"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A35" s="197"/>
-      <c r="B35" s="209"/>
-      <c r="C35" s="168"/>
-      <c r="D35" s="186"/>
-      <c r="E35" s="170"/>
+      <c r="A35" s="212"/>
+      <c r="B35" s="275"/>
+      <c r="C35" s="173"/>
+      <c r="D35" s="175"/>
+      <c r="E35" s="177"/>
       <c r="F35" s="10" t="s">
         <v>211</v>
       </c>
       <c r="G35" s="135">
         <v>14648</v>
       </c>
-      <c r="H35" s="165" t="s">
+      <c r="H35" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I35" s="166"/>
-      <c r="J35" s="166"/>
-      <c r="K35" s="166"/>
-      <c r="L35" s="166"/>
-      <c r="M35" s="166"/>
-      <c r="N35" s="166"/>
-      <c r="O35" s="166"/>
-      <c r="P35" s="166"/>
+      <c r="I35" s="182"/>
+      <c r="J35" s="182"/>
+      <c r="K35" s="182"/>
+      <c r="L35" s="182"/>
+      <c r="M35" s="182"/>
+      <c r="N35" s="182"/>
+      <c r="O35" s="182"/>
+      <c r="P35" s="182"/>
       <c r="Q35" s="22"/>
       <c r="R35" s="90"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A36" s="197"/>
-      <c r="B36" s="209"/>
-      <c r="C36" s="168"/>
-      <c r="D36" s="186"/>
-      <c r="E36" s="170"/>
+      <c r="A36" s="212"/>
+      <c r="B36" s="275"/>
+      <c r="C36" s="173"/>
+      <c r="D36" s="175"/>
+      <c r="E36" s="177"/>
       <c r="F36" s="10" t="s">
         <v>212</v>
       </c>
       <c r="G36" s="135">
         <v>14649</v>
       </c>
-      <c r="H36" s="165" t="s">
+      <c r="H36" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I36" s="166"/>
-      <c r="J36" s="166"/>
-      <c r="K36" s="166"/>
-      <c r="L36" s="166"/>
-      <c r="M36" s="166"/>
-      <c r="N36" s="166"/>
-      <c r="O36" s="166"/>
-      <c r="P36" s="166"/>
+      <c r="I36" s="182"/>
+      <c r="J36" s="182"/>
+      <c r="K36" s="182"/>
+      <c r="L36" s="182"/>
+      <c r="M36" s="182"/>
+      <c r="N36" s="182"/>
+      <c r="O36" s="182"/>
+      <c r="P36" s="182"/>
       <c r="Q36" s="22"/>
       <c r="R36" s="90"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A37" s="197"/>
-      <c r="B37" s="209"/>
-      <c r="C37" s="168"/>
-      <c r="D37" s="186"/>
-      <c r="E37" s="170"/>
+      <c r="A37" s="212"/>
+      <c r="B37" s="275"/>
+      <c r="C37" s="173"/>
+      <c r="D37" s="175"/>
+      <c r="E37" s="177"/>
       <c r="F37" s="10" t="s">
         <v>213</v>
       </c>
       <c r="G37" s="135">
         <v>14650</v>
       </c>
-      <c r="H37" s="165" t="s">
+      <c r="H37" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I37" s="166"/>
-      <c r="J37" s="166"/>
-      <c r="K37" s="166"/>
-      <c r="L37" s="166"/>
-      <c r="M37" s="166"/>
-      <c r="N37" s="166"/>
-      <c r="O37" s="166"/>
-      <c r="P37" s="166"/>
+      <c r="I37" s="182"/>
+      <c r="J37" s="182"/>
+      <c r="K37" s="182"/>
+      <c r="L37" s="182"/>
+      <c r="M37" s="182"/>
+      <c r="N37" s="182"/>
+      <c r="O37" s="182"/>
+      <c r="P37" s="182"/>
       <c r="Q37" s="22"/>
       <c r="R37" s="90"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A38" s="197"/>
-      <c r="B38" s="209"/>
-      <c r="C38" s="168"/>
-      <c r="D38" s="186"/>
-      <c r="E38" s="170"/>
+      <c r="A38" s="212"/>
+      <c r="B38" s="275"/>
+      <c r="C38" s="173"/>
+      <c r="D38" s="175"/>
+      <c r="E38" s="177"/>
       <c r="F38" s="10" t="s">
         <v>214</v>
       </c>
       <c r="G38" s="135">
         <v>14651</v>
       </c>
-      <c r="H38" s="165" t="s">
+      <c r="H38" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I38" s="166"/>
-      <c r="J38" s="166"/>
-      <c r="K38" s="166"/>
-      <c r="L38" s="166"/>
-      <c r="M38" s="166"/>
-      <c r="N38" s="166"/>
-      <c r="O38" s="166"/>
-      <c r="P38" s="166"/>
+      <c r="I38" s="182"/>
+      <c r="J38" s="182"/>
+      <c r="K38" s="182"/>
+      <c r="L38" s="182"/>
+      <c r="M38" s="182"/>
+      <c r="N38" s="182"/>
+      <c r="O38" s="182"/>
+      <c r="P38" s="182"/>
       <c r="Q38" s="22"/>
       <c r="R38" s="90"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A39" s="197"/>
-      <c r="B39" s="209"/>
-      <c r="C39" s="168"/>
-      <c r="D39" s="186"/>
-      <c r="E39" s="170"/>
+      <c r="A39" s="212"/>
+      <c r="B39" s="275"/>
+      <c r="C39" s="173"/>
+      <c r="D39" s="175"/>
+      <c r="E39" s="177"/>
       <c r="F39" s="10" t="s">
         <v>215</v>
       </c>
       <c r="G39" s="135">
         <v>14652</v>
       </c>
-      <c r="H39" s="165" t="s">
+      <c r="H39" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I39" s="166"/>
-      <c r="J39" s="166"/>
-      <c r="K39" s="166"/>
-      <c r="L39" s="166"/>
-      <c r="M39" s="166"/>
-      <c r="N39" s="166"/>
-      <c r="O39" s="166"/>
-      <c r="P39" s="166"/>
+      <c r="I39" s="182"/>
+      <c r="J39" s="182"/>
+      <c r="K39" s="182"/>
+      <c r="L39" s="182"/>
+      <c r="M39" s="182"/>
+      <c r="N39" s="182"/>
+      <c r="O39" s="182"/>
+      <c r="P39" s="182"/>
       <c r="Q39" s="22"/>
       <c r="R39" s="90"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A40" s="197"/>
-      <c r="B40" s="209"/>
-      <c r="C40" s="168"/>
-      <c r="D40" s="186"/>
-      <c r="E40" s="170"/>
+      <c r="A40" s="212"/>
+      <c r="B40" s="275"/>
+      <c r="C40" s="173"/>
+      <c r="D40" s="175"/>
+      <c r="E40" s="177"/>
       <c r="F40" s="10" t="s">
         <v>216</v>
       </c>
       <c r="G40" s="135">
         <v>14657</v>
       </c>
-      <c r="H40" s="165" t="s">
+      <c r="H40" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I40" s="166"/>
-      <c r="J40" s="166"/>
-      <c r="K40" s="166"/>
-      <c r="L40" s="166"/>
-      <c r="M40" s="166"/>
-      <c r="N40" s="166"/>
-      <c r="O40" s="166"/>
-      <c r="P40" s="166"/>
+      <c r="I40" s="182"/>
+      <c r="J40" s="182"/>
+      <c r="K40" s="182"/>
+      <c r="L40" s="182"/>
+      <c r="M40" s="182"/>
+      <c r="N40" s="182"/>
+      <c r="O40" s="182"/>
+      <c r="P40" s="182"/>
       <c r="Q40" s="22"/>
       <c r="R40" s="90"/>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A41" s="197"/>
-      <c r="B41" s="209"/>
-      <c r="C41" s="168"/>
-      <c r="D41" s="186"/>
-      <c r="E41" s="170"/>
+      <c r="A41" s="212"/>
+      <c r="B41" s="275"/>
+      <c r="C41" s="173"/>
+      <c r="D41" s="175"/>
+      <c r="E41" s="177"/>
       <c r="F41" s="10" t="s">
         <v>217</v>
       </c>
       <c r="G41" s="135">
         <v>17435</v>
       </c>
-      <c r="H41" s="165" t="s">
+      <c r="H41" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I41" s="166"/>
-      <c r="J41" s="166"/>
-      <c r="K41" s="166"/>
-      <c r="L41" s="166"/>
-      <c r="M41" s="166"/>
-      <c r="N41" s="166"/>
-      <c r="O41" s="166"/>
-      <c r="P41" s="166"/>
+      <c r="I41" s="182"/>
+      <c r="J41" s="182"/>
+      <c r="K41" s="182"/>
+      <c r="L41" s="182"/>
+      <c r="M41" s="182"/>
+      <c r="N41" s="182"/>
+      <c r="O41" s="182"/>
+      <c r="P41" s="182"/>
       <c r="Q41" s="22"/>
       <c r="R41" s="90"/>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A42" s="197"/>
-      <c r="B42" s="209"/>
-      <c r="C42" s="168"/>
-      <c r="D42" s="186"/>
-      <c r="E42" s="170"/>
+      <c r="A42" s="212"/>
+      <c r="B42" s="275"/>
+      <c r="C42" s="173"/>
+      <c r="D42" s="175"/>
+      <c r="E42" s="177"/>
       <c r="F42" s="10" t="s">
         <v>218</v>
       </c>
       <c r="G42" s="135" t="s">
         <v>119</v>
       </c>
-      <c r="H42" s="165" t="s">
+      <c r="H42" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I42" s="166"/>
-      <c r="J42" s="166"/>
-      <c r="K42" s="166"/>
-      <c r="L42" s="166"/>
-      <c r="M42" s="166"/>
-      <c r="N42" s="166"/>
-      <c r="O42" s="166"/>
-      <c r="P42" s="166"/>
+      <c r="I42" s="182"/>
+      <c r="J42" s="182"/>
+      <c r="K42" s="182"/>
+      <c r="L42" s="182"/>
+      <c r="M42" s="182"/>
+      <c r="N42" s="182"/>
+      <c r="O42" s="182"/>
+      <c r="P42" s="182"/>
       <c r="Q42" s="22"/>
       <c r="R42" s="90"/>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A43" s="197"/>
-      <c r="B43" s="209"/>
-      <c r="C43" s="168"/>
-      <c r="D43" s="186"/>
-      <c r="E43" s="170"/>
+      <c r="A43" s="212"/>
+      <c r="B43" s="275"/>
+      <c r="C43" s="173"/>
+      <c r="D43" s="175"/>
+      <c r="E43" s="177"/>
       <c r="F43" s="10" t="s">
         <v>219</v>
       </c>
       <c r="G43" s="135" t="s">
         <v>120</v>
       </c>
-      <c r="H43" s="165" t="s">
+      <c r="H43" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I43" s="166"/>
-      <c r="J43" s="166"/>
-      <c r="K43" s="166"/>
-      <c r="L43" s="166"/>
-      <c r="M43" s="166"/>
-      <c r="N43" s="166"/>
-      <c r="O43" s="166"/>
-      <c r="P43" s="166"/>
+      <c r="I43" s="182"/>
+      <c r="J43" s="182"/>
+      <c r="K43" s="182"/>
+      <c r="L43" s="182"/>
+      <c r="M43" s="182"/>
+      <c r="N43" s="182"/>
+      <c r="O43" s="182"/>
+      <c r="P43" s="182"/>
       <c r="Q43" s="22"/>
       <c r="R43" s="90"/>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A44" s="197"/>
-      <c r="B44" s="209"/>
-      <c r="C44" s="168"/>
-      <c r="D44" s="186"/>
-      <c r="E44" s="170"/>
+      <c r="A44" s="212"/>
+      <c r="B44" s="275"/>
+      <c r="C44" s="173"/>
+      <c r="D44" s="175"/>
+      <c r="E44" s="177"/>
       <c r="F44" s="10" t="s">
         <v>220</v>
       </c>
       <c r="G44" s="135" t="s">
         <v>121</v>
       </c>
-      <c r="H44" s="165" t="s">
+      <c r="H44" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I44" s="166"/>
-      <c r="J44" s="166"/>
-      <c r="K44" s="166"/>
-      <c r="L44" s="166"/>
-      <c r="M44" s="166"/>
-      <c r="N44" s="166"/>
-      <c r="O44" s="166"/>
-      <c r="P44" s="166"/>
+      <c r="I44" s="182"/>
+      <c r="J44" s="182"/>
+      <c r="K44" s="182"/>
+      <c r="L44" s="182"/>
+      <c r="M44" s="182"/>
+      <c r="N44" s="182"/>
+      <c r="O44" s="182"/>
+      <c r="P44" s="182"/>
       <c r="Q44" s="22"/>
       <c r="R44" s="90"/>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A45" s="197"/>
-      <c r="B45" s="209"/>
-      <c r="C45" s="168"/>
-      <c r="D45" s="186"/>
-      <c r="E45" s="170"/>
+      <c r="A45" s="212"/>
+      <c r="B45" s="275"/>
+      <c r="C45" s="173"/>
+      <c r="D45" s="175"/>
+      <c r="E45" s="177"/>
       <c r="F45" s="10" t="s">
         <v>221</v>
       </c>
       <c r="G45" s="135" t="s">
         <v>122</v>
       </c>
-      <c r="H45" s="165" t="s">
+      <c r="H45" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I45" s="166"/>
-      <c r="J45" s="166"/>
-      <c r="K45" s="166"/>
-      <c r="L45" s="166"/>
-      <c r="M45" s="166"/>
-      <c r="N45" s="166"/>
-      <c r="O45" s="166"/>
-      <c r="P45" s="166"/>
+      <c r="I45" s="182"/>
+      <c r="J45" s="182"/>
+      <c r="K45" s="182"/>
+      <c r="L45" s="182"/>
+      <c r="M45" s="182"/>
+      <c r="N45" s="182"/>
+      <c r="O45" s="182"/>
+      <c r="P45" s="182"/>
       <c r="Q45" s="22"/>
       <c r="R45" s="90"/>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A46" s="197"/>
-      <c r="B46" s="209"/>
-      <c r="C46" s="183"/>
-      <c r="D46" s="187"/>
-      <c r="E46" s="182"/>
+      <c r="A46" s="212"/>
+      <c r="B46" s="275"/>
+      <c r="C46" s="174"/>
+      <c r="D46" s="176"/>
+      <c r="E46" s="178"/>
       <c r="F46" s="10" t="s">
         <v>222</v>
       </c>
       <c r="G46" s="135">
         <v>20669</v>
       </c>
-      <c r="H46" s="165" t="s">
+      <c r="H46" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I46" s="166"/>
-      <c r="J46" s="166"/>
-      <c r="K46" s="166"/>
-      <c r="L46" s="166"/>
-      <c r="M46" s="166"/>
-      <c r="N46" s="166"/>
-      <c r="O46" s="166"/>
-      <c r="P46" s="166"/>
+      <c r="I46" s="182"/>
+      <c r="J46" s="182"/>
+      <c r="K46" s="182"/>
+      <c r="L46" s="182"/>
+      <c r="M46" s="182"/>
+      <c r="N46" s="182"/>
+      <c r="O46" s="182"/>
+      <c r="P46" s="182"/>
       <c r="Q46" s="22"/>
       <c r="R46" s="90"/>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A47" s="197"/>
-      <c r="B47" s="209"/>
+      <c r="A47" s="212"/>
+      <c r="B47" s="275"/>
       <c r="C47" s="79" t="s">
         <v>8</v>
       </c>
@@ -4698,8 +4707,8 @@
       <c r="R47" s="90"/>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A48" s="197"/>
-      <c r="B48" s="209"/>
+      <c r="A48" s="212"/>
+      <c r="B48" s="275"/>
       <c r="C48" s="79" t="s">
         <v>6</v>
       </c>
@@ -4742,8 +4751,8 @@
       <c r="R48" s="90"/>
     </row>
     <row r="49" spans="1:18" ht="31" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="208"/>
-      <c r="B49" s="210"/>
+      <c r="A49" s="227"/>
+      <c r="B49" s="269"/>
       <c r="C49" s="80" t="s">
         <v>7</v>
       </c>
@@ -4759,34 +4768,34 @@
       <c r="G49" s="136">
         <v>11406</v>
       </c>
-      <c r="H49" s="194" t="s">
+      <c r="H49" s="186" t="s">
         <v>197</v>
       </c>
-      <c r="I49" s="195"/>
-      <c r="J49" s="195"/>
-      <c r="K49" s="195"/>
-      <c r="L49" s="195"/>
-      <c r="M49" s="195"/>
-      <c r="N49" s="195"/>
-      <c r="O49" s="195"/>
-      <c r="P49" s="195"/>
+      <c r="I49" s="187"/>
+      <c r="J49" s="187"/>
+      <c r="K49" s="187"/>
+      <c r="L49" s="187"/>
+      <c r="M49" s="187"/>
+      <c r="N49" s="187"/>
+      <c r="O49" s="187"/>
+      <c r="P49" s="187"/>
       <c r="Q49" s="94"/>
       <c r="R49" s="95"/>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A50" s="196" t="s">
+    <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="211" t="s">
         <v>21</v>
       </c>
-      <c r="B50" s="199" t="s">
+      <c r="B50" s="288" t="s">
         <v>197</v>
       </c>
-      <c r="C50" s="202" t="s">
+      <c r="C50" s="225" t="s">
         <v>20</v>
       </c>
       <c r="D50" s="99">
         <v>114</v>
       </c>
-      <c r="E50" s="271">
+      <c r="E50" s="191">
         <v>513011445</v>
       </c>
       <c r="F50" s="100" t="s">
@@ -4795,58 +4804,60 @@
       <c r="G50" s="134">
         <v>31</v>
       </c>
-      <c r="H50" s="203" t="s">
+      <c r="H50" s="271" t="s">
         <v>347</v>
       </c>
-      <c r="I50" s="203"/>
-      <c r="J50" s="203"/>
-      <c r="K50" s="203"/>
-      <c r="L50" s="203"/>
-      <c r="M50" s="203"/>
-      <c r="N50" s="203"/>
-      <c r="O50" s="203"/>
-      <c r="P50" s="203"/>
+      <c r="I50" s="271"/>
+      <c r="J50" s="271"/>
+      <c r="K50" s="271"/>
+      <c r="L50" s="271"/>
+      <c r="M50" s="271"/>
+      <c r="N50" s="271"/>
+      <c r="O50" s="271"/>
+      <c r="P50" s="271"/>
       <c r="Q50" s="88" t="s">
         <v>188</v>
       </c>
       <c r="R50" s="89"/>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A51" s="197"/>
-      <c r="B51" s="200"/>
-      <c r="C51" s="183"/>
+      <c r="A51" s="212"/>
+      <c r="B51" s="165"/>
+      <c r="C51" s="174"/>
       <c r="D51" s="13">
         <v>114</v>
       </c>
-      <c r="E51" s="272"/>
+      <c r="E51" s="192"/>
       <c r="F51" s="77" t="s">
         <v>231</v>
       </c>
       <c r="G51" s="135">
         <v>41</v>
       </c>
-      <c r="H51" s="204"/>
-      <c r="I51" s="204"/>
-      <c r="J51" s="204"/>
-      <c r="K51" s="204"/>
-      <c r="L51" s="204"/>
-      <c r="M51" s="204"/>
-      <c r="N51" s="204"/>
-      <c r="O51" s="204"/>
-      <c r="P51" s="204"/>
+      <c r="H51" s="272"/>
+      <c r="I51" s="272"/>
+      <c r="J51" s="272"/>
+      <c r="K51" s="272"/>
+      <c r="L51" s="272"/>
+      <c r="M51" s="272"/>
+      <c r="N51" s="272"/>
+      <c r="O51" s="272"/>
+      <c r="P51" s="272"/>
       <c r="Q51" s="6"/>
       <c r="R51" s="90"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A52" s="197"/>
-      <c r="B52" s="200"/>
-      <c r="C52" s="192" t="s">
+    <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="212"/>
+      <c r="B52" s="218" t="s">
         <v>101</v>
+      </c>
+      <c r="C52" s="79" t="s">
+        <v>22</v>
       </c>
       <c r="D52" s="12">
         <v>116</v>
       </c>
-      <c r="E52" s="269">
+      <c r="E52" s="189">
         <v>520030677</v>
       </c>
       <c r="F52" s="76" t="s">
@@ -4855,48 +4866,50 @@
       <c r="G52" s="135">
         <v>10</v>
       </c>
-      <c r="H52" s="206" t="s">
+      <c r="H52" s="273" t="s">
         <v>347</v>
       </c>
-      <c r="I52" s="206"/>
-      <c r="J52" s="206"/>
-      <c r="K52" s="206"/>
-      <c r="L52" s="206"/>
-      <c r="M52" s="206"/>
-      <c r="N52" s="206"/>
-      <c r="O52" s="206"/>
-      <c r="P52" s="206"/>
+      <c r="I52" s="273"/>
+      <c r="J52" s="273"/>
+      <c r="K52" s="273"/>
+      <c r="L52" s="273"/>
+      <c r="M52" s="273"/>
+      <c r="N52" s="273"/>
+      <c r="O52" s="273"/>
+      <c r="P52" s="273"/>
       <c r="Q52" s="6"/>
       <c r="R52" s="90"/>
     </row>
     <row r="53" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="198"/>
-      <c r="B53" s="201"/>
-      <c r="C53" s="205"/>
+      <c r="A53" s="213"/>
+      <c r="B53" s="219"/>
+      <c r="C53" s="79" t="s">
+        <v>380</v>
+      </c>
       <c r="D53" s="91">
         <v>96</v>
       </c>
-      <c r="E53" s="270"/>
+      <c r="E53" s="190"/>
       <c r="F53" s="92" t="s">
         <v>100</v>
       </c>
       <c r="G53" s="137">
         <v>20</v>
       </c>
-      <c r="H53" s="207"/>
-      <c r="I53" s="207"/>
-      <c r="J53" s="207"/>
-      <c r="K53" s="207"/>
-      <c r="L53" s="207"/>
-      <c r="M53" s="207"/>
-      <c r="N53" s="207"/>
-      <c r="O53" s="207"/>
-      <c r="P53" s="207"/>
+      <c r="H53" s="274"/>
+      <c r="I53" s="274"/>
+      <c r="J53" s="274"/>
+      <c r="K53" s="274"/>
+      <c r="L53" s="274"/>
+      <c r="M53" s="274"/>
+      <c r="N53" s="274"/>
+      <c r="O53" s="274"/>
+      <c r="P53" s="274"/>
       <c r="Q53" s="102"/>
       <c r="R53" s="93"/>
     </row>
     <row r="54" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="196" t="s">
+      <c r="A54" s="211" t="s">
         <v>23</v>
       </c>
       <c r="B54" s="83" t="s">
@@ -4917,22 +4930,22 @@
       <c r="G54" s="138">
         <v>100</v>
       </c>
-      <c r="H54" s="218" t="s">
+      <c r="H54" s="266" t="s">
         <v>347</v>
       </c>
-      <c r="I54" s="219"/>
-      <c r="J54" s="219"/>
-      <c r="K54" s="219"/>
-      <c r="L54" s="219"/>
-      <c r="M54" s="219"/>
-      <c r="N54" s="219"/>
-      <c r="O54" s="219"/>
-      <c r="P54" s="219"/>
+      <c r="I54" s="267"/>
+      <c r="J54" s="267"/>
+      <c r="K54" s="267"/>
+      <c r="L54" s="267"/>
+      <c r="M54" s="267"/>
+      <c r="N54" s="267"/>
+      <c r="O54" s="267"/>
+      <c r="P54" s="267"/>
       <c r="Q54" s="88"/>
       <c r="R54" s="89"/>
     </row>
     <row r="55" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A55" s="197"/>
+      <c r="A55" s="212"/>
       <c r="B55" s="1" t="s">
         <v>197</v>
       </c>
@@ -4951,32 +4964,32 @@
       <c r="G55" s="145">
         <v>100</v>
       </c>
-      <c r="H55" s="220" t="s">
+      <c r="H55" s="256" t="s">
         <v>347</v>
       </c>
-      <c r="I55" s="221"/>
-      <c r="J55" s="221"/>
-      <c r="K55" s="221"/>
-      <c r="L55" s="221"/>
-      <c r="M55" s="221"/>
-      <c r="N55" s="221"/>
-      <c r="O55" s="221"/>
-      <c r="P55" s="221"/>
+      <c r="I55" s="257"/>
+      <c r="J55" s="257"/>
+      <c r="K55" s="257"/>
+      <c r="L55" s="257"/>
+      <c r="M55" s="257"/>
+      <c r="N55" s="257"/>
+      <c r="O55" s="257"/>
+      <c r="P55" s="257"/>
       <c r="Q55" s="6"/>
       <c r="R55" s="90"/>
     </row>
     <row r="56" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="197"/>
-      <c r="B56" s="210" t="s">
+      <c r="A56" s="212"/>
+      <c r="B56" s="269" t="s">
         <v>24</v>
       </c>
-      <c r="C56" s="175" t="s">
+      <c r="C56" s="268" t="s">
         <v>25</v>
       </c>
-      <c r="D56" s="191">
+      <c r="D56" s="200">
         <v>1203</v>
       </c>
-      <c r="E56" s="193">
+      <c r="E56" s="221">
         <v>520028861</v>
       </c>
       <c r="F56" s="10" t="s">
@@ -4985,75 +4998,75 @@
       <c r="G56" s="135" t="s">
         <v>124</v>
       </c>
-      <c r="H56" s="165" t="s">
+      <c r="H56" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I56" s="166"/>
-      <c r="J56" s="166"/>
-      <c r="K56" s="166"/>
-      <c r="L56" s="166"/>
-      <c r="M56" s="166"/>
-      <c r="N56" s="166"/>
-      <c r="O56" s="166"/>
-      <c r="P56" s="166"/>
+      <c r="I56" s="182"/>
+      <c r="J56" s="182"/>
+      <c r="K56" s="182"/>
+      <c r="L56" s="182"/>
+      <c r="M56" s="182"/>
+      <c r="N56" s="182"/>
+      <c r="O56" s="182"/>
+      <c r="P56" s="182"/>
       <c r="Q56" s="6"/>
       <c r="R56" s="90"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A57" s="197"/>
-      <c r="B57" s="224"/>
-      <c r="C57" s="175"/>
-      <c r="D57" s="191"/>
-      <c r="E57" s="193"/>
+      <c r="A57" s="212"/>
+      <c r="B57" s="270"/>
+      <c r="C57" s="268"/>
+      <c r="D57" s="200"/>
+      <c r="E57" s="221"/>
       <c r="F57" s="10" t="s">
         <v>234</v>
       </c>
       <c r="G57" s="135" t="s">
         <v>125</v>
       </c>
-      <c r="H57" s="165" t="s">
+      <c r="H57" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I57" s="166"/>
-      <c r="J57" s="166"/>
-      <c r="K57" s="166"/>
-      <c r="L57" s="166"/>
-      <c r="M57" s="166"/>
-      <c r="N57" s="166"/>
-      <c r="O57" s="166"/>
-      <c r="P57" s="166"/>
+      <c r="I57" s="182"/>
+      <c r="J57" s="182"/>
+      <c r="K57" s="182"/>
+      <c r="L57" s="182"/>
+      <c r="M57" s="182"/>
+      <c r="N57" s="182"/>
+      <c r="O57" s="182"/>
+      <c r="P57" s="182"/>
       <c r="Q57" s="6"/>
       <c r="R57" s="90"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A58" s="197"/>
-      <c r="B58" s="224"/>
-      <c r="C58" s="175"/>
-      <c r="D58" s="191"/>
-      <c r="E58" s="193"/>
+      <c r="A58" s="212"/>
+      <c r="B58" s="270"/>
+      <c r="C58" s="268"/>
+      <c r="D58" s="200"/>
+      <c r="E58" s="221"/>
       <c r="F58" s="10" t="s">
         <v>235</v>
       </c>
       <c r="G58" s="135" t="s">
         <v>126</v>
       </c>
-      <c r="H58" s="165" t="s">
+      <c r="H58" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I58" s="166"/>
-      <c r="J58" s="166"/>
-      <c r="K58" s="166"/>
-      <c r="L58" s="166"/>
-      <c r="M58" s="166"/>
-      <c r="N58" s="166"/>
-      <c r="O58" s="166"/>
-      <c r="P58" s="166"/>
+      <c r="I58" s="182"/>
+      <c r="J58" s="182"/>
+      <c r="K58" s="182"/>
+      <c r="L58" s="182"/>
+      <c r="M58" s="182"/>
+      <c r="N58" s="182"/>
+      <c r="O58" s="182"/>
+      <c r="P58" s="182"/>
       <c r="Q58" s="6"/>
       <c r="R58" s="90"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A59" s="197"/>
-      <c r="B59" s="224"/>
+      <c r="A59" s="212"/>
+      <c r="B59" s="270"/>
       <c r="C59" s="79" t="s">
         <v>26</v>
       </c>
@@ -5069,23 +5082,23 @@
       <c r="G59" s="135" t="s">
         <v>127</v>
       </c>
-      <c r="H59" s="165" t="s">
+      <c r="H59" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I59" s="166"/>
-      <c r="J59" s="166"/>
-      <c r="K59" s="166"/>
-      <c r="L59" s="166"/>
-      <c r="M59" s="166"/>
-      <c r="N59" s="166"/>
-      <c r="O59" s="166"/>
-      <c r="P59" s="166"/>
+      <c r="I59" s="182"/>
+      <c r="J59" s="182"/>
+      <c r="K59" s="182"/>
+      <c r="L59" s="182"/>
+      <c r="M59" s="182"/>
+      <c r="N59" s="182"/>
+      <c r="O59" s="182"/>
+      <c r="P59" s="182"/>
       <c r="Q59" s="6"/>
       <c r="R59" s="90"/>
     </row>
     <row r="60" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A60" s="197"/>
-      <c r="B60" s="224"/>
+      <c r="A60" s="212"/>
+      <c r="B60" s="270"/>
       <c r="C60" s="79" t="s">
         <v>27</v>
       </c>
@@ -5101,23 +5114,23 @@
       <c r="G60" s="135" t="s">
         <v>128</v>
       </c>
-      <c r="H60" s="165" t="s">
+      <c r="H60" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I60" s="166"/>
-      <c r="J60" s="166"/>
-      <c r="K60" s="166"/>
-      <c r="L60" s="166"/>
-      <c r="M60" s="166"/>
-      <c r="N60" s="166"/>
-      <c r="O60" s="166"/>
-      <c r="P60" s="166"/>
+      <c r="I60" s="182"/>
+      <c r="J60" s="182"/>
+      <c r="K60" s="182"/>
+      <c r="L60" s="182"/>
+      <c r="M60" s="182"/>
+      <c r="N60" s="182"/>
+      <c r="O60" s="182"/>
+      <c r="P60" s="182"/>
       <c r="Q60" s="6"/>
       <c r="R60" s="90"/>
     </row>
     <row r="61" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A61" s="208"/>
-      <c r="B61" s="224"/>
+      <c r="A61" s="227"/>
+      <c r="B61" s="270"/>
       <c r="C61" s="146" t="s">
         <v>28</v>
       </c>
@@ -5133,30 +5146,30 @@
       <c r="G61" s="135" t="s">
         <v>129</v>
       </c>
-      <c r="H61" s="280" t="s">
+      <c r="H61" s="172" t="s">
         <v>197</v>
       </c>
-      <c r="I61" s="280"/>
-      <c r="J61" s="280"/>
-      <c r="K61" s="280"/>
-      <c r="L61" s="280"/>
-      <c r="M61" s="280"/>
-      <c r="N61" s="280"/>
-      <c r="O61" s="280"/>
-      <c r="P61" s="280"/>
+      <c r="I61" s="172"/>
+      <c r="J61" s="172"/>
+      <c r="K61" s="172"/>
+      <c r="L61" s="172"/>
+      <c r="M61" s="172"/>
+      <c r="N61" s="172"/>
+      <c r="O61" s="172"/>
+      <c r="P61" s="172"/>
       <c r="Q61" s="6"/>
       <c r="R61" s="6"/>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A62" s="208"/>
-      <c r="B62" s="224"/>
-      <c r="C62" s="168" t="s">
+      <c r="A62" s="227"/>
+      <c r="B62" s="270"/>
+      <c r="C62" s="173" t="s">
         <v>90</v>
       </c>
-      <c r="D62" s="186">
+      <c r="D62" s="175">
         <v>98</v>
       </c>
-      <c r="E62" s="170">
+      <c r="E62" s="177">
         <v>520031659</v>
       </c>
       <c r="F62" s="132" t="s">
@@ -5165,56 +5178,56 @@
       <c r="G62" s="145" t="s">
         <v>159</v>
       </c>
-      <c r="H62" s="262" t="s">
+      <c r="H62" s="179" t="s">
         <v>197</v>
       </c>
-      <c r="I62" s="263"/>
-      <c r="J62" s="263"/>
-      <c r="K62" s="263"/>
-      <c r="L62" s="263"/>
-      <c r="M62" s="263"/>
-      <c r="N62" s="263"/>
-      <c r="O62" s="263"/>
-      <c r="P62" s="263"/>
+      <c r="I62" s="180"/>
+      <c r="J62" s="180"/>
+      <c r="K62" s="180"/>
+      <c r="L62" s="180"/>
+      <c r="M62" s="180"/>
+      <c r="N62" s="180"/>
+      <c r="O62" s="180"/>
+      <c r="P62" s="180"/>
       <c r="Q62" s="85"/>
       <c r="R62" s="116"/>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A63" s="208"/>
-      <c r="B63" s="224"/>
-      <c r="C63" s="183"/>
-      <c r="D63" s="187"/>
-      <c r="E63" s="182"/>
+      <c r="A63" s="227"/>
+      <c r="B63" s="270"/>
+      <c r="C63" s="174"/>
+      <c r="D63" s="176"/>
+      <c r="E63" s="178"/>
       <c r="F63" s="10" t="s">
         <v>315</v>
       </c>
       <c r="G63" s="135" t="s">
         <v>160</v>
       </c>
-      <c r="H63" s="165" t="s">
+      <c r="H63" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I63" s="166"/>
-      <c r="J63" s="166"/>
-      <c r="K63" s="166"/>
-      <c r="L63" s="166"/>
-      <c r="M63" s="166"/>
-      <c r="N63" s="166"/>
-      <c r="O63" s="166"/>
-      <c r="P63" s="166"/>
+      <c r="I63" s="182"/>
+      <c r="J63" s="182"/>
+      <c r="K63" s="182"/>
+      <c r="L63" s="182"/>
+      <c r="M63" s="182"/>
+      <c r="N63" s="182"/>
+      <c r="O63" s="182"/>
+      <c r="P63" s="182"/>
       <c r="Q63" s="6"/>
       <c r="R63" s="90"/>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A64" s="208"/>
-      <c r="B64" s="224"/>
-      <c r="C64" s="167" t="s">
+      <c r="A64" s="227"/>
+      <c r="B64" s="270"/>
+      <c r="C64" s="183" t="s">
         <v>91</v>
       </c>
-      <c r="D64" s="188">
+      <c r="D64" s="184">
         <v>100</v>
       </c>
-      <c r="E64" s="169">
+      <c r="E64" s="185">
         <v>570009449</v>
       </c>
       <c r="F64" s="10" t="s">
@@ -5223,138 +5236,138 @@
       <c r="G64" s="135" t="s">
         <v>161</v>
       </c>
-      <c r="H64" s="165" t="s">
+      <c r="H64" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I64" s="166"/>
-      <c r="J64" s="166"/>
-      <c r="K64" s="166"/>
-      <c r="L64" s="166"/>
-      <c r="M64" s="166"/>
-      <c r="N64" s="166"/>
-      <c r="O64" s="166"/>
-      <c r="P64" s="166"/>
+      <c r="I64" s="182"/>
+      <c r="J64" s="182"/>
+      <c r="K64" s="182"/>
+      <c r="L64" s="182"/>
+      <c r="M64" s="182"/>
+      <c r="N64" s="182"/>
+      <c r="O64" s="182"/>
+      <c r="P64" s="182"/>
       <c r="Q64" s="6"/>
       <c r="R64" s="90"/>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A65" s="208"/>
-      <c r="B65" s="224"/>
-      <c r="C65" s="168"/>
-      <c r="D65" s="186"/>
-      <c r="E65" s="170"/>
+      <c r="A65" s="227"/>
+      <c r="B65" s="270"/>
+      <c r="C65" s="173"/>
+      <c r="D65" s="175"/>
+      <c r="E65" s="177"/>
       <c r="F65" s="10" t="s">
         <v>317</v>
       </c>
       <c r="G65" s="135" t="s">
         <v>162</v>
       </c>
-      <c r="H65" s="165" t="s">
+      <c r="H65" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I65" s="166"/>
-      <c r="J65" s="166"/>
-      <c r="K65" s="166"/>
-      <c r="L65" s="166"/>
-      <c r="M65" s="166"/>
-      <c r="N65" s="166"/>
-      <c r="O65" s="166"/>
-      <c r="P65" s="166"/>
+      <c r="I65" s="182"/>
+      <c r="J65" s="182"/>
+      <c r="K65" s="182"/>
+      <c r="L65" s="182"/>
+      <c r="M65" s="182"/>
+      <c r="N65" s="182"/>
+      <c r="O65" s="182"/>
+      <c r="P65" s="182"/>
       <c r="Q65" s="6"/>
       <c r="R65" s="90"/>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A66" s="208"/>
-      <c r="B66" s="224"/>
-      <c r="C66" s="168"/>
-      <c r="D66" s="186"/>
-      <c r="E66" s="170"/>
+      <c r="A66" s="227"/>
+      <c r="B66" s="270"/>
+      <c r="C66" s="173"/>
+      <c r="D66" s="175"/>
+      <c r="E66" s="177"/>
       <c r="F66" s="10" t="s">
         <v>318</v>
       </c>
       <c r="G66" s="135" t="s">
         <v>163</v>
       </c>
-      <c r="H66" s="165" t="s">
+      <c r="H66" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I66" s="166"/>
-      <c r="J66" s="166"/>
-      <c r="K66" s="166"/>
-      <c r="L66" s="166"/>
-      <c r="M66" s="166"/>
-      <c r="N66" s="166"/>
-      <c r="O66" s="166"/>
-      <c r="P66" s="166"/>
+      <c r="I66" s="182"/>
+      <c r="J66" s="182"/>
+      <c r="K66" s="182"/>
+      <c r="L66" s="182"/>
+      <c r="M66" s="182"/>
+      <c r="N66" s="182"/>
+      <c r="O66" s="182"/>
+      <c r="P66" s="182"/>
       <c r="Q66" s="6"/>
       <c r="R66" s="90"/>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A67" s="208"/>
-      <c r="B67" s="224"/>
-      <c r="C67" s="168"/>
-      <c r="D67" s="186"/>
-      <c r="E67" s="170"/>
+      <c r="A67" s="227"/>
+      <c r="B67" s="270"/>
+      <c r="C67" s="173"/>
+      <c r="D67" s="175"/>
+      <c r="E67" s="177"/>
       <c r="F67" s="10" t="s">
         <v>319</v>
       </c>
       <c r="G67" s="135" t="s">
         <v>164</v>
       </c>
-      <c r="H67" s="165" t="s">
+      <c r="H67" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I67" s="166"/>
-      <c r="J67" s="166"/>
-      <c r="K67" s="166"/>
-      <c r="L67" s="166"/>
-      <c r="M67" s="166"/>
-      <c r="N67" s="166"/>
-      <c r="O67" s="166"/>
-      <c r="P67" s="166"/>
+      <c r="I67" s="182"/>
+      <c r="J67" s="182"/>
+      <c r="K67" s="182"/>
+      <c r="L67" s="182"/>
+      <c r="M67" s="182"/>
+      <c r="N67" s="182"/>
+      <c r="O67" s="182"/>
+      <c r="P67" s="182"/>
       <c r="Q67" s="6"/>
       <c r="R67" s="90"/>
     </row>
     <row r="68" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="208"/>
-      <c r="B68" s="224"/>
-      <c r="C68" s="168"/>
-      <c r="D68" s="186"/>
-      <c r="E68" s="170"/>
+      <c r="A68" s="227"/>
+      <c r="B68" s="270"/>
+      <c r="C68" s="173"/>
+      <c r="D68" s="175"/>
+      <c r="E68" s="177"/>
       <c r="F68" s="76" t="s">
         <v>320</v>
       </c>
       <c r="G68" s="136" t="s">
         <v>165</v>
       </c>
-      <c r="H68" s="194" t="s">
+      <c r="H68" s="186" t="s">
         <v>197</v>
       </c>
-      <c r="I68" s="195"/>
-      <c r="J68" s="195"/>
-      <c r="K68" s="195"/>
-      <c r="L68" s="195"/>
-      <c r="M68" s="195"/>
-      <c r="N68" s="195"/>
-      <c r="O68" s="195"/>
-      <c r="P68" s="195"/>
+      <c r="I68" s="187"/>
+      <c r="J68" s="187"/>
+      <c r="K68" s="187"/>
+      <c r="L68" s="187"/>
+      <c r="M68" s="187"/>
+      <c r="N68" s="187"/>
+      <c r="O68" s="187"/>
+      <c r="P68" s="187"/>
       <c r="Q68" s="96"/>
       <c r="R68" s="95"/>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A69" s="211" t="s">
+      <c r="A69" s="260" t="s">
         <v>207</v>
       </c>
-      <c r="B69" s="199" t="s">
+      <c r="B69" s="214" t="s">
         <v>197</v>
       </c>
-      <c r="C69" s="202" t="s">
+      <c r="C69" s="225" t="s">
         <v>29</v>
       </c>
-      <c r="D69" s="264">
+      <c r="D69" s="198">
         <v>50</v>
       </c>
-      <c r="E69" s="214">
+      <c r="E69" s="238">
         <v>511944670</v>
       </c>
       <c r="F69" s="104" t="s">
@@ -5363,18 +5376,18 @@
       <c r="G69" s="134">
         <v>131</v>
       </c>
-      <c r="H69" s="176" t="s">
+      <c r="H69" s="239" t="s">
         <v>347</v>
       </c>
-      <c r="I69" s="177"/>
-      <c r="J69" s="177"/>
-      <c r="K69" s="177"/>
-      <c r="L69" s="177"/>
-      <c r="M69" s="177"/>
-      <c r="N69" s="177"/>
-      <c r="O69" s="177"/>
-      <c r="P69" s="177"/>
-      <c r="Q69" s="215" t="s">
+      <c r="I69" s="240"/>
+      <c r="J69" s="240"/>
+      <c r="K69" s="240"/>
+      <c r="L69" s="240"/>
+      <c r="M69" s="240"/>
+      <c r="N69" s="240"/>
+      <c r="O69" s="240"/>
+      <c r="P69" s="240"/>
+      <c r="Q69" s="263" t="s">
         <v>251</v>
       </c>
       <c r="R69" s="105" t="s">
@@ -5382,47 +5395,47 @@
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A70" s="212"/>
-      <c r="B70" s="200"/>
-      <c r="C70" s="168"/>
-      <c r="D70" s="186"/>
-      <c r="E70" s="170"/>
+      <c r="A70" s="261"/>
+      <c r="B70" s="215"/>
+      <c r="C70" s="173"/>
+      <c r="D70" s="175"/>
+      <c r="E70" s="177"/>
       <c r="F70" s="10" t="s">
         <v>238</v>
       </c>
       <c r="G70" s="135">
         <v>132</v>
       </c>
-      <c r="H70" s="180"/>
-      <c r="I70" s="181"/>
-      <c r="J70" s="181"/>
-      <c r="K70" s="181"/>
-      <c r="L70" s="181"/>
-      <c r="M70" s="181"/>
-      <c r="N70" s="181"/>
-      <c r="O70" s="181"/>
-      <c r="P70" s="181"/>
-      <c r="Q70" s="216"/>
+      <c r="H70" s="242"/>
+      <c r="I70" s="243"/>
+      <c r="J70" s="243"/>
+      <c r="K70" s="243"/>
+      <c r="L70" s="243"/>
+      <c r="M70" s="243"/>
+      <c r="N70" s="243"/>
+      <c r="O70" s="243"/>
+      <c r="P70" s="243"/>
+      <c r="Q70" s="264"/>
       <c r="R70" s="90"/>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A71" s="212"/>
-      <c r="B71" s="226" t="s">
+      <c r="A71" s="261"/>
+      <c r="B71" s="166" t="s">
         <v>197</v>
       </c>
-      <c r="C71" s="273" t="s">
+      <c r="C71" s="193" t="s">
         <v>30</v>
       </c>
-      <c r="D71" s="188">
+      <c r="D71" s="184">
         <v>49</v>
       </c>
       <c r="E71" s="156">
         <v>513173393</v>
       </c>
-      <c r="F71" s="276" t="s">
+      <c r="F71" s="168" t="s">
         <v>245</v>
       </c>
-      <c r="G71" s="278">
+      <c r="G71" s="170">
         <v>3</v>
       </c>
       <c r="H71" s="43">
@@ -5438,47 +5451,47 @@
       <c r="N71" s="43"/>
       <c r="O71" s="43"/>
       <c r="P71" s="43"/>
-      <c r="Q71" s="216"/>
+      <c r="Q71" s="264"/>
       <c r="R71" s="90" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A72" s="212"/>
-      <c r="B72" s="257"/>
-      <c r="C72" s="185"/>
-      <c r="D72" s="187"/>
+      <c r="A72" s="261"/>
+      <c r="B72" s="167"/>
+      <c r="C72" s="194"/>
+      <c r="D72" s="176"/>
       <c r="E72" s="156">
         <v>540319472</v>
       </c>
-      <c r="F72" s="277"/>
-      <c r="G72" s="279"/>
-      <c r="H72" s="165" t="s">
+      <c r="F72" s="169"/>
+      <c r="G72" s="171"/>
+      <c r="H72" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I72" s="166"/>
-      <c r="J72" s="166"/>
-      <c r="K72" s="166"/>
-      <c r="L72" s="166"/>
-      <c r="M72" s="166"/>
-      <c r="N72" s="166"/>
-      <c r="O72" s="166"/>
-      <c r="P72" s="166"/>
-      <c r="Q72" s="216"/>
+      <c r="I72" s="182"/>
+      <c r="J72" s="182"/>
+      <c r="K72" s="182"/>
+      <c r="L72" s="182"/>
+      <c r="M72" s="182"/>
+      <c r="N72" s="182"/>
+      <c r="O72" s="182"/>
+      <c r="P72" s="182"/>
+      <c r="Q72" s="264"/>
       <c r="R72" s="90"/>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A73" s="212"/>
-      <c r="B73" s="226" t="s">
+      <c r="A73" s="261"/>
+      <c r="B73" s="166" t="s">
         <v>197</v>
       </c>
-      <c r="C73" s="192" t="s">
+      <c r="C73" s="218" t="s">
         <v>31</v>
       </c>
-      <c r="D73" s="191">
+      <c r="D73" s="200">
         <v>62</v>
       </c>
-      <c r="E73" s="193">
+      <c r="E73" s="221">
         <v>511446551</v>
       </c>
       <c r="F73" s="10" t="s">
@@ -5487,294 +5500,294 @@
       <c r="G73" s="8">
         <v>43</v>
       </c>
-      <c r="H73" s="165" t="s">
+      <c r="H73" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I73" s="166"/>
-      <c r="J73" s="166"/>
-      <c r="K73" s="166"/>
-      <c r="L73" s="166"/>
-      <c r="M73" s="166"/>
-      <c r="N73" s="166"/>
-      <c r="O73" s="166"/>
-      <c r="P73" s="166"/>
-      <c r="Q73" s="216"/>
+      <c r="I73" s="182"/>
+      <c r="J73" s="182"/>
+      <c r="K73" s="182"/>
+      <c r="L73" s="182"/>
+      <c r="M73" s="182"/>
+      <c r="N73" s="182"/>
+      <c r="O73" s="182"/>
+      <c r="P73" s="182"/>
+      <c r="Q73" s="264"/>
       <c r="R73" s="90"/>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A74" s="212"/>
-      <c r="B74" s="260"/>
-      <c r="C74" s="192"/>
-      <c r="D74" s="191"/>
-      <c r="E74" s="193"/>
+      <c r="A74" s="261"/>
+      <c r="B74" s="258"/>
+      <c r="C74" s="218"/>
+      <c r="D74" s="200"/>
+      <c r="E74" s="221"/>
       <c r="F74" s="10" t="s">
         <v>31</v>
       </c>
       <c r="G74" s="8">
         <v>47</v>
       </c>
-      <c r="H74" s="165" t="s">
+      <c r="H74" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I74" s="166"/>
-      <c r="J74" s="166"/>
-      <c r="K74" s="166"/>
-      <c r="L74" s="166"/>
-      <c r="M74" s="166"/>
-      <c r="N74" s="166"/>
-      <c r="O74" s="166"/>
-      <c r="P74" s="166"/>
-      <c r="Q74" s="216"/>
+      <c r="I74" s="182"/>
+      <c r="J74" s="182"/>
+      <c r="K74" s="182"/>
+      <c r="L74" s="182"/>
+      <c r="M74" s="182"/>
+      <c r="N74" s="182"/>
+      <c r="O74" s="182"/>
+      <c r="P74" s="182"/>
+      <c r="Q74" s="264"/>
       <c r="R74" s="90"/>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A75" s="212"/>
-      <c r="B75" s="260"/>
-      <c r="C75" s="192"/>
-      <c r="D75" s="191"/>
-      <c r="E75" s="193"/>
+      <c r="A75" s="261"/>
+      <c r="B75" s="258"/>
+      <c r="C75" s="218"/>
+      <c r="D75" s="200"/>
+      <c r="E75" s="221"/>
       <c r="F75" s="10" t="s">
         <v>31</v>
       </c>
       <c r="G75" s="8">
         <v>51</v>
       </c>
-      <c r="H75" s="165" t="s">
+      <c r="H75" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I75" s="166"/>
-      <c r="J75" s="166"/>
-      <c r="K75" s="166"/>
-      <c r="L75" s="166"/>
-      <c r="M75" s="166"/>
-      <c r="N75" s="166"/>
-      <c r="O75" s="166"/>
-      <c r="P75" s="166"/>
-      <c r="Q75" s="216"/>
+      <c r="I75" s="182"/>
+      <c r="J75" s="182"/>
+      <c r="K75" s="182"/>
+      <c r="L75" s="182"/>
+      <c r="M75" s="182"/>
+      <c r="N75" s="182"/>
+      <c r="O75" s="182"/>
+      <c r="P75" s="182"/>
+      <c r="Q75" s="264"/>
       <c r="R75" s="90"/>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A76" s="212"/>
-      <c r="B76" s="260"/>
-      <c r="C76" s="192"/>
-      <c r="D76" s="191"/>
-      <c r="E76" s="193"/>
+      <c r="A76" s="261"/>
+      <c r="B76" s="258"/>
+      <c r="C76" s="218"/>
+      <c r="D76" s="200"/>
+      <c r="E76" s="221"/>
       <c r="F76" s="10" t="s">
         <v>31</v>
       </c>
       <c r="G76" s="8">
         <v>54</v>
       </c>
-      <c r="H76" s="165" t="s">
+      <c r="H76" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I76" s="166"/>
-      <c r="J76" s="166"/>
-      <c r="K76" s="166"/>
-      <c r="L76" s="166"/>
-      <c r="M76" s="166"/>
-      <c r="N76" s="166"/>
-      <c r="O76" s="166"/>
-      <c r="P76" s="166"/>
-      <c r="Q76" s="216"/>
+      <c r="I76" s="182"/>
+      <c r="J76" s="182"/>
+      <c r="K76" s="182"/>
+      <c r="L76" s="182"/>
+      <c r="M76" s="182"/>
+      <c r="N76" s="182"/>
+      <c r="O76" s="182"/>
+      <c r="P76" s="182"/>
+      <c r="Q76" s="264"/>
       <c r="R76" s="90"/>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A77" s="212"/>
-      <c r="B77" s="260"/>
-      <c r="C77" s="192"/>
-      <c r="D77" s="191"/>
-      <c r="E77" s="193"/>
+      <c r="A77" s="261"/>
+      <c r="B77" s="258"/>
+      <c r="C77" s="218"/>
+      <c r="D77" s="200"/>
+      <c r="E77" s="221"/>
       <c r="F77" s="10" t="s">
         <v>31</v>
       </c>
       <c r="G77" s="8">
         <v>67</v>
       </c>
-      <c r="H77" s="165" t="s">
+      <c r="H77" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I77" s="166"/>
-      <c r="J77" s="166"/>
-      <c r="K77" s="166"/>
-      <c r="L77" s="166"/>
-      <c r="M77" s="166"/>
-      <c r="N77" s="166"/>
-      <c r="O77" s="166"/>
-      <c r="P77" s="166"/>
-      <c r="Q77" s="216"/>
+      <c r="I77" s="182"/>
+      <c r="J77" s="182"/>
+      <c r="K77" s="182"/>
+      <c r="L77" s="182"/>
+      <c r="M77" s="182"/>
+      <c r="N77" s="182"/>
+      <c r="O77" s="182"/>
+      <c r="P77" s="182"/>
+      <c r="Q77" s="264"/>
       <c r="R77" s="90"/>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A78" s="212"/>
-      <c r="B78" s="260"/>
-      <c r="C78" s="192"/>
-      <c r="D78" s="191"/>
-      <c r="E78" s="193"/>
+      <c r="A78" s="261"/>
+      <c r="B78" s="258"/>
+      <c r="C78" s="218"/>
+      <c r="D78" s="200"/>
+      <c r="E78" s="221"/>
       <c r="F78" s="10" t="s">
         <v>31</v>
       </c>
       <c r="G78" s="8">
         <v>77</v>
       </c>
-      <c r="H78" s="165" t="s">
+      <c r="H78" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I78" s="166"/>
-      <c r="J78" s="166"/>
-      <c r="K78" s="166"/>
-      <c r="L78" s="166"/>
-      <c r="M78" s="166"/>
-      <c r="N78" s="166"/>
-      <c r="O78" s="166"/>
-      <c r="P78" s="166"/>
-      <c r="Q78" s="216"/>
+      <c r="I78" s="182"/>
+      <c r="J78" s="182"/>
+      <c r="K78" s="182"/>
+      <c r="L78" s="182"/>
+      <c r="M78" s="182"/>
+      <c r="N78" s="182"/>
+      <c r="O78" s="182"/>
+      <c r="P78" s="182"/>
+      <c r="Q78" s="264"/>
       <c r="R78" s="90"/>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A79" s="212"/>
-      <c r="B79" s="260"/>
-      <c r="C79" s="192"/>
-      <c r="D79" s="191"/>
-      <c r="E79" s="193"/>
+      <c r="A79" s="261"/>
+      <c r="B79" s="258"/>
+      <c r="C79" s="218"/>
+      <c r="D79" s="200"/>
+      <c r="E79" s="221"/>
       <c r="F79" s="10" t="s">
         <v>31</v>
       </c>
       <c r="G79" s="8">
         <v>81</v>
       </c>
-      <c r="H79" s="165" t="s">
+      <c r="H79" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I79" s="166"/>
-      <c r="J79" s="166"/>
-      <c r="K79" s="166"/>
-      <c r="L79" s="166"/>
-      <c r="M79" s="166"/>
-      <c r="N79" s="166"/>
-      <c r="O79" s="166"/>
-      <c r="P79" s="166"/>
-      <c r="Q79" s="216"/>
+      <c r="I79" s="182"/>
+      <c r="J79" s="182"/>
+      <c r="K79" s="182"/>
+      <c r="L79" s="182"/>
+      <c r="M79" s="182"/>
+      <c r="N79" s="182"/>
+      <c r="O79" s="182"/>
+      <c r="P79" s="182"/>
+      <c r="Q79" s="264"/>
       <c r="R79" s="90"/>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A80" s="212"/>
-      <c r="B80" s="260"/>
-      <c r="C80" s="192"/>
-      <c r="D80" s="191"/>
-      <c r="E80" s="193"/>
+      <c r="A80" s="261"/>
+      <c r="B80" s="258"/>
+      <c r="C80" s="218"/>
+      <c r="D80" s="200"/>
+      <c r="E80" s="221"/>
       <c r="F80" s="10" t="s">
         <v>246</v>
       </c>
       <c r="G80" s="8">
         <v>86</v>
       </c>
-      <c r="H80" s="165" t="s">
+      <c r="H80" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I80" s="166"/>
-      <c r="J80" s="166"/>
-      <c r="K80" s="166"/>
-      <c r="L80" s="166"/>
-      <c r="M80" s="166"/>
-      <c r="N80" s="166"/>
-      <c r="O80" s="166"/>
-      <c r="P80" s="166"/>
-      <c r="Q80" s="216"/>
+      <c r="I80" s="182"/>
+      <c r="J80" s="182"/>
+      <c r="K80" s="182"/>
+      <c r="L80" s="182"/>
+      <c r="M80" s="182"/>
+      <c r="N80" s="182"/>
+      <c r="O80" s="182"/>
+      <c r="P80" s="182"/>
+      <c r="Q80" s="264"/>
       <c r="R80" s="90"/>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A81" s="212"/>
-      <c r="B81" s="260"/>
-      <c r="C81" s="192"/>
-      <c r="D81" s="191"/>
-      <c r="E81" s="193"/>
+      <c r="A81" s="261"/>
+      <c r="B81" s="258"/>
+      <c r="C81" s="218"/>
+      <c r="D81" s="200"/>
+      <c r="E81" s="221"/>
       <c r="F81" s="10" t="s">
         <v>247</v>
       </c>
       <c r="G81" s="8">
         <v>87</v>
       </c>
-      <c r="H81" s="165" t="s">
+      <c r="H81" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I81" s="166"/>
-      <c r="J81" s="166"/>
-      <c r="K81" s="166"/>
-      <c r="L81" s="166"/>
-      <c r="M81" s="166"/>
-      <c r="N81" s="166"/>
-      <c r="O81" s="166"/>
-      <c r="P81" s="166"/>
-      <c r="Q81" s="216"/>
+      <c r="I81" s="182"/>
+      <c r="J81" s="182"/>
+      <c r="K81" s="182"/>
+      <c r="L81" s="182"/>
+      <c r="M81" s="182"/>
+      <c r="N81" s="182"/>
+      <c r="O81" s="182"/>
+      <c r="P81" s="182"/>
+      <c r="Q81" s="264"/>
       <c r="R81" s="90"/>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A82" s="212"/>
-      <c r="B82" s="260"/>
-      <c r="C82" s="192"/>
-      <c r="D82" s="191"/>
-      <c r="E82" s="193"/>
+      <c r="A82" s="261"/>
+      <c r="B82" s="258"/>
+      <c r="C82" s="218"/>
+      <c r="D82" s="200"/>
+      <c r="E82" s="221"/>
       <c r="F82" s="10" t="s">
         <v>248</v>
       </c>
       <c r="G82" s="8">
         <v>89</v>
       </c>
-      <c r="H82" s="165" t="s">
+      <c r="H82" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I82" s="166"/>
-      <c r="J82" s="166"/>
-      <c r="K82" s="166"/>
-      <c r="L82" s="166"/>
-      <c r="M82" s="166"/>
-      <c r="N82" s="166"/>
-      <c r="O82" s="166"/>
-      <c r="P82" s="166"/>
-      <c r="Q82" s="216"/>
+      <c r="I82" s="182"/>
+      <c r="J82" s="182"/>
+      <c r="K82" s="182"/>
+      <c r="L82" s="182"/>
+      <c r="M82" s="182"/>
+      <c r="N82" s="182"/>
+      <c r="O82" s="182"/>
+      <c r="P82" s="182"/>
+      <c r="Q82" s="264"/>
       <c r="R82" s="90"/>
     </row>
     <row r="83" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="213"/>
-      <c r="B83" s="261"/>
-      <c r="C83" s="205"/>
-      <c r="D83" s="266"/>
-      <c r="E83" s="225"/>
+      <c r="A83" s="262"/>
+      <c r="B83" s="259"/>
+      <c r="C83" s="219"/>
+      <c r="D83" s="201"/>
+      <c r="E83" s="222"/>
       <c r="F83" s="92" t="s">
         <v>249</v>
       </c>
       <c r="G83" s="106">
         <v>92</v>
       </c>
-      <c r="H83" s="222" t="s">
+      <c r="H83" s="208" t="s">
         <v>197</v>
       </c>
-      <c r="I83" s="223"/>
-      <c r="J83" s="223"/>
-      <c r="K83" s="223"/>
-      <c r="L83" s="223"/>
-      <c r="M83" s="223"/>
-      <c r="N83" s="223"/>
-      <c r="O83" s="223"/>
-      <c r="P83" s="223"/>
-      <c r="Q83" s="217"/>
+      <c r="I83" s="209"/>
+      <c r="J83" s="209"/>
+      <c r="K83" s="209"/>
+      <c r="L83" s="209"/>
+      <c r="M83" s="209"/>
+      <c r="N83" s="209"/>
+      <c r="O83" s="209"/>
+      <c r="P83" s="209"/>
+      <c r="Q83" s="265"/>
       <c r="R83" s="93"/>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A84" s="196" t="s">
+      <c r="A84" s="211" t="s">
         <v>32</v>
       </c>
-      <c r="B84" s="199" t="s">
+      <c r="B84" s="214" t="s">
         <v>197</v>
       </c>
-      <c r="C84" s="202" t="s">
+      <c r="C84" s="225" t="s">
         <v>33</v>
       </c>
-      <c r="D84" s="264">
+      <c r="D84" s="198">
         <v>1180</v>
       </c>
-      <c r="E84" s="214">
+      <c r="E84" s="238">
         <v>511146490</v>
       </c>
       <c r="F84" s="104" t="s">
@@ -5783,48 +5796,48 @@
       <c r="G84" s="134">
         <v>514</v>
       </c>
-      <c r="H84" s="238" t="s">
+      <c r="H84" s="206" t="s">
         <v>197</v>
       </c>
-      <c r="I84" s="239"/>
-      <c r="J84" s="239"/>
-      <c r="K84" s="239"/>
-      <c r="L84" s="239"/>
-      <c r="M84" s="239"/>
-      <c r="N84" s="239"/>
-      <c r="O84" s="239"/>
-      <c r="P84" s="239"/>
+      <c r="I84" s="207"/>
+      <c r="J84" s="207"/>
+      <c r="K84" s="207"/>
+      <c r="L84" s="207"/>
+      <c r="M84" s="207"/>
+      <c r="N84" s="207"/>
+      <c r="O84" s="207"/>
+      <c r="P84" s="207"/>
       <c r="Q84" s="88"/>
       <c r="R84" s="89"/>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A85" s="197"/>
-      <c r="B85" s="200"/>
-      <c r="C85" s="183"/>
-      <c r="D85" s="187"/>
-      <c r="E85" s="182"/>
+      <c r="A85" s="212"/>
+      <c r="B85" s="215"/>
+      <c r="C85" s="174"/>
+      <c r="D85" s="176"/>
+      <c r="E85" s="178"/>
       <c r="F85" s="10" t="s">
         <v>253</v>
       </c>
       <c r="G85" s="135">
         <v>535</v>
       </c>
-      <c r="H85" s="165" t="s">
+      <c r="H85" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I85" s="166"/>
-      <c r="J85" s="166"/>
-      <c r="K85" s="166"/>
-      <c r="L85" s="166"/>
-      <c r="M85" s="166"/>
-      <c r="N85" s="166"/>
-      <c r="O85" s="166"/>
-      <c r="P85" s="166"/>
+      <c r="I85" s="182"/>
+      <c r="J85" s="182"/>
+      <c r="K85" s="182"/>
+      <c r="L85" s="182"/>
+      <c r="M85" s="182"/>
+      <c r="N85" s="182"/>
+      <c r="O85" s="182"/>
+      <c r="P85" s="182"/>
       <c r="Q85" s="6"/>
       <c r="R85" s="90"/>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A86" s="197"/>
+      <c r="A86" s="212"/>
       <c r="B86" s="1" t="s">
         <v>197</v>
       </c>
@@ -5843,34 +5856,34 @@
       <c r="G86" s="135">
         <v>439</v>
       </c>
-      <c r="H86" s="165" t="s">
+      <c r="H86" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I86" s="166"/>
-      <c r="J86" s="166"/>
-      <c r="K86" s="166"/>
-      <c r="L86" s="166"/>
-      <c r="M86" s="166"/>
-      <c r="N86" s="166"/>
-      <c r="O86" s="166"/>
-      <c r="P86" s="166"/>
+      <c r="I86" s="182"/>
+      <c r="J86" s="182"/>
+      <c r="K86" s="182"/>
+      <c r="L86" s="182"/>
+      <c r="M86" s="182"/>
+      <c r="N86" s="182"/>
+      <c r="O86" s="182"/>
+      <c r="P86" s="182"/>
       <c r="Q86" s="7" t="s">
         <v>255</v>
       </c>
       <c r="R86" s="107"/>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A87" s="197"/>
-      <c r="B87" s="226" t="s">
+      <c r="A87" s="212"/>
+      <c r="B87" s="166" t="s">
         <v>197</v>
       </c>
-      <c r="C87" s="192" t="s">
+      <c r="C87" s="218" t="s">
         <v>35</v>
       </c>
-      <c r="D87" s="191">
+      <c r="D87" s="200">
         <v>1181</v>
       </c>
-      <c r="E87" s="193" t="s">
+      <c r="E87" s="221" t="s">
         <v>377</v>
       </c>
       <c r="F87" s="10" t="s">
@@ -5879,121 +5892,121 @@
       <c r="G87" s="135">
         <v>3931</v>
       </c>
-      <c r="H87" s="165" t="s">
+      <c r="H87" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I87" s="166"/>
-      <c r="J87" s="166"/>
-      <c r="K87" s="166"/>
-      <c r="L87" s="166"/>
-      <c r="M87" s="166"/>
-      <c r="N87" s="166"/>
-      <c r="O87" s="166"/>
-      <c r="P87" s="166"/>
+      <c r="I87" s="182"/>
+      <c r="J87" s="182"/>
+      <c r="K87" s="182"/>
+      <c r="L87" s="182"/>
+      <c r="M87" s="182"/>
+      <c r="N87" s="182"/>
+      <c r="O87" s="182"/>
+      <c r="P87" s="182"/>
       <c r="Q87" s="7"/>
       <c r="R87" s="107"/>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A88" s="197"/>
-      <c r="B88" s="260"/>
-      <c r="C88" s="192"/>
-      <c r="D88" s="191"/>
-      <c r="E88" s="193"/>
+      <c r="A88" s="212"/>
+      <c r="B88" s="258"/>
+      <c r="C88" s="218"/>
+      <c r="D88" s="200"/>
+      <c r="E88" s="221"/>
       <c r="F88" s="10" t="s">
         <v>257</v>
       </c>
       <c r="G88" s="135">
         <v>3936</v>
       </c>
-      <c r="H88" s="165" t="s">
+      <c r="H88" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I88" s="166"/>
-      <c r="J88" s="166"/>
-      <c r="K88" s="166"/>
-      <c r="L88" s="166"/>
-      <c r="M88" s="166"/>
-      <c r="N88" s="166"/>
-      <c r="O88" s="166"/>
-      <c r="P88" s="166"/>
+      <c r="I88" s="182"/>
+      <c r="J88" s="182"/>
+      <c r="K88" s="182"/>
+      <c r="L88" s="182"/>
+      <c r="M88" s="182"/>
+      <c r="N88" s="182"/>
+      <c r="O88" s="182"/>
+      <c r="P88" s="182"/>
       <c r="Q88" s="7"/>
       <c r="R88" s="107"/>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A89" s="197"/>
-      <c r="B89" s="260"/>
-      <c r="C89" s="192"/>
-      <c r="D89" s="191"/>
-      <c r="E89" s="193"/>
+      <c r="A89" s="212"/>
+      <c r="B89" s="258"/>
+      <c r="C89" s="218"/>
+      <c r="D89" s="200"/>
+      <c r="E89" s="221"/>
       <c r="F89" s="10" t="s">
         <v>258</v>
       </c>
       <c r="G89" s="135">
         <v>3937</v>
       </c>
-      <c r="H89" s="165" t="s">
+      <c r="H89" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I89" s="166"/>
-      <c r="J89" s="166"/>
-      <c r="K89" s="166"/>
-      <c r="L89" s="166"/>
-      <c r="M89" s="166"/>
-      <c r="N89" s="166"/>
-      <c r="O89" s="166"/>
-      <c r="P89" s="166"/>
+      <c r="I89" s="182"/>
+      <c r="J89" s="182"/>
+      <c r="K89" s="182"/>
+      <c r="L89" s="182"/>
+      <c r="M89" s="182"/>
+      <c r="N89" s="182"/>
+      <c r="O89" s="182"/>
+      <c r="P89" s="182"/>
       <c r="Q89" s="7"/>
       <c r="R89" s="107"/>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A90" s="197"/>
-      <c r="B90" s="260"/>
-      <c r="C90" s="192"/>
-      <c r="D90" s="191"/>
-      <c r="E90" s="193"/>
+      <c r="A90" s="212"/>
+      <c r="B90" s="258"/>
+      <c r="C90" s="218"/>
+      <c r="D90" s="200"/>
+      <c r="E90" s="221"/>
       <c r="F90" s="10" t="s">
         <v>259</v>
       </c>
       <c r="G90" s="135">
         <v>3938</v>
       </c>
-      <c r="H90" s="165" t="s">
+      <c r="H90" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I90" s="166"/>
-      <c r="J90" s="166"/>
-      <c r="K90" s="166"/>
-      <c r="L90" s="166"/>
-      <c r="M90" s="166"/>
-      <c r="N90" s="166"/>
-      <c r="O90" s="166"/>
-      <c r="P90" s="166"/>
+      <c r="I90" s="182"/>
+      <c r="J90" s="182"/>
+      <c r="K90" s="182"/>
+      <c r="L90" s="182"/>
+      <c r="M90" s="182"/>
+      <c r="N90" s="182"/>
+      <c r="O90" s="182"/>
+      <c r="P90" s="182"/>
       <c r="Q90" s="7"/>
       <c r="R90" s="107"/>
     </row>
     <row r="91" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="198"/>
-      <c r="B91" s="261"/>
-      <c r="C91" s="205"/>
-      <c r="D91" s="266"/>
-      <c r="E91" s="225"/>
+      <c r="A91" s="213"/>
+      <c r="B91" s="259"/>
+      <c r="C91" s="219"/>
+      <c r="D91" s="201"/>
+      <c r="E91" s="222"/>
       <c r="F91" s="92" t="s">
         <v>259</v>
       </c>
       <c r="G91" s="137">
         <v>4560</v>
       </c>
-      <c r="H91" s="222" t="s">
+      <c r="H91" s="208" t="s">
         <v>197</v>
       </c>
-      <c r="I91" s="223"/>
-      <c r="J91" s="223"/>
-      <c r="K91" s="223"/>
-      <c r="L91" s="223"/>
-      <c r="M91" s="223"/>
-      <c r="N91" s="223"/>
-      <c r="O91" s="223"/>
-      <c r="P91" s="223"/>
+      <c r="I91" s="209"/>
+      <c r="J91" s="209"/>
+      <c r="K91" s="209"/>
+      <c r="L91" s="209"/>
+      <c r="M91" s="209"/>
+      <c r="N91" s="209"/>
+      <c r="O91" s="209"/>
+      <c r="P91" s="209"/>
       <c r="Q91" s="102"/>
       <c r="R91" s="93"/>
     </row>
@@ -6019,34 +6032,34 @@
       <c r="G92" s="138">
         <v>100</v>
       </c>
-      <c r="H92" s="246" t="s">
+      <c r="H92" s="204" t="s">
         <v>197</v>
       </c>
-      <c r="I92" s="247"/>
-      <c r="J92" s="247"/>
-      <c r="K92" s="247"/>
-      <c r="L92" s="247"/>
-      <c r="M92" s="247"/>
-      <c r="N92" s="247"/>
-      <c r="O92" s="247"/>
-      <c r="P92" s="247"/>
+      <c r="I92" s="205"/>
+      <c r="J92" s="205"/>
+      <c r="K92" s="205"/>
+      <c r="L92" s="205"/>
+      <c r="M92" s="205"/>
+      <c r="N92" s="205"/>
+      <c r="O92" s="205"/>
+      <c r="P92" s="205"/>
       <c r="Q92" s="113"/>
       <c r="R92" s="114"/>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A93" s="196" t="s">
+      <c r="A93" s="211" t="s">
         <v>37</v>
       </c>
-      <c r="B93" s="199" t="s">
+      <c r="B93" s="214" t="s">
         <v>197</v>
       </c>
-      <c r="C93" s="202" t="s">
+      <c r="C93" s="225" t="s">
         <v>38</v>
       </c>
-      <c r="D93" s="264">
+      <c r="D93" s="198">
         <v>151</v>
       </c>
-      <c r="E93" s="214">
+      <c r="E93" s="238">
         <v>511776783</v>
       </c>
       <c r="F93" s="104" t="s">
@@ -6055,51 +6068,51 @@
       <c r="G93" s="134">
         <v>1</v>
       </c>
-      <c r="H93" s="227" t="s">
+      <c r="H93" s="249" t="s">
         <v>347</v>
       </c>
-      <c r="I93" s="228"/>
-      <c r="J93" s="228"/>
-      <c r="K93" s="228"/>
-      <c r="L93" s="228"/>
-      <c r="M93" s="228"/>
-      <c r="N93" s="228"/>
-      <c r="O93" s="228"/>
-      <c r="P93" s="228"/>
+      <c r="I93" s="250"/>
+      <c r="J93" s="250"/>
+      <c r="K93" s="250"/>
+      <c r="L93" s="250"/>
+      <c r="M93" s="250"/>
+      <c r="N93" s="250"/>
+      <c r="O93" s="250"/>
+      <c r="P93" s="250"/>
       <c r="Q93" s="88"/>
       <c r="R93" s="89"/>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A94" s="197"/>
-      <c r="B94" s="200"/>
-      <c r="C94" s="183"/>
-      <c r="D94" s="187"/>
-      <c r="E94" s="182"/>
+      <c r="A94" s="212"/>
+      <c r="B94" s="215"/>
+      <c r="C94" s="174"/>
+      <c r="D94" s="176"/>
+      <c r="E94" s="178"/>
       <c r="F94" s="10" t="s">
         <v>261</v>
       </c>
       <c r="G94" s="135">
         <v>2</v>
       </c>
-      <c r="H94" s="229"/>
-      <c r="I94" s="230"/>
-      <c r="J94" s="230"/>
-      <c r="K94" s="230"/>
-      <c r="L94" s="230"/>
-      <c r="M94" s="230"/>
-      <c r="N94" s="230"/>
-      <c r="O94" s="230"/>
-      <c r="P94" s="230"/>
+      <c r="H94" s="251"/>
+      <c r="I94" s="252"/>
+      <c r="J94" s="252"/>
+      <c r="K94" s="252"/>
+      <c r="L94" s="252"/>
+      <c r="M94" s="252"/>
+      <c r="N94" s="252"/>
+      <c r="O94" s="252"/>
+      <c r="P94" s="252"/>
       <c r="Q94" s="6"/>
       <c r="R94" s="90"/>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A95" s="197"/>
-      <c r="B95" s="200"/>
-      <c r="C95" s="167" t="s">
+      <c r="A95" s="212"/>
+      <c r="B95" s="215"/>
+      <c r="C95" s="183" t="s">
         <v>39</v>
       </c>
-      <c r="D95" s="188">
+      <c r="D95" s="184">
         <v>150</v>
       </c>
       <c r="E95" s="156">
@@ -6111,25 +6124,25 @@
       <c r="G95" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="H95" s="165" t="s">
+      <c r="H95" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I95" s="166"/>
-      <c r="J95" s="166"/>
-      <c r="K95" s="166"/>
-      <c r="L95" s="166"/>
-      <c r="M95" s="166"/>
-      <c r="N95" s="166"/>
-      <c r="O95" s="166"/>
-      <c r="P95" s="166"/>
+      <c r="I95" s="182"/>
+      <c r="J95" s="182"/>
+      <c r="K95" s="182"/>
+      <c r="L95" s="182"/>
+      <c r="M95" s="182"/>
+      <c r="N95" s="182"/>
+      <c r="O95" s="182"/>
+      <c r="P95" s="182"/>
       <c r="Q95" s="6"/>
       <c r="R95" s="90"/>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A96" s="197"/>
-      <c r="B96" s="200"/>
-      <c r="C96" s="168"/>
-      <c r="D96" s="186"/>
+      <c r="A96" s="212"/>
+      <c r="B96" s="215"/>
+      <c r="C96" s="173"/>
+      <c r="D96" s="175"/>
       <c r="E96" s="156">
         <v>512267592</v>
       </c>
@@ -6139,25 +6152,25 @@
       <c r="G96" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="H96" s="165" t="s">
+      <c r="H96" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I96" s="166"/>
-      <c r="J96" s="166"/>
-      <c r="K96" s="166"/>
-      <c r="L96" s="166"/>
-      <c r="M96" s="166"/>
-      <c r="N96" s="166"/>
-      <c r="O96" s="166"/>
-      <c r="P96" s="166"/>
+      <c r="I96" s="182"/>
+      <c r="J96" s="182"/>
+      <c r="K96" s="182"/>
+      <c r="L96" s="182"/>
+      <c r="M96" s="182"/>
+      <c r="N96" s="182"/>
+      <c r="O96" s="182"/>
+      <c r="P96" s="182"/>
       <c r="Q96" s="6"/>
       <c r="R96" s="90"/>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A97" s="197"/>
-      <c r="B97" s="200"/>
-      <c r="C97" s="168"/>
-      <c r="D97" s="186"/>
+      <c r="A97" s="212"/>
+      <c r="B97" s="215"/>
+      <c r="C97" s="173"/>
+      <c r="D97" s="175"/>
       <c r="E97" s="156">
         <v>511423048</v>
       </c>
@@ -6167,25 +6180,25 @@
       <c r="G97" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="H97" s="165" t="s">
+      <c r="H97" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I97" s="166"/>
-      <c r="J97" s="166"/>
-      <c r="K97" s="166"/>
-      <c r="L97" s="166"/>
-      <c r="M97" s="166"/>
-      <c r="N97" s="166"/>
-      <c r="O97" s="166"/>
-      <c r="P97" s="166"/>
+      <c r="I97" s="182"/>
+      <c r="J97" s="182"/>
+      <c r="K97" s="182"/>
+      <c r="L97" s="182"/>
+      <c r="M97" s="182"/>
+      <c r="N97" s="182"/>
+      <c r="O97" s="182"/>
+      <c r="P97" s="182"/>
       <c r="Q97" s="6"/>
       <c r="R97" s="90"/>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A98" s="197"/>
-      <c r="B98" s="200"/>
-      <c r="C98" s="168"/>
-      <c r="D98" s="186"/>
+      <c r="A98" s="212"/>
+      <c r="B98" s="215"/>
+      <c r="C98" s="173"/>
+      <c r="D98" s="175"/>
       <c r="E98" s="156">
         <v>511033060</v>
       </c>
@@ -6195,25 +6208,25 @@
       <c r="G98" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="H98" s="165" t="s">
+      <c r="H98" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I98" s="166"/>
-      <c r="J98" s="166"/>
-      <c r="K98" s="166"/>
-      <c r="L98" s="166"/>
-      <c r="M98" s="166"/>
-      <c r="N98" s="166"/>
-      <c r="O98" s="166"/>
-      <c r="P98" s="166"/>
+      <c r="I98" s="182"/>
+      <c r="J98" s="182"/>
+      <c r="K98" s="182"/>
+      <c r="L98" s="182"/>
+      <c r="M98" s="182"/>
+      <c r="N98" s="182"/>
+      <c r="O98" s="182"/>
+      <c r="P98" s="182"/>
       <c r="Q98" s="6"/>
       <c r="R98" s="90"/>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A99" s="197"/>
-      <c r="B99" s="200"/>
-      <c r="C99" s="168"/>
-      <c r="D99" s="186"/>
+      <c r="A99" s="212"/>
+      <c r="B99" s="215"/>
+      <c r="C99" s="173"/>
+      <c r="D99" s="175"/>
       <c r="E99" s="156">
         <v>512310509</v>
       </c>
@@ -6223,25 +6236,25 @@
       <c r="G99" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="H99" s="165" t="s">
+      <c r="H99" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I99" s="166"/>
-      <c r="J99" s="166"/>
-      <c r="K99" s="166"/>
-      <c r="L99" s="166"/>
-      <c r="M99" s="166"/>
-      <c r="N99" s="166"/>
-      <c r="O99" s="166"/>
-      <c r="P99" s="166"/>
+      <c r="I99" s="182"/>
+      <c r="J99" s="182"/>
+      <c r="K99" s="182"/>
+      <c r="L99" s="182"/>
+      <c r="M99" s="182"/>
+      <c r="N99" s="182"/>
+      <c r="O99" s="182"/>
+      <c r="P99" s="182"/>
       <c r="Q99" s="6"/>
       <c r="R99" s="90"/>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A100" s="208"/>
-      <c r="B100" s="226"/>
-      <c r="C100" s="168"/>
-      <c r="D100" s="186"/>
+      <c r="A100" s="227"/>
+      <c r="B100" s="166"/>
+      <c r="C100" s="173"/>
+      <c r="D100" s="175"/>
       <c r="E100" s="156">
         <v>512624487</v>
       </c>
@@ -6251,25 +6264,25 @@
       <c r="G100" s="97" t="s">
         <v>152</v>
       </c>
-      <c r="H100" s="165" t="s">
+      <c r="H100" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I100" s="166"/>
-      <c r="J100" s="166"/>
-      <c r="K100" s="166"/>
-      <c r="L100" s="166"/>
-      <c r="M100" s="166"/>
-      <c r="N100" s="166"/>
-      <c r="O100" s="166"/>
-      <c r="P100" s="166"/>
+      <c r="I100" s="182"/>
+      <c r="J100" s="182"/>
+      <c r="K100" s="182"/>
+      <c r="L100" s="182"/>
+      <c r="M100" s="182"/>
+      <c r="N100" s="182"/>
+      <c r="O100" s="182"/>
+      <c r="P100" s="182"/>
       <c r="Q100" s="96"/>
       <c r="R100" s="95"/>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A101" s="208"/>
-      <c r="B101" s="226"/>
-      <c r="C101" s="168"/>
-      <c r="D101" s="186"/>
+      <c r="A101" s="227"/>
+      <c r="B101" s="166"/>
+      <c r="C101" s="173"/>
+      <c r="D101" s="175"/>
       <c r="E101" s="156">
         <v>540247772</v>
       </c>
@@ -6288,10 +6301,10 @@
       <c r="R101" s="95"/>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A102" s="208"/>
-      <c r="B102" s="226"/>
-      <c r="C102" s="168"/>
-      <c r="D102" s="186"/>
+      <c r="A102" s="227"/>
+      <c r="B102" s="166"/>
+      <c r="C102" s="173"/>
+      <c r="D102" s="175"/>
       <c r="E102" s="156">
         <v>540247780</v>
       </c>
@@ -6310,10 +6323,10 @@
       <c r="R102" s="95"/>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A103" s="208"/>
-      <c r="B103" s="226"/>
-      <c r="C103" s="168"/>
-      <c r="D103" s="186"/>
+      <c r="A103" s="227"/>
+      <c r="B103" s="166"/>
+      <c r="C103" s="173"/>
+      <c r="D103" s="175"/>
       <c r="E103" s="156">
         <v>540247764</v>
       </c>
@@ -6332,10 +6345,10 @@
       <c r="R103" s="95"/>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A104" s="208"/>
-      <c r="B104" s="226"/>
-      <c r="C104" s="168"/>
-      <c r="D104" s="186"/>
+      <c r="A104" s="227"/>
+      <c r="B104" s="166"/>
+      <c r="C104" s="173"/>
+      <c r="D104" s="175"/>
       <c r="E104" s="156">
         <v>540247756</v>
       </c>
@@ -6354,10 +6367,10 @@
       <c r="R104" s="95"/>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A105" s="208"/>
-      <c r="B105" s="226"/>
-      <c r="C105" s="168"/>
-      <c r="D105" s="186"/>
+      <c r="A105" s="227"/>
+      <c r="B105" s="166"/>
+      <c r="C105" s="173"/>
+      <c r="D105" s="175"/>
       <c r="E105" s="156">
         <v>540247798</v>
       </c>
@@ -6376,10 +6389,10 @@
       <c r="R105" s="95"/>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A106" s="208"/>
-      <c r="B106" s="226"/>
-      <c r="C106" s="168"/>
-      <c r="D106" s="186"/>
+      <c r="A106" s="227"/>
+      <c r="B106" s="166"/>
+      <c r="C106" s="173"/>
+      <c r="D106" s="175"/>
       <c r="E106" s="156">
         <v>550261903</v>
       </c>
@@ -6398,10 +6411,10 @@
       <c r="R106" s="95"/>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A107" s="208"/>
-      <c r="B107" s="226"/>
-      <c r="C107" s="168"/>
-      <c r="D107" s="186"/>
+      <c r="A107" s="227"/>
+      <c r="B107" s="166"/>
+      <c r="C107" s="173"/>
+      <c r="D107" s="175"/>
       <c r="E107" s="156">
         <v>550261895</v>
       </c>
@@ -6420,10 +6433,10 @@
       <c r="R107" s="95"/>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A108" s="208"/>
-      <c r="B108" s="226"/>
-      <c r="C108" s="168"/>
-      <c r="D108" s="186"/>
+      <c r="A108" s="227"/>
+      <c r="B108" s="166"/>
+      <c r="C108" s="173"/>
+      <c r="D108" s="175"/>
       <c r="E108" s="156">
         <v>540256716</v>
       </c>
@@ -6442,10 +6455,10 @@
       <c r="R108" s="95"/>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A109" s="208"/>
-      <c r="B109" s="226"/>
-      <c r="C109" s="168"/>
-      <c r="D109" s="186"/>
+      <c r="A109" s="227"/>
+      <c r="B109" s="166"/>
+      <c r="C109" s="173"/>
+      <c r="D109" s="175"/>
       <c r="E109" s="156">
         <v>520033986</v>
       </c>
@@ -6464,10 +6477,10 @@
       <c r="R109" s="95"/>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A110" s="208"/>
-      <c r="B110" s="226"/>
-      <c r="C110" s="168"/>
-      <c r="D110" s="186"/>
+      <c r="A110" s="227"/>
+      <c r="B110" s="166"/>
+      <c r="C110" s="173"/>
+      <c r="D110" s="175"/>
       <c r="E110" s="156">
         <v>540303526</v>
       </c>
@@ -6486,10 +6499,10 @@
       <c r="R110" s="95"/>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A111" s="208"/>
-      <c r="B111" s="226"/>
-      <c r="C111" s="168"/>
-      <c r="D111" s="186"/>
+      <c r="A111" s="227"/>
+      <c r="B111" s="166"/>
+      <c r="C111" s="173"/>
+      <c r="D111" s="175"/>
       <c r="E111" s="156">
         <v>540303369</v>
       </c>
@@ -6508,10 +6521,10 @@
       <c r="R111" s="95"/>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A112" s="208"/>
-      <c r="B112" s="226"/>
-      <c r="C112" s="168"/>
-      <c r="D112" s="186"/>
+      <c r="A112" s="227"/>
+      <c r="B112" s="166"/>
+      <c r="C112" s="173"/>
+      <c r="D112" s="175"/>
       <c r="E112" s="156">
         <v>550275507</v>
       </c>
@@ -6530,43 +6543,43 @@
       <c r="R112" s="95"/>
     </row>
     <row r="113" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="208"/>
-      <c r="B113" s="226"/>
-      <c r="C113" s="168"/>
-      <c r="D113" s="186"/>
+      <c r="A113" s="227"/>
+      <c r="B113" s="166"/>
+      <c r="C113" s="173"/>
+      <c r="D113" s="175"/>
       <c r="E113" s="156">
         <v>540306099</v>
       </c>
       <c r="F113" s="152"/>
       <c r="G113" s="154"/>
-      <c r="H113" s="194" t="s">
+      <c r="H113" s="186" t="s">
         <v>197</v>
       </c>
-      <c r="I113" s="195"/>
-      <c r="J113" s="195"/>
-      <c r="K113" s="195"/>
-      <c r="L113" s="195"/>
-      <c r="M113" s="195"/>
-      <c r="N113" s="195"/>
-      <c r="O113" s="195"/>
-      <c r="P113" s="195"/>
+      <c r="I113" s="187"/>
+      <c r="J113" s="187"/>
+      <c r="K113" s="187"/>
+      <c r="L113" s="187"/>
+      <c r="M113" s="187"/>
+      <c r="N113" s="187"/>
+      <c r="O113" s="187"/>
+      <c r="P113" s="187"/>
       <c r="Q113" s="96"/>
       <c r="R113" s="95"/>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A114" s="196" t="s">
+      <c r="A114" s="211" t="s">
         <v>43</v>
       </c>
-      <c r="B114" s="199" t="s">
+      <c r="B114" s="214" t="s">
         <v>197</v>
       </c>
-      <c r="C114" s="202" t="s">
+      <c r="C114" s="225" t="s">
         <v>40</v>
       </c>
-      <c r="D114" s="264">
+      <c r="D114" s="198">
         <v>119</v>
       </c>
-      <c r="E114" s="214">
+      <c r="E114" s="238">
         <v>513846808</v>
       </c>
       <c r="F114" s="104" t="s">
@@ -6575,49 +6588,49 @@
       <c r="G114" s="134">
         <v>100</v>
       </c>
-      <c r="H114" s="227" t="s">
+      <c r="H114" s="249" t="s">
         <v>347</v>
       </c>
-      <c r="I114" s="228"/>
-      <c r="J114" s="228"/>
-      <c r="K114" s="228"/>
-      <c r="L114" s="228"/>
-      <c r="M114" s="228"/>
-      <c r="N114" s="228"/>
-      <c r="O114" s="228"/>
-      <c r="P114" s="228"/>
-      <c r="Q114" s="231" t="s">
+      <c r="I114" s="250"/>
+      <c r="J114" s="250"/>
+      <c r="K114" s="250"/>
+      <c r="L114" s="250"/>
+      <c r="M114" s="250"/>
+      <c r="N114" s="250"/>
+      <c r="O114" s="250"/>
+      <c r="P114" s="250"/>
+      <c r="Q114" s="253" t="s">
         <v>189</v>
       </c>
       <c r="R114" s="89"/>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A115" s="197"/>
-      <c r="B115" s="200"/>
-      <c r="C115" s="183"/>
-      <c r="D115" s="187"/>
-      <c r="E115" s="182"/>
+      <c r="A115" s="212"/>
+      <c r="B115" s="215"/>
+      <c r="C115" s="174"/>
+      <c r="D115" s="176"/>
+      <c r="E115" s="178"/>
       <c r="F115" s="10" t="s">
         <v>272</v>
       </c>
       <c r="G115" s="135">
         <v>200</v>
       </c>
-      <c r="H115" s="229"/>
-      <c r="I115" s="230"/>
-      <c r="J115" s="230"/>
-      <c r="K115" s="230"/>
-      <c r="L115" s="230"/>
-      <c r="M115" s="230"/>
-      <c r="N115" s="230"/>
-      <c r="O115" s="230"/>
-      <c r="P115" s="230"/>
-      <c r="Q115" s="232"/>
+      <c r="H115" s="251"/>
+      <c r="I115" s="252"/>
+      <c r="J115" s="252"/>
+      <c r="K115" s="252"/>
+      <c r="L115" s="252"/>
+      <c r="M115" s="252"/>
+      <c r="N115" s="252"/>
+      <c r="O115" s="252"/>
+      <c r="P115" s="252"/>
+      <c r="Q115" s="254"/>
       <c r="R115" s="90"/>
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A116" s="197"/>
-      <c r="B116" s="200"/>
+      <c r="A116" s="212"/>
+      <c r="B116" s="215"/>
       <c r="C116" s="79" t="s">
         <v>41</v>
       </c>
@@ -6633,32 +6646,32 @@
       <c r="G116" s="135">
         <v>100</v>
       </c>
-      <c r="H116" s="220" t="s">
+      <c r="H116" s="256" t="s">
         <v>347</v>
       </c>
-      <c r="I116" s="221"/>
-      <c r="J116" s="221"/>
-      <c r="K116" s="221"/>
-      <c r="L116" s="221"/>
-      <c r="M116" s="221"/>
-      <c r="N116" s="221"/>
-      <c r="O116" s="221"/>
-      <c r="P116" s="221"/>
-      <c r="Q116" s="232"/>
+      <c r="I116" s="257"/>
+      <c r="J116" s="257"/>
+      <c r="K116" s="257"/>
+      <c r="L116" s="257"/>
+      <c r="M116" s="257"/>
+      <c r="N116" s="257"/>
+      <c r="O116" s="257"/>
+      <c r="P116" s="257"/>
+      <c r="Q116" s="254"/>
       <c r="R116" s="90"/>
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A117" s="197"/>
-      <c r="B117" s="234" t="s">
+      <c r="A117" s="212"/>
+      <c r="B117" s="245" t="s">
         <v>44</v>
       </c>
-      <c r="C117" s="192" t="s">
+      <c r="C117" s="218" t="s">
         <v>42</v>
       </c>
-      <c r="D117" s="191">
+      <c r="D117" s="200">
         <v>74</v>
       </c>
-      <c r="E117" s="193">
+      <c r="E117" s="221">
         <v>512362914</v>
       </c>
       <c r="F117" s="10" t="s">
@@ -6676,15 +6689,15 @@
       <c r="N117" s="43"/>
       <c r="O117" s="43"/>
       <c r="P117" s="1"/>
-      <c r="Q117" s="232"/>
+      <c r="Q117" s="254"/>
       <c r="R117" s="90"/>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A118" s="197"/>
-      <c r="B118" s="234"/>
-      <c r="C118" s="192"/>
-      <c r="D118" s="191"/>
-      <c r="E118" s="193"/>
+      <c r="A118" s="212"/>
+      <c r="B118" s="245"/>
+      <c r="C118" s="218"/>
+      <c r="D118" s="200"/>
+      <c r="E118" s="221"/>
       <c r="F118" s="10" t="s">
         <v>177</v>
       </c>
@@ -6700,15 +6713,15 @@
       <c r="N118" s="43"/>
       <c r="O118" s="43"/>
       <c r="P118" s="1"/>
-      <c r="Q118" s="232"/>
+      <c r="Q118" s="254"/>
       <c r="R118" s="90"/>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A119" s="197"/>
-      <c r="B119" s="234"/>
-      <c r="C119" s="192"/>
-      <c r="D119" s="191"/>
-      <c r="E119" s="193"/>
+      <c r="A119" s="212"/>
+      <c r="B119" s="245"/>
+      <c r="C119" s="218"/>
+      <c r="D119" s="200"/>
+      <c r="E119" s="221"/>
       <c r="F119" s="10" t="s">
         <v>178</v>
       </c>
@@ -6724,15 +6737,15 @@
       <c r="N119" s="43"/>
       <c r="O119" s="43"/>
       <c r="P119" s="1"/>
-      <c r="Q119" s="232"/>
+      <c r="Q119" s="254"/>
       <c r="R119" s="90"/>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A120" s="197"/>
-      <c r="B120" s="234"/>
-      <c r="C120" s="192"/>
-      <c r="D120" s="191"/>
-      <c r="E120" s="193"/>
+      <c r="A120" s="212"/>
+      <c r="B120" s="245"/>
+      <c r="C120" s="218"/>
+      <c r="D120" s="200"/>
+      <c r="E120" s="221"/>
       <c r="F120" s="10" t="s">
         <v>178</v>
       </c>
@@ -6748,15 +6761,15 @@
       <c r="N120" s="43"/>
       <c r="O120" s="43"/>
       <c r="P120" s="1"/>
-      <c r="Q120" s="232"/>
+      <c r="Q120" s="254"/>
       <c r="R120" s="90"/>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A121" s="197"/>
-      <c r="B121" s="234"/>
-      <c r="C121" s="192"/>
-      <c r="D121" s="191"/>
-      <c r="E121" s="193"/>
+      <c r="A121" s="212"/>
+      <c r="B121" s="245"/>
+      <c r="C121" s="218"/>
+      <c r="D121" s="200"/>
+      <c r="E121" s="221"/>
       <c r="F121" s="10" t="s">
         <v>360</v>
       </c>
@@ -6772,15 +6785,15 @@
       <c r="N121" s="43"/>
       <c r="O121" s="43"/>
       <c r="P121" s="1"/>
-      <c r="Q121" s="232"/>
+      <c r="Q121" s="254"/>
       <c r="R121" s="90"/>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A122" s="197"/>
-      <c r="B122" s="234"/>
-      <c r="C122" s="192"/>
-      <c r="D122" s="191"/>
-      <c r="E122" s="193"/>
+      <c r="A122" s="212"/>
+      <c r="B122" s="245"/>
+      <c r="C122" s="218"/>
+      <c r="D122" s="200"/>
+      <c r="E122" s="221"/>
       <c r="F122" s="10" t="s">
         <v>360</v>
       </c>
@@ -6796,15 +6809,15 @@
       <c r="N122" s="43"/>
       <c r="O122" s="43"/>
       <c r="P122" s="1"/>
-      <c r="Q122" s="232"/>
+      <c r="Q122" s="254"/>
       <c r="R122" s="90"/>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A123" s="197"/>
-      <c r="B123" s="234"/>
-      <c r="C123" s="192"/>
-      <c r="D123" s="191"/>
-      <c r="E123" s="193"/>
+      <c r="A123" s="212"/>
+      <c r="B123" s="245"/>
+      <c r="C123" s="218"/>
+      <c r="D123" s="200"/>
+      <c r="E123" s="221"/>
       <c r="F123" s="10" t="s">
         <v>179</v>
       </c>
@@ -6820,15 +6833,15 @@
       <c r="N123" s="43"/>
       <c r="O123" s="43"/>
       <c r="P123" s="1"/>
-      <c r="Q123" s="232"/>
+      <c r="Q123" s="254"/>
       <c r="R123" s="90"/>
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A124" s="197"/>
-      <c r="B124" s="234"/>
-      <c r="C124" s="192"/>
-      <c r="D124" s="191"/>
-      <c r="E124" s="193"/>
+      <c r="A124" s="212"/>
+      <c r="B124" s="245"/>
+      <c r="C124" s="218"/>
+      <c r="D124" s="200"/>
+      <c r="E124" s="221"/>
       <c r="F124" s="10" t="s">
         <v>179</v>
       </c>
@@ -6844,15 +6857,15 @@
       <c r="N124" s="43"/>
       <c r="O124" s="43"/>
       <c r="P124" s="1"/>
-      <c r="Q124" s="232"/>
+      <c r="Q124" s="254"/>
       <c r="R124" s="90"/>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A125" s="197"/>
-      <c r="B125" s="234"/>
-      <c r="C125" s="192"/>
-      <c r="D125" s="191"/>
-      <c r="E125" s="193"/>
+      <c r="A125" s="212"/>
+      <c r="B125" s="245"/>
+      <c r="C125" s="218"/>
+      <c r="D125" s="200"/>
+      <c r="E125" s="221"/>
       <c r="F125" s="10" t="s">
         <v>180</v>
       </c>
@@ -6868,15 +6881,15 @@
       <c r="N125" s="43"/>
       <c r="O125" s="43"/>
       <c r="P125" s="1"/>
-      <c r="Q125" s="232"/>
+      <c r="Q125" s="254"/>
       <c r="R125" s="90"/>
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A126" s="208"/>
-      <c r="B126" s="235"/>
-      <c r="C126" s="167"/>
-      <c r="D126" s="188"/>
-      <c r="E126" s="169"/>
+      <c r="A126" s="227"/>
+      <c r="B126" s="248"/>
+      <c r="C126" s="183"/>
+      <c r="D126" s="184"/>
+      <c r="E126" s="185"/>
       <c r="F126" s="10" t="s">
         <v>180</v>
       </c>
@@ -6892,15 +6905,15 @@
       <c r="N126" s="129"/>
       <c r="O126" s="129"/>
       <c r="P126" s="11"/>
-      <c r="Q126" s="232"/>
+      <c r="Q126" s="254"/>
       <c r="R126" s="95"/>
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A127" s="208"/>
-      <c r="B127" s="235"/>
-      <c r="C127" s="167"/>
-      <c r="D127" s="188"/>
-      <c r="E127" s="169"/>
+      <c r="A127" s="227"/>
+      <c r="B127" s="248"/>
+      <c r="C127" s="183"/>
+      <c r="D127" s="184"/>
+      <c r="E127" s="185"/>
       <c r="F127" s="10" t="s">
         <v>181</v>
       </c>
@@ -6916,15 +6929,15 @@
       <c r="N127" s="129"/>
       <c r="O127" s="129"/>
       <c r="P127" s="11"/>
-      <c r="Q127" s="232"/>
+      <c r="Q127" s="254"/>
       <c r="R127" s="95"/>
     </row>
     <row r="128" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="198"/>
-      <c r="B128" s="236"/>
-      <c r="C128" s="205"/>
-      <c r="D128" s="266"/>
-      <c r="E128" s="225"/>
+      <c r="A128" s="213"/>
+      <c r="B128" s="246"/>
+      <c r="C128" s="219"/>
+      <c r="D128" s="201"/>
+      <c r="E128" s="222"/>
       <c r="F128" s="92" t="s">
         <v>181</v>
       </c>
@@ -6940,23 +6953,23 @@
       <c r="N128" s="117"/>
       <c r="O128" s="117"/>
       <c r="P128" s="101"/>
-      <c r="Q128" s="233"/>
+      <c r="Q128" s="255"/>
       <c r="R128" s="93"/>
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A129" s="196" t="s">
+      <c r="A129" s="211" t="s">
         <v>45</v>
       </c>
-      <c r="B129" s="199" t="s">
+      <c r="B129" s="214" t="s">
         <v>197</v>
       </c>
-      <c r="C129" s="237" t="s">
+      <c r="C129" s="217" t="s">
         <v>46</v>
       </c>
-      <c r="D129" s="264">
+      <c r="D129" s="198">
         <v>1164</v>
       </c>
-      <c r="E129" s="214">
+      <c r="E129" s="238">
         <v>511303661</v>
       </c>
       <c r="F129" s="104" t="s">
@@ -6965,51 +6978,51 @@
       <c r="G129" s="134">
         <v>100</v>
       </c>
-      <c r="H129" s="176" t="s">
+      <c r="H129" s="239" t="s">
         <v>347</v>
       </c>
-      <c r="I129" s="177"/>
-      <c r="J129" s="177"/>
-      <c r="K129" s="177"/>
-      <c r="L129" s="177"/>
-      <c r="M129" s="177"/>
-      <c r="N129" s="177"/>
-      <c r="O129" s="177"/>
-      <c r="P129" s="177"/>
+      <c r="I129" s="240"/>
+      <c r="J129" s="240"/>
+      <c r="K129" s="240"/>
+      <c r="L129" s="240"/>
+      <c r="M129" s="240"/>
+      <c r="N129" s="240"/>
+      <c r="O129" s="240"/>
+      <c r="P129" s="240"/>
       <c r="Q129" s="88"/>
       <c r="R129" s="89"/>
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A130" s="197"/>
-      <c r="B130" s="200"/>
-      <c r="C130" s="192"/>
-      <c r="D130" s="186"/>
-      <c r="E130" s="170"/>
+      <c r="A130" s="212"/>
+      <c r="B130" s="215"/>
+      <c r="C130" s="218"/>
+      <c r="D130" s="175"/>
+      <c r="E130" s="177"/>
       <c r="F130" s="10" t="s">
         <v>278</v>
       </c>
       <c r="G130" s="135">
         <v>200</v>
       </c>
-      <c r="H130" s="180"/>
-      <c r="I130" s="181"/>
-      <c r="J130" s="181"/>
-      <c r="K130" s="181"/>
-      <c r="L130" s="181"/>
-      <c r="M130" s="181"/>
-      <c r="N130" s="181"/>
-      <c r="O130" s="181"/>
-      <c r="P130" s="181"/>
+      <c r="H130" s="242"/>
+      <c r="I130" s="243"/>
+      <c r="J130" s="243"/>
+      <c r="K130" s="243"/>
+      <c r="L130" s="243"/>
+      <c r="M130" s="243"/>
+      <c r="N130" s="243"/>
+      <c r="O130" s="243"/>
+      <c r="P130" s="243"/>
       <c r="Q130" s="6"/>
       <c r="R130" s="90"/>
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A131" s="197"/>
-      <c r="B131" s="200"/>
-      <c r="C131" s="167" t="s">
+      <c r="A131" s="212"/>
+      <c r="B131" s="215"/>
+      <c r="C131" s="183" t="s">
         <v>47</v>
       </c>
-      <c r="D131" s="186">
+      <c r="D131" s="175">
         <v>146</v>
       </c>
       <c r="E131" s="157">
@@ -7021,25 +7034,25 @@
       <c r="G131" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="H131" s="165" t="s">
+      <c r="H131" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I131" s="166"/>
-      <c r="J131" s="166"/>
-      <c r="K131" s="166"/>
-      <c r="L131" s="166"/>
-      <c r="M131" s="166"/>
-      <c r="N131" s="166"/>
-      <c r="O131" s="166"/>
-      <c r="P131" s="166"/>
+      <c r="I131" s="182"/>
+      <c r="J131" s="182"/>
+      <c r="K131" s="182"/>
+      <c r="L131" s="182"/>
+      <c r="M131" s="182"/>
+      <c r="N131" s="182"/>
+      <c r="O131" s="182"/>
+      <c r="P131" s="182"/>
       <c r="Q131" s="6"/>
       <c r="R131" s="90"/>
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A132" s="197"/>
-      <c r="B132" s="200"/>
-      <c r="C132" s="168"/>
-      <c r="D132" s="186"/>
+      <c r="A132" s="212"/>
+      <c r="B132" s="215"/>
+      <c r="C132" s="173"/>
+      <c r="D132" s="175"/>
       <c r="E132" s="157">
         <v>540281631</v>
       </c>
@@ -7049,25 +7062,25 @@
       <c r="G132" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="H132" s="165" t="s">
+      <c r="H132" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I132" s="166"/>
-      <c r="J132" s="166"/>
-      <c r="K132" s="166"/>
-      <c r="L132" s="166"/>
-      <c r="M132" s="166"/>
-      <c r="N132" s="166"/>
-      <c r="O132" s="166"/>
-      <c r="P132" s="166"/>
+      <c r="I132" s="182"/>
+      <c r="J132" s="182"/>
+      <c r="K132" s="182"/>
+      <c r="L132" s="182"/>
+      <c r="M132" s="182"/>
+      <c r="N132" s="182"/>
+      <c r="O132" s="182"/>
+      <c r="P132" s="182"/>
       <c r="Q132" s="6"/>
       <c r="R132" s="90"/>
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A133" s="197"/>
-      <c r="B133" s="200"/>
-      <c r="C133" s="183"/>
-      <c r="D133" s="187"/>
+      <c r="A133" s="212"/>
+      <c r="B133" s="215"/>
+      <c r="C133" s="174"/>
+      <c r="D133" s="176"/>
       <c r="E133" s="157">
         <v>520004896</v>
       </c>
@@ -7077,23 +7090,23 @@
       <c r="G133" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="H133" s="165" t="s">
+      <c r="H133" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I133" s="166"/>
-      <c r="J133" s="166"/>
-      <c r="K133" s="166"/>
-      <c r="L133" s="166"/>
-      <c r="M133" s="166"/>
-      <c r="N133" s="166"/>
-      <c r="O133" s="166"/>
-      <c r="P133" s="166"/>
+      <c r="I133" s="182"/>
+      <c r="J133" s="182"/>
+      <c r="K133" s="182"/>
+      <c r="L133" s="182"/>
+      <c r="M133" s="182"/>
+      <c r="N133" s="182"/>
+      <c r="O133" s="182"/>
+      <c r="P133" s="182"/>
       <c r="Q133" s="6"/>
       <c r="R133" s="90"/>
     </row>
     <row r="134" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="198"/>
-      <c r="B134" s="201"/>
+      <c r="A134" s="213"/>
+      <c r="B134" s="216"/>
       <c r="C134" s="84" t="s">
         <v>48</v>
       </c>
@@ -7109,34 +7122,34 @@
       <c r="G134" s="106" t="s">
         <v>118</v>
       </c>
-      <c r="H134" s="222" t="s">
+      <c r="H134" s="208" t="s">
         <v>197</v>
       </c>
-      <c r="I134" s="223"/>
-      <c r="J134" s="223"/>
-      <c r="K134" s="223"/>
-      <c r="L134" s="223"/>
-      <c r="M134" s="223"/>
-      <c r="N134" s="223"/>
-      <c r="O134" s="223"/>
-      <c r="P134" s="223"/>
+      <c r="I134" s="209"/>
+      <c r="J134" s="209"/>
+      <c r="K134" s="209"/>
+      <c r="L134" s="209"/>
+      <c r="M134" s="209"/>
+      <c r="N134" s="209"/>
+      <c r="O134" s="209"/>
+      <c r="P134" s="209"/>
       <c r="Q134" s="102"/>
       <c r="R134" s="93"/>
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A135" s="196" t="s">
+      <c r="A135" s="211" t="s">
         <v>49</v>
       </c>
-      <c r="B135" s="199" t="s">
+      <c r="B135" s="214" t="s">
         <v>197</v>
       </c>
-      <c r="C135" s="202" t="s">
+      <c r="C135" s="225" t="s">
         <v>50</v>
       </c>
-      <c r="D135" s="264">
+      <c r="D135" s="198">
         <v>70</v>
       </c>
-      <c r="E135" s="214">
+      <c r="E135" s="238">
         <v>514884485</v>
       </c>
       <c r="F135" s="104" t="s">
@@ -7145,49 +7158,49 @@
       <c r="G135" s="134">
         <v>100</v>
       </c>
-      <c r="H135" s="238" t="s">
+      <c r="H135" s="206" t="s">
         <v>197</v>
       </c>
-      <c r="I135" s="239"/>
-      <c r="J135" s="239"/>
-      <c r="K135" s="239"/>
-      <c r="L135" s="239"/>
-      <c r="M135" s="239"/>
-      <c r="N135" s="239"/>
-      <c r="O135" s="239"/>
-      <c r="P135" s="239"/>
+      <c r="I135" s="207"/>
+      <c r="J135" s="207"/>
+      <c r="K135" s="207"/>
+      <c r="L135" s="207"/>
+      <c r="M135" s="207"/>
+      <c r="N135" s="207"/>
+      <c r="O135" s="207"/>
+      <c r="P135" s="207"/>
       <c r="Q135" s="88"/>
       <c r="R135" s="89"/>
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A136" s="197"/>
-      <c r="B136" s="200"/>
-      <c r="C136" s="183"/>
-      <c r="D136" s="187"/>
-      <c r="E136" s="182"/>
+      <c r="A136" s="212"/>
+      <c r="B136" s="215"/>
+      <c r="C136" s="174"/>
+      <c r="D136" s="176"/>
+      <c r="E136" s="178"/>
       <c r="F136" s="10" t="s">
         <v>285</v>
       </c>
       <c r="G136" s="135">
         <v>200</v>
       </c>
-      <c r="H136" s="165" t="s">
+      <c r="H136" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I136" s="166"/>
-      <c r="J136" s="166"/>
-      <c r="K136" s="166"/>
-      <c r="L136" s="166"/>
-      <c r="M136" s="166"/>
-      <c r="N136" s="166"/>
-      <c r="O136" s="166"/>
-      <c r="P136" s="166"/>
+      <c r="I136" s="182"/>
+      <c r="J136" s="182"/>
+      <c r="K136" s="182"/>
+      <c r="L136" s="182"/>
+      <c r="M136" s="182"/>
+      <c r="N136" s="182"/>
+      <c r="O136" s="182"/>
+      <c r="P136" s="182"/>
       <c r="Q136" s="6"/>
       <c r="R136" s="90"/>
     </row>
     <row r="137" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="198"/>
-      <c r="B137" s="201"/>
+      <c r="A137" s="213"/>
+      <c r="B137" s="216"/>
       <c r="C137" s="84" t="s">
         <v>51</v>
       </c>
@@ -7203,22 +7216,22 @@
       <c r="G137" s="137">
         <v>100</v>
       </c>
-      <c r="H137" s="222" t="s">
+      <c r="H137" s="208" t="s">
         <v>197</v>
       </c>
-      <c r="I137" s="223"/>
-      <c r="J137" s="223"/>
-      <c r="K137" s="223"/>
-      <c r="L137" s="223"/>
-      <c r="M137" s="223"/>
-      <c r="N137" s="223"/>
-      <c r="O137" s="223"/>
-      <c r="P137" s="223"/>
+      <c r="I137" s="209"/>
+      <c r="J137" s="209"/>
+      <c r="K137" s="209"/>
+      <c r="L137" s="209"/>
+      <c r="M137" s="209"/>
+      <c r="N137" s="209"/>
+      <c r="O137" s="209"/>
+      <c r="P137" s="209"/>
       <c r="Q137" s="102"/>
       <c r="R137" s="93"/>
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A138" s="196" t="s">
+      <c r="A138" s="211" t="s">
         <v>52</v>
       </c>
       <c r="B138" s="83" t="s">
@@ -7239,29 +7252,29 @@
       <c r="G138" s="134">
         <v>8831</v>
       </c>
-      <c r="H138" s="238" t="s">
+      <c r="H138" s="206" t="s">
         <v>197</v>
       </c>
-      <c r="I138" s="239"/>
-      <c r="J138" s="239"/>
-      <c r="K138" s="239"/>
-      <c r="L138" s="239"/>
-      <c r="M138" s="239"/>
-      <c r="N138" s="239"/>
-      <c r="O138" s="239"/>
-      <c r="P138" s="239"/>
+      <c r="I138" s="207"/>
+      <c r="J138" s="207"/>
+      <c r="K138" s="207"/>
+      <c r="L138" s="207"/>
+      <c r="M138" s="207"/>
+      <c r="N138" s="207"/>
+      <c r="O138" s="207"/>
+      <c r="P138" s="207"/>
       <c r="Q138" s="88"/>
       <c r="R138" s="89"/>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A139" s="197"/>
-      <c r="B139" s="200" t="s">
+      <c r="A139" s="212"/>
+      <c r="B139" s="215" t="s">
         <v>197</v>
       </c>
-      <c r="C139" s="167" t="s">
+      <c r="C139" s="183" t="s">
         <v>54</v>
       </c>
-      <c r="D139" s="188">
+      <c r="D139" s="184">
         <v>1169</v>
       </c>
       <c r="E139" s="156">
@@ -7273,25 +7286,25 @@
       <c r="G139" s="135">
         <v>1</v>
       </c>
-      <c r="H139" s="165" t="s">
+      <c r="H139" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I139" s="166"/>
-      <c r="J139" s="166"/>
-      <c r="K139" s="166"/>
-      <c r="L139" s="166"/>
-      <c r="M139" s="166"/>
-      <c r="N139" s="166"/>
-      <c r="O139" s="166"/>
-      <c r="P139" s="166"/>
+      <c r="I139" s="182"/>
+      <c r="J139" s="182"/>
+      <c r="K139" s="182"/>
+      <c r="L139" s="182"/>
+      <c r="M139" s="182"/>
+      <c r="N139" s="182"/>
+      <c r="O139" s="182"/>
+      <c r="P139" s="182"/>
       <c r="Q139" s="6"/>
       <c r="R139" s="90"/>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A140" s="197"/>
-      <c r="B140" s="200"/>
-      <c r="C140" s="168"/>
-      <c r="D140" s="186"/>
+      <c r="A140" s="212"/>
+      <c r="B140" s="215"/>
+      <c r="C140" s="173"/>
+      <c r="D140" s="175"/>
       <c r="E140" s="156">
         <v>540313467</v>
       </c>
@@ -7301,25 +7314,25 @@
       <c r="G140" s="135">
         <v>1000</v>
       </c>
-      <c r="H140" s="165" t="s">
+      <c r="H140" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I140" s="166"/>
-      <c r="J140" s="166"/>
-      <c r="K140" s="166"/>
-      <c r="L140" s="166"/>
-      <c r="M140" s="166"/>
-      <c r="N140" s="166"/>
-      <c r="O140" s="166"/>
-      <c r="P140" s="166"/>
+      <c r="I140" s="182"/>
+      <c r="J140" s="182"/>
+      <c r="K140" s="182"/>
+      <c r="L140" s="182"/>
+      <c r="M140" s="182"/>
+      <c r="N140" s="182"/>
+      <c r="O140" s="182"/>
+      <c r="P140" s="182"/>
       <c r="Q140" s="6"/>
       <c r="R140" s="90"/>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A141" s="197"/>
-      <c r="B141" s="200"/>
-      <c r="C141" s="168"/>
-      <c r="D141" s="186"/>
+      <c r="A141" s="212"/>
+      <c r="B141" s="215"/>
+      <c r="C141" s="173"/>
+      <c r="D141" s="175"/>
       <c r="E141" s="156">
         <v>540313566</v>
       </c>
@@ -7329,25 +7342,25 @@
       <c r="G141" s="135">
         <v>1001</v>
       </c>
-      <c r="H141" s="165" t="s">
+      <c r="H141" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I141" s="166"/>
-      <c r="J141" s="166"/>
-      <c r="K141" s="166"/>
-      <c r="L141" s="166"/>
-      <c r="M141" s="166"/>
-      <c r="N141" s="166"/>
-      <c r="O141" s="166"/>
-      <c r="P141" s="166"/>
+      <c r="I141" s="182"/>
+      <c r="J141" s="182"/>
+      <c r="K141" s="182"/>
+      <c r="L141" s="182"/>
+      <c r="M141" s="182"/>
+      <c r="N141" s="182"/>
+      <c r="O141" s="182"/>
+      <c r="P141" s="182"/>
       <c r="Q141" s="6"/>
       <c r="R141" s="90"/>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A142" s="197"/>
-      <c r="B142" s="200"/>
-      <c r="C142" s="168"/>
-      <c r="D142" s="186"/>
+      <c r="A142" s="212"/>
+      <c r="B142" s="215"/>
+      <c r="C142" s="173"/>
+      <c r="D142" s="175"/>
       <c r="E142" s="156">
         <v>540330099</v>
       </c>
@@ -7357,25 +7370,25 @@
       <c r="G142" s="135">
         <v>1002</v>
       </c>
-      <c r="H142" s="165" t="s">
+      <c r="H142" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I142" s="166"/>
-      <c r="J142" s="166"/>
-      <c r="K142" s="166"/>
-      <c r="L142" s="166"/>
-      <c r="M142" s="166"/>
-      <c r="N142" s="166"/>
-      <c r="O142" s="166"/>
-      <c r="P142" s="166"/>
+      <c r="I142" s="182"/>
+      <c r="J142" s="182"/>
+      <c r="K142" s="182"/>
+      <c r="L142" s="182"/>
+      <c r="M142" s="182"/>
+      <c r="N142" s="182"/>
+      <c r="O142" s="182"/>
+      <c r="P142" s="182"/>
       <c r="Q142" s="6"/>
       <c r="R142" s="90"/>
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A143" s="197"/>
-      <c r="B143" s="200"/>
-      <c r="C143" s="183"/>
-      <c r="D143" s="187"/>
+      <c r="A143" s="212"/>
+      <c r="B143" s="215"/>
+      <c r="C143" s="174"/>
+      <c r="D143" s="176"/>
       <c r="E143" s="156">
         <v>540313459</v>
       </c>
@@ -7385,23 +7398,23 @@
       <c r="G143" s="135">
         <v>1003</v>
       </c>
-      <c r="H143" s="165" t="s">
+      <c r="H143" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I143" s="166"/>
-      <c r="J143" s="166"/>
-      <c r="K143" s="166"/>
-      <c r="L143" s="166"/>
-      <c r="M143" s="166"/>
-      <c r="N143" s="166"/>
-      <c r="O143" s="166"/>
-      <c r="P143" s="166"/>
+      <c r="I143" s="182"/>
+      <c r="J143" s="182"/>
+      <c r="K143" s="182"/>
+      <c r="L143" s="182"/>
+      <c r="M143" s="182"/>
+      <c r="N143" s="182"/>
+      <c r="O143" s="182"/>
+      <c r="P143" s="182"/>
       <c r="Q143" s="6"/>
       <c r="R143" s="90"/>
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A144" s="197"/>
-      <c r="B144" s="234" t="s">
+      <c r="A144" s="212"/>
+      <c r="B144" s="245" t="s">
         <v>70</v>
       </c>
       <c r="C144" s="79" t="s">
@@ -7419,23 +7432,23 @@
       <c r="G144" s="135">
         <v>16</v>
       </c>
-      <c r="H144" s="165" t="s">
+      <c r="H144" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I144" s="166"/>
-      <c r="J144" s="166"/>
-      <c r="K144" s="166"/>
-      <c r="L144" s="166"/>
-      <c r="M144" s="166"/>
-      <c r="N144" s="166"/>
-      <c r="O144" s="166"/>
-      <c r="P144" s="166"/>
+      <c r="I144" s="182"/>
+      <c r="J144" s="182"/>
+      <c r="K144" s="182"/>
+      <c r="L144" s="182"/>
+      <c r="M144" s="182"/>
+      <c r="N144" s="182"/>
+      <c r="O144" s="182"/>
+      <c r="P144" s="182"/>
       <c r="Q144" s="6"/>
       <c r="R144" s="90"/>
     </row>
     <row r="145" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A145" s="197"/>
-      <c r="B145" s="234"/>
+      <c r="A145" s="212"/>
+      <c r="B145" s="245"/>
       <c r="C145" s="79" t="s">
         <v>58</v>
       </c>
@@ -7451,23 +7464,23 @@
       <c r="G145" s="135">
         <v>5</v>
       </c>
-      <c r="H145" s="165" t="s">
+      <c r="H145" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I145" s="166"/>
-      <c r="J145" s="166"/>
-      <c r="K145" s="166"/>
-      <c r="L145" s="166"/>
-      <c r="M145" s="166"/>
-      <c r="N145" s="166"/>
-      <c r="O145" s="166"/>
-      <c r="P145" s="166"/>
+      <c r="I145" s="182"/>
+      <c r="J145" s="182"/>
+      <c r="K145" s="182"/>
+      <c r="L145" s="182"/>
+      <c r="M145" s="182"/>
+      <c r="N145" s="182"/>
+      <c r="O145" s="182"/>
+      <c r="P145" s="182"/>
       <c r="Q145" s="6"/>
       <c r="R145" s="90"/>
     </row>
     <row r="146" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A146" s="197"/>
-      <c r="B146" s="234"/>
+      <c r="A146" s="212"/>
+      <c r="B146" s="245"/>
       <c r="C146" s="79" t="s">
         <v>63</v>
       </c>
@@ -7483,23 +7496,23 @@
       <c r="G146" s="135">
         <v>19</v>
       </c>
-      <c r="H146" s="165" t="s">
+      <c r="H146" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I146" s="166"/>
-      <c r="J146" s="166"/>
-      <c r="K146" s="166"/>
-      <c r="L146" s="166"/>
-      <c r="M146" s="166"/>
-      <c r="N146" s="166"/>
-      <c r="O146" s="166"/>
-      <c r="P146" s="166"/>
+      <c r="I146" s="182"/>
+      <c r="J146" s="182"/>
+      <c r="K146" s="182"/>
+      <c r="L146" s="182"/>
+      <c r="M146" s="182"/>
+      <c r="N146" s="182"/>
+      <c r="O146" s="182"/>
+      <c r="P146" s="182"/>
       <c r="Q146" s="6"/>
       <c r="R146" s="90"/>
     </row>
     <row r="147" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A147" s="197"/>
-      <c r="B147" s="234"/>
+      <c r="A147" s="212"/>
+      <c r="B147" s="245"/>
       <c r="C147" s="79" t="s">
         <v>69</v>
       </c>
@@ -7515,25 +7528,25 @@
       <c r="G147" s="135">
         <v>29</v>
       </c>
-      <c r="H147" s="165" t="s">
+      <c r="H147" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I147" s="166"/>
-      <c r="J147" s="166"/>
-      <c r="K147" s="166"/>
-      <c r="L147" s="166"/>
-      <c r="M147" s="166"/>
-      <c r="N147" s="166"/>
-      <c r="O147" s="166"/>
-      <c r="P147" s="166"/>
+      <c r="I147" s="182"/>
+      <c r="J147" s="182"/>
+      <c r="K147" s="182"/>
+      <c r="L147" s="182"/>
+      <c r="M147" s="182"/>
+      <c r="N147" s="182"/>
+      <c r="O147" s="182"/>
+      <c r="P147" s="182"/>
       <c r="Q147" s="6" t="s">
         <v>295</v>
       </c>
       <c r="R147" s="90"/>
     </row>
     <row r="148" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A148" s="197"/>
-      <c r="B148" s="234"/>
+      <c r="A148" s="212"/>
+      <c r="B148" s="245"/>
       <c r="C148" s="79" t="s">
         <v>56</v>
       </c>
@@ -7549,23 +7562,23 @@
       <c r="G148" s="135">
         <v>2</v>
       </c>
-      <c r="H148" s="165" t="s">
+      <c r="H148" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I148" s="166"/>
-      <c r="J148" s="166"/>
-      <c r="K148" s="166"/>
-      <c r="L148" s="166"/>
-      <c r="M148" s="166"/>
-      <c r="N148" s="166"/>
-      <c r="O148" s="166"/>
-      <c r="P148" s="166"/>
+      <c r="I148" s="182"/>
+      <c r="J148" s="182"/>
+      <c r="K148" s="182"/>
+      <c r="L148" s="182"/>
+      <c r="M148" s="182"/>
+      <c r="N148" s="182"/>
+      <c r="O148" s="182"/>
+      <c r="P148" s="182"/>
       <c r="Q148" s="6"/>
       <c r="R148" s="90"/>
     </row>
     <row r="149" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A149" s="197"/>
-      <c r="B149" s="234"/>
+      <c r="A149" s="212"/>
+      <c r="B149" s="245"/>
       <c r="C149" s="79" t="s">
         <v>62</v>
       </c>
@@ -7581,23 +7594,23 @@
       <c r="G149" s="135">
         <v>18</v>
       </c>
-      <c r="H149" s="165" t="s">
+      <c r="H149" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I149" s="166"/>
-      <c r="J149" s="166"/>
-      <c r="K149" s="166"/>
-      <c r="L149" s="166"/>
-      <c r="M149" s="166"/>
-      <c r="N149" s="166"/>
-      <c r="O149" s="166"/>
-      <c r="P149" s="166"/>
+      <c r="I149" s="182"/>
+      <c r="J149" s="182"/>
+      <c r="K149" s="182"/>
+      <c r="L149" s="182"/>
+      <c r="M149" s="182"/>
+      <c r="N149" s="182"/>
+      <c r="O149" s="182"/>
+      <c r="P149" s="182"/>
       <c r="Q149" s="6"/>
       <c r="R149" s="90"/>
     </row>
     <row r="150" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A150" s="197"/>
-      <c r="B150" s="234"/>
+      <c r="A150" s="212"/>
+      <c r="B150" s="245"/>
       <c r="C150" s="79" t="s">
         <v>64</v>
       </c>
@@ -7613,23 +7626,23 @@
       <c r="G150" s="135">
         <v>20</v>
       </c>
-      <c r="H150" s="165" t="s">
+      <c r="H150" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I150" s="166"/>
-      <c r="J150" s="166"/>
-      <c r="K150" s="166"/>
-      <c r="L150" s="166"/>
-      <c r="M150" s="166"/>
-      <c r="N150" s="166"/>
-      <c r="O150" s="166"/>
-      <c r="P150" s="166"/>
+      <c r="I150" s="182"/>
+      <c r="J150" s="182"/>
+      <c r="K150" s="182"/>
+      <c r="L150" s="182"/>
+      <c r="M150" s="182"/>
+      <c r="N150" s="182"/>
+      <c r="O150" s="182"/>
+      <c r="P150" s="182"/>
       <c r="Q150" s="6"/>
       <c r="R150" s="90"/>
     </row>
     <row r="151" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A151" s="197"/>
-      <c r="B151" s="234"/>
+      <c r="A151" s="212"/>
+      <c r="B151" s="245"/>
       <c r="C151" s="79" t="s">
         <v>61</v>
       </c>
@@ -7645,23 +7658,23 @@
       <c r="G151" s="135">
         <v>17</v>
       </c>
-      <c r="H151" s="165" t="s">
+      <c r="H151" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I151" s="166"/>
-      <c r="J151" s="166"/>
-      <c r="K151" s="166"/>
-      <c r="L151" s="166"/>
-      <c r="M151" s="166"/>
-      <c r="N151" s="166"/>
-      <c r="O151" s="166"/>
-      <c r="P151" s="166"/>
+      <c r="I151" s="182"/>
+      <c r="J151" s="182"/>
+      <c r="K151" s="182"/>
+      <c r="L151" s="182"/>
+      <c r="M151" s="182"/>
+      <c r="N151" s="182"/>
+      <c r="O151" s="182"/>
+      <c r="P151" s="182"/>
       <c r="Q151" s="6"/>
       <c r="R151" s="90"/>
     </row>
     <row r="152" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A152" s="197"/>
-      <c r="B152" s="234"/>
+      <c r="A152" s="212"/>
+      <c r="B152" s="245"/>
       <c r="C152" s="79" t="s">
         <v>176</v>
       </c>
@@ -7677,23 +7690,23 @@
       <c r="G152" s="135">
         <v>14</v>
       </c>
-      <c r="H152" s="165" t="s">
+      <c r="H152" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I152" s="166"/>
-      <c r="J152" s="166"/>
-      <c r="K152" s="166"/>
-      <c r="L152" s="166"/>
-      <c r="M152" s="166"/>
-      <c r="N152" s="166"/>
-      <c r="O152" s="166"/>
-      <c r="P152" s="166"/>
+      <c r="I152" s="182"/>
+      <c r="J152" s="182"/>
+      <c r="K152" s="182"/>
+      <c r="L152" s="182"/>
+      <c r="M152" s="182"/>
+      <c r="N152" s="182"/>
+      <c r="O152" s="182"/>
+      <c r="P152" s="182"/>
       <c r="Q152" s="6"/>
       <c r="R152" s="90"/>
     </row>
     <row r="153" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A153" s="197"/>
-      <c r="B153" s="234"/>
+      <c r="A153" s="212"/>
+      <c r="B153" s="245"/>
       <c r="C153" s="79" t="s">
         <v>59</v>
       </c>
@@ -7709,23 +7722,23 @@
       <c r="G153" s="135">
         <v>6</v>
       </c>
-      <c r="H153" s="165" t="s">
+      <c r="H153" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I153" s="166"/>
-      <c r="J153" s="166"/>
-      <c r="K153" s="166"/>
-      <c r="L153" s="166"/>
-      <c r="M153" s="166"/>
-      <c r="N153" s="166"/>
-      <c r="O153" s="166"/>
-      <c r="P153" s="166"/>
+      <c r="I153" s="182"/>
+      <c r="J153" s="182"/>
+      <c r="K153" s="182"/>
+      <c r="L153" s="182"/>
+      <c r="M153" s="182"/>
+      <c r="N153" s="182"/>
+      <c r="O153" s="182"/>
+      <c r="P153" s="182"/>
       <c r="Q153" s="6"/>
       <c r="R153" s="90"/>
     </row>
     <row r="154" spans="1:18" ht="45" x14ac:dyDescent="0.2">
-      <c r="A154" s="197"/>
-      <c r="B154" s="234"/>
+      <c r="A154" s="212"/>
+      <c r="B154" s="245"/>
       <c r="C154" s="79" t="s">
         <v>66</v>
       </c>
@@ -7741,30 +7754,30 @@
       <c r="G154" s="135">
         <v>24</v>
       </c>
-      <c r="H154" s="165" t="s">
+      <c r="H154" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I154" s="166"/>
-      <c r="J154" s="166"/>
-      <c r="K154" s="166"/>
-      <c r="L154" s="166"/>
-      <c r="M154" s="166"/>
-      <c r="N154" s="166"/>
-      <c r="O154" s="166"/>
-      <c r="P154" s="166"/>
+      <c r="I154" s="182"/>
+      <c r="J154" s="182"/>
+      <c r="K154" s="182"/>
+      <c r="L154" s="182"/>
+      <c r="M154" s="182"/>
+      <c r="N154" s="182"/>
+      <c r="O154" s="182"/>
+      <c r="P154" s="182"/>
       <c r="Q154" s="6"/>
       <c r="R154" s="90"/>
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A155" s="197"/>
-      <c r="B155" s="234"/>
-      <c r="C155" s="167" t="s">
+      <c r="A155" s="212"/>
+      <c r="B155" s="245"/>
+      <c r="C155" s="183" t="s">
         <v>98</v>
       </c>
-      <c r="D155" s="188">
+      <c r="D155" s="184">
         <v>72</v>
       </c>
-      <c r="E155" s="169">
+      <c r="E155" s="185">
         <v>520030693</v>
       </c>
       <c r="F155" s="10" t="s">
@@ -7773,75 +7786,75 @@
       <c r="G155" s="135">
         <v>8</v>
       </c>
-      <c r="H155" s="165" t="s">
+      <c r="H155" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I155" s="166"/>
-      <c r="J155" s="166"/>
-      <c r="K155" s="166"/>
-      <c r="L155" s="166"/>
-      <c r="M155" s="166"/>
-      <c r="N155" s="166"/>
-      <c r="O155" s="166"/>
-      <c r="P155" s="166"/>
+      <c r="I155" s="182"/>
+      <c r="J155" s="182"/>
+      <c r="K155" s="182"/>
+      <c r="L155" s="182"/>
+      <c r="M155" s="182"/>
+      <c r="N155" s="182"/>
+      <c r="O155" s="182"/>
+      <c r="P155" s="182"/>
       <c r="Q155" s="6"/>
       <c r="R155" s="90"/>
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A156" s="197"/>
-      <c r="B156" s="234"/>
-      <c r="C156" s="168"/>
-      <c r="D156" s="186"/>
-      <c r="E156" s="170"/>
+      <c r="A156" s="212"/>
+      <c r="B156" s="245"/>
+      <c r="C156" s="173"/>
+      <c r="D156" s="175"/>
+      <c r="E156" s="177"/>
       <c r="F156" s="10" t="s">
         <v>293</v>
       </c>
       <c r="G156" s="135">
         <v>18</v>
       </c>
-      <c r="H156" s="165" t="s">
+      <c r="H156" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I156" s="166"/>
-      <c r="J156" s="166"/>
-      <c r="K156" s="166"/>
-      <c r="L156" s="166"/>
-      <c r="M156" s="166"/>
-      <c r="N156" s="166"/>
-      <c r="O156" s="166"/>
-      <c r="P156" s="166"/>
+      <c r="I156" s="182"/>
+      <c r="J156" s="182"/>
+      <c r="K156" s="182"/>
+      <c r="L156" s="182"/>
+      <c r="M156" s="182"/>
+      <c r="N156" s="182"/>
+      <c r="O156" s="182"/>
+      <c r="P156" s="182"/>
       <c r="Q156" s="6"/>
       <c r="R156" s="90"/>
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A157" s="197"/>
-      <c r="B157" s="234"/>
-      <c r="C157" s="183"/>
-      <c r="D157" s="187"/>
-      <c r="E157" s="182"/>
+      <c r="A157" s="212"/>
+      <c r="B157" s="245"/>
+      <c r="C157" s="174"/>
+      <c r="D157" s="176"/>
+      <c r="E157" s="178"/>
       <c r="F157" s="10" t="s">
         <v>294</v>
       </c>
       <c r="G157" s="135">
         <v>848</v>
       </c>
-      <c r="H157" s="165" t="s">
+      <c r="H157" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I157" s="166"/>
-      <c r="J157" s="166"/>
-      <c r="K157" s="166"/>
-      <c r="L157" s="166"/>
-      <c r="M157" s="166"/>
-      <c r="N157" s="166"/>
-      <c r="O157" s="166"/>
-      <c r="P157" s="166"/>
+      <c r="I157" s="182"/>
+      <c r="J157" s="182"/>
+      <c r="K157" s="182"/>
+      <c r="L157" s="182"/>
+      <c r="M157" s="182"/>
+      <c r="N157" s="182"/>
+      <c r="O157" s="182"/>
+      <c r="P157" s="182"/>
       <c r="Q157" s="6"/>
       <c r="R157" s="90"/>
     </row>
     <row r="158" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A158" s="197"/>
-      <c r="B158" s="234"/>
+      <c r="A158" s="212"/>
+      <c r="B158" s="245"/>
       <c r="C158" s="79" t="s">
         <v>67</v>
       </c>
@@ -7857,23 +7870,23 @@
       <c r="G158" s="135">
         <v>25</v>
       </c>
-      <c r="H158" s="165" t="s">
+      <c r="H158" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I158" s="166"/>
-      <c r="J158" s="166"/>
-      <c r="K158" s="166"/>
-      <c r="L158" s="166"/>
-      <c r="M158" s="166"/>
-      <c r="N158" s="166"/>
-      <c r="O158" s="166"/>
-      <c r="P158" s="166"/>
+      <c r="I158" s="182"/>
+      <c r="J158" s="182"/>
+      <c r="K158" s="182"/>
+      <c r="L158" s="182"/>
+      <c r="M158" s="182"/>
+      <c r="N158" s="182"/>
+      <c r="O158" s="182"/>
+      <c r="P158" s="182"/>
       <c r="Q158" s="6"/>
       <c r="R158" s="90"/>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A159" s="197"/>
-      <c r="B159" s="234"/>
+      <c r="A159" s="212"/>
+      <c r="B159" s="245"/>
       <c r="C159" s="79" t="s">
         <v>65</v>
       </c>
@@ -7889,23 +7902,23 @@
       <c r="G159" s="135">
         <v>23</v>
       </c>
-      <c r="H159" s="165" t="s">
+      <c r="H159" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I159" s="166"/>
-      <c r="J159" s="166"/>
-      <c r="K159" s="166"/>
-      <c r="L159" s="166"/>
-      <c r="M159" s="166"/>
-      <c r="N159" s="166"/>
-      <c r="O159" s="166"/>
-      <c r="P159" s="166"/>
+      <c r="I159" s="182"/>
+      <c r="J159" s="182"/>
+      <c r="K159" s="182"/>
+      <c r="L159" s="182"/>
+      <c r="M159" s="182"/>
+      <c r="N159" s="182"/>
+      <c r="O159" s="182"/>
+      <c r="P159" s="182"/>
       <c r="Q159" s="6"/>
       <c r="R159" s="90"/>
     </row>
     <row r="160" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A160" s="197"/>
-      <c r="B160" s="234"/>
+      <c r="A160" s="212"/>
+      <c r="B160" s="245"/>
       <c r="C160" s="79" t="s">
         <v>57</v>
       </c>
@@ -7921,27 +7934,27 @@
       <c r="G160" s="135">
         <v>4</v>
       </c>
-      <c r="H160" s="165" t="s">
+      <c r="H160" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I160" s="166"/>
-      <c r="J160" s="166"/>
-      <c r="K160" s="166"/>
-      <c r="L160" s="166"/>
-      <c r="M160" s="166"/>
-      <c r="N160" s="166"/>
-      <c r="O160" s="166"/>
-      <c r="P160" s="166"/>
+      <c r="I160" s="182"/>
+      <c r="J160" s="182"/>
+      <c r="K160" s="182"/>
+      <c r="L160" s="182"/>
+      <c r="M160" s="182"/>
+      <c r="N160" s="182"/>
+      <c r="O160" s="182"/>
+      <c r="P160" s="182"/>
       <c r="Q160" s="6"/>
       <c r="R160" s="90"/>
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A161" s="197"/>
-      <c r="B161" s="234"/>
-      <c r="C161" s="167" t="s">
+      <c r="A161" s="212"/>
+      <c r="B161" s="245"/>
+      <c r="C161" s="183" t="s">
         <v>55</v>
       </c>
-      <c r="D161" s="188">
+      <c r="D161" s="184">
         <v>25</v>
       </c>
       <c r="E161" s="156">
@@ -7953,27 +7966,27 @@
       <c r="G161" s="135">
         <v>30</v>
       </c>
-      <c r="H161" s="165" t="s">
+      <c r="H161" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I161" s="166"/>
-      <c r="J161" s="166"/>
-      <c r="K161" s="166"/>
-      <c r="L161" s="166"/>
-      <c r="M161" s="166"/>
-      <c r="N161" s="166"/>
-      <c r="O161" s="166"/>
-      <c r="P161" s="166"/>
+      <c r="I161" s="182"/>
+      <c r="J161" s="182"/>
+      <c r="K161" s="182"/>
+      <c r="L161" s="182"/>
+      <c r="M161" s="182"/>
+      <c r="N161" s="182"/>
+      <c r="O161" s="182"/>
+      <c r="P161" s="182"/>
       <c r="Q161" s="6" t="s">
         <v>296</v>
       </c>
       <c r="R161" s="90"/>
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A162" s="197"/>
-      <c r="B162" s="234"/>
-      <c r="C162" s="183"/>
-      <c r="D162" s="187"/>
+      <c r="A162" s="212"/>
+      <c r="B162" s="245"/>
+      <c r="C162" s="174"/>
+      <c r="D162" s="176"/>
       <c r="E162" s="155">
         <v>513452003</v>
       </c>
@@ -7983,25 +7996,25 @@
       <c r="G162" s="135">
         <v>31</v>
       </c>
-      <c r="H162" s="165" t="s">
+      <c r="H162" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I162" s="166"/>
-      <c r="J162" s="166"/>
-      <c r="K162" s="166"/>
-      <c r="L162" s="166"/>
-      <c r="M162" s="166"/>
-      <c r="N162" s="166"/>
-      <c r="O162" s="166"/>
-      <c r="P162" s="166"/>
+      <c r="I162" s="182"/>
+      <c r="J162" s="182"/>
+      <c r="K162" s="182"/>
+      <c r="L162" s="182"/>
+      <c r="M162" s="182"/>
+      <c r="N162" s="182"/>
+      <c r="O162" s="182"/>
+      <c r="P162" s="182"/>
       <c r="Q162" s="6" t="s">
         <v>297</v>
       </c>
       <c r="R162" s="90"/>
     </row>
     <row r="163" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="208"/>
-      <c r="B163" s="235"/>
+      <c r="A163" s="227"/>
+      <c r="B163" s="248"/>
       <c r="C163" s="80" t="s">
         <v>68</v>
       </c>
@@ -8017,17 +8030,17 @@
       <c r="G163" s="136">
         <v>26</v>
       </c>
-      <c r="H163" s="194" t="s">
+      <c r="H163" s="186" t="s">
         <v>197</v>
       </c>
-      <c r="I163" s="195"/>
-      <c r="J163" s="195"/>
-      <c r="K163" s="195"/>
-      <c r="L163" s="195"/>
-      <c r="M163" s="195"/>
-      <c r="N163" s="195"/>
-      <c r="O163" s="195"/>
-      <c r="P163" s="195"/>
+      <c r="I163" s="187"/>
+      <c r="J163" s="187"/>
+      <c r="K163" s="187"/>
+      <c r="L163" s="187"/>
+      <c r="M163" s="187"/>
+      <c r="N163" s="187"/>
+      <c r="O163" s="187"/>
+      <c r="P163" s="187"/>
       <c r="Q163" s="96"/>
       <c r="R163" s="95"/>
     </row>
@@ -8053,17 +8066,17 @@
       <c r="G164" s="138">
         <v>5000</v>
       </c>
-      <c r="H164" s="246" t="s">
+      <c r="H164" s="204" t="s">
         <v>197</v>
       </c>
-      <c r="I164" s="247"/>
-      <c r="J164" s="247"/>
-      <c r="K164" s="247"/>
-      <c r="L164" s="247"/>
-      <c r="M164" s="247"/>
-      <c r="N164" s="247"/>
-      <c r="O164" s="247"/>
-      <c r="P164" s="247"/>
+      <c r="I164" s="205"/>
+      <c r="J164" s="205"/>
+      <c r="K164" s="205"/>
+      <c r="L164" s="205"/>
+      <c r="M164" s="205"/>
+      <c r="N164" s="205"/>
+      <c r="O164" s="205"/>
+      <c r="P164" s="205"/>
       <c r="Q164" s="113"/>
       <c r="R164" s="114"/>
     </row>
@@ -8089,34 +8102,34 @@
       <c r="G165" s="138">
         <v>100</v>
       </c>
-      <c r="H165" s="246" t="s">
+      <c r="H165" s="204" t="s">
         <v>197</v>
       </c>
-      <c r="I165" s="247"/>
-      <c r="J165" s="247"/>
-      <c r="K165" s="247"/>
-      <c r="L165" s="247"/>
-      <c r="M165" s="247"/>
-      <c r="N165" s="247"/>
-      <c r="O165" s="247"/>
-      <c r="P165" s="247"/>
+      <c r="I165" s="205"/>
+      <c r="J165" s="205"/>
+      <c r="K165" s="205"/>
+      <c r="L165" s="205"/>
+      <c r="M165" s="205"/>
+      <c r="N165" s="205"/>
+      <c r="O165" s="205"/>
+      <c r="P165" s="205"/>
       <c r="Q165" s="113"/>
       <c r="R165" s="114"/>
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A166" s="196" t="s">
+      <c r="A166" s="211" t="s">
         <v>73</v>
       </c>
-      <c r="B166" s="199" t="s">
+      <c r="B166" s="214" t="s">
         <v>197</v>
       </c>
-      <c r="C166" s="202" t="s">
+      <c r="C166" s="225" t="s">
         <v>74</v>
       </c>
-      <c r="D166" s="264">
+      <c r="D166" s="198">
         <v>124</v>
       </c>
-      <c r="E166" s="214">
+      <c r="E166" s="238">
         <v>510938608</v>
       </c>
       <c r="F166" s="104" t="s">
@@ -8125,56 +8138,56 @@
       <c r="G166" s="134">
         <v>100</v>
       </c>
-      <c r="H166" s="176" t="s">
+      <c r="H166" s="239" t="s">
         <v>347</v>
       </c>
-      <c r="I166" s="177"/>
-      <c r="J166" s="177"/>
-      <c r="K166" s="177"/>
-      <c r="L166" s="177"/>
-      <c r="M166" s="177"/>
-      <c r="N166" s="177"/>
-      <c r="O166" s="177"/>
-      <c r="P166" s="252"/>
+      <c r="I166" s="240"/>
+      <c r="J166" s="240"/>
+      <c r="K166" s="240"/>
+      <c r="L166" s="240"/>
+      <c r="M166" s="240"/>
+      <c r="N166" s="240"/>
+      <c r="O166" s="240"/>
+      <c r="P166" s="241"/>
       <c r="Q166" s="88"/>
       <c r="R166" s="89"/>
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A167" s="197"/>
-      <c r="B167" s="200"/>
-      <c r="C167" s="183"/>
-      <c r="D167" s="187"/>
-      <c r="E167" s="182"/>
+      <c r="A167" s="212"/>
+      <c r="B167" s="215"/>
+      <c r="C167" s="174"/>
+      <c r="D167" s="176"/>
+      <c r="E167" s="178"/>
       <c r="F167" s="10" t="s">
         <v>299</v>
       </c>
       <c r="G167" s="135">
         <v>200</v>
       </c>
-      <c r="H167" s="180"/>
-      <c r="I167" s="181"/>
-      <c r="J167" s="181"/>
-      <c r="K167" s="181"/>
-      <c r="L167" s="181"/>
-      <c r="M167" s="181"/>
-      <c r="N167" s="181"/>
-      <c r="O167" s="181"/>
-      <c r="P167" s="253"/>
+      <c r="H167" s="242"/>
+      <c r="I167" s="243"/>
+      <c r="J167" s="243"/>
+      <c r="K167" s="243"/>
+      <c r="L167" s="243"/>
+      <c r="M167" s="243"/>
+      <c r="N167" s="243"/>
+      <c r="O167" s="243"/>
+      <c r="P167" s="244"/>
       <c r="Q167" s="6"/>
       <c r="R167" s="90"/>
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A168" s="197"/>
-      <c r="B168" s="234" t="s">
+      <c r="A168" s="212"/>
+      <c r="B168" s="245" t="s">
         <v>133</v>
       </c>
-      <c r="C168" s="167" t="s">
+      <c r="C168" s="183" t="s">
         <v>75</v>
       </c>
-      <c r="D168" s="188">
+      <c r="D168" s="184">
         <v>123</v>
       </c>
-      <c r="E168" s="169">
+      <c r="E168" s="185">
         <v>520023094</v>
       </c>
       <c r="F168" s="10" t="s">
@@ -8183,69 +8196,69 @@
       <c r="G168" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="H168" s="165" t="s">
+      <c r="H168" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I168" s="166"/>
-      <c r="J168" s="166"/>
-      <c r="K168" s="166"/>
-      <c r="L168" s="166"/>
-      <c r="M168" s="166"/>
-      <c r="N168" s="166"/>
-      <c r="O168" s="166"/>
-      <c r="P168" s="166"/>
+      <c r="I168" s="182"/>
+      <c r="J168" s="182"/>
+      <c r="K168" s="182"/>
+      <c r="L168" s="182"/>
+      <c r="M168" s="182"/>
+      <c r="N168" s="182"/>
+      <c r="O168" s="182"/>
+      <c r="P168" s="182"/>
       <c r="Q168" s="6"/>
       <c r="R168" s="90"/>
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A169" s="197"/>
-      <c r="B169" s="234"/>
-      <c r="C169" s="168"/>
-      <c r="D169" s="186"/>
-      <c r="E169" s="170"/>
+      <c r="A169" s="212"/>
+      <c r="B169" s="245"/>
+      <c r="C169" s="173"/>
+      <c r="D169" s="175"/>
+      <c r="E169" s="177"/>
       <c r="F169" s="10" t="s">
         <v>303</v>
       </c>
       <c r="G169" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="H169" s="165" t="s">
+      <c r="H169" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I169" s="166"/>
-      <c r="J169" s="166"/>
-      <c r="K169" s="166"/>
-      <c r="L169" s="166"/>
-      <c r="M169" s="166"/>
-      <c r="N169" s="166"/>
-      <c r="O169" s="166"/>
-      <c r="P169" s="166"/>
+      <c r="I169" s="182"/>
+      <c r="J169" s="182"/>
+      <c r="K169" s="182"/>
+      <c r="L169" s="182"/>
+      <c r="M169" s="182"/>
+      <c r="N169" s="182"/>
+      <c r="O169" s="182"/>
+      <c r="P169" s="182"/>
       <c r="Q169" s="6"/>
       <c r="R169" s="90"/>
     </row>
     <row r="170" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="198"/>
-      <c r="B170" s="236"/>
-      <c r="C170" s="254"/>
-      <c r="D170" s="265"/>
-      <c r="E170" s="255"/>
+      <c r="A170" s="213"/>
+      <c r="B170" s="246"/>
+      <c r="C170" s="223"/>
+      <c r="D170" s="195"/>
+      <c r="E170" s="247"/>
       <c r="F170" s="92" t="s">
         <v>304</v>
       </c>
       <c r="G170" s="106" t="s">
         <v>132</v>
       </c>
-      <c r="H170" s="222" t="s">
+      <c r="H170" s="208" t="s">
         <v>197</v>
       </c>
-      <c r="I170" s="223"/>
-      <c r="J170" s="223"/>
-      <c r="K170" s="223"/>
-      <c r="L170" s="223"/>
-      <c r="M170" s="223"/>
-      <c r="N170" s="223"/>
-      <c r="O170" s="223"/>
-      <c r="P170" s="223"/>
+      <c r="I170" s="209"/>
+      <c r="J170" s="209"/>
+      <c r="K170" s="209"/>
+      <c r="L170" s="209"/>
+      <c r="M170" s="209"/>
+      <c r="N170" s="209"/>
+      <c r="O170" s="209"/>
+      <c r="P170" s="209"/>
       <c r="Q170" s="120"/>
       <c r="R170" s="93"/>
     </row>
@@ -8271,17 +8284,17 @@
       <c r="G171" s="138">
         <v>100</v>
       </c>
-      <c r="H171" s="246" t="s">
+      <c r="H171" s="204" t="s">
         <v>197</v>
       </c>
-      <c r="I171" s="247"/>
-      <c r="J171" s="247"/>
-      <c r="K171" s="247"/>
-      <c r="L171" s="247"/>
-      <c r="M171" s="247"/>
-      <c r="N171" s="247"/>
-      <c r="O171" s="247"/>
-      <c r="P171" s="247"/>
+      <c r="I171" s="205"/>
+      <c r="J171" s="205"/>
+      <c r="K171" s="205"/>
+      <c r="L171" s="205"/>
+      <c r="M171" s="205"/>
+      <c r="N171" s="205"/>
+      <c r="O171" s="205"/>
+      <c r="P171" s="205"/>
       <c r="Q171" s="113"/>
       <c r="R171" s="114"/>
     </row>
@@ -8307,34 +8320,34 @@
       <c r="G172" s="138">
         <v>100</v>
       </c>
-      <c r="H172" s="249" t="s">
+      <c r="H172" s="235" t="s">
         <v>347</v>
       </c>
-      <c r="I172" s="250"/>
-      <c r="J172" s="250"/>
-      <c r="K172" s="250"/>
-      <c r="L172" s="250"/>
-      <c r="M172" s="250"/>
-      <c r="N172" s="250"/>
-      <c r="O172" s="250"/>
-      <c r="P172" s="251"/>
+      <c r="I172" s="236"/>
+      <c r="J172" s="236"/>
+      <c r="K172" s="236"/>
+      <c r="L172" s="236"/>
+      <c r="M172" s="236"/>
+      <c r="N172" s="236"/>
+      <c r="O172" s="236"/>
+      <c r="P172" s="237"/>
       <c r="Q172" s="113"/>
       <c r="R172" s="114"/>
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A173" s="240" t="s">
+      <c r="A173" s="228" t="s">
         <v>197</v>
       </c>
-      <c r="B173" s="243" t="s">
+      <c r="B173" s="231" t="s">
         <v>197</v>
       </c>
-      <c r="C173" s="183" t="s">
+      <c r="C173" s="174" t="s">
         <v>78</v>
       </c>
-      <c r="D173" s="187">
+      <c r="D173" s="176">
         <v>1156</v>
       </c>
-      <c r="E173" s="182">
+      <c r="E173" s="178">
         <v>520042177</v>
       </c>
       <c r="F173" s="10" t="s">
@@ -8343,121 +8356,121 @@
       <c r="G173" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="H173" s="165" t="s">
+      <c r="H173" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I173" s="166"/>
-      <c r="J173" s="166"/>
-      <c r="K173" s="166"/>
-      <c r="L173" s="166"/>
-      <c r="M173" s="166"/>
-      <c r="N173" s="166"/>
-      <c r="O173" s="166"/>
-      <c r="P173" s="166"/>
+      <c r="I173" s="182"/>
+      <c r="J173" s="182"/>
+      <c r="K173" s="182"/>
+      <c r="L173" s="182"/>
+      <c r="M173" s="182"/>
+      <c r="N173" s="182"/>
+      <c r="O173" s="182"/>
+      <c r="P173" s="182"/>
       <c r="Q173" s="85"/>
       <c r="R173" s="116"/>
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A174" s="241"/>
-      <c r="B174" s="244"/>
-      <c r="C174" s="168"/>
-      <c r="D174" s="186"/>
-      <c r="E174" s="170"/>
+      <c r="A174" s="229"/>
+      <c r="B174" s="232"/>
+      <c r="C174" s="173"/>
+      <c r="D174" s="175"/>
+      <c r="E174" s="177"/>
       <c r="F174" s="10" t="s">
         <v>362</v>
       </c>
       <c r="G174" s="8">
         <v>925932</v>
       </c>
-      <c r="H174" s="165" t="s">
+      <c r="H174" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I174" s="166"/>
-      <c r="J174" s="166"/>
-      <c r="K174" s="166"/>
-      <c r="L174" s="166"/>
-      <c r="M174" s="166"/>
-      <c r="N174" s="166"/>
-      <c r="O174" s="166"/>
-      <c r="P174" s="166"/>
+      <c r="I174" s="182"/>
+      <c r="J174" s="182"/>
+      <c r="K174" s="182"/>
+      <c r="L174" s="182"/>
+      <c r="M174" s="182"/>
+      <c r="N174" s="182"/>
+      <c r="O174" s="182"/>
+      <c r="P174" s="182"/>
       <c r="Q174" s="130"/>
       <c r="R174" s="131"/>
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A175" s="241"/>
-      <c r="B175" s="244"/>
-      <c r="C175" s="168"/>
-      <c r="D175" s="186"/>
-      <c r="E175" s="170"/>
+      <c r="A175" s="229"/>
+      <c r="B175" s="232"/>
+      <c r="C175" s="173"/>
+      <c r="D175" s="175"/>
+      <c r="E175" s="177"/>
       <c r="F175" s="10" t="s">
         <v>363</v>
       </c>
       <c r="G175" s="8">
         <v>925933</v>
       </c>
-      <c r="H175" s="165" t="s">
+      <c r="H175" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I175" s="166"/>
-      <c r="J175" s="166"/>
-      <c r="K175" s="166"/>
-      <c r="L175" s="166"/>
-      <c r="M175" s="166"/>
-      <c r="N175" s="166"/>
-      <c r="O175" s="166"/>
-      <c r="P175" s="166"/>
+      <c r="I175" s="182"/>
+      <c r="J175" s="182"/>
+      <c r="K175" s="182"/>
+      <c r="L175" s="182"/>
+      <c r="M175" s="182"/>
+      <c r="N175" s="182"/>
+      <c r="O175" s="182"/>
+      <c r="P175" s="182"/>
       <c r="Q175" s="130"/>
       <c r="R175" s="131"/>
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A176" s="241"/>
-      <c r="B176" s="244"/>
-      <c r="C176" s="168"/>
-      <c r="D176" s="186"/>
-      <c r="E176" s="170"/>
+      <c r="A176" s="229"/>
+      <c r="B176" s="232"/>
+      <c r="C176" s="173"/>
+      <c r="D176" s="175"/>
+      <c r="E176" s="177"/>
       <c r="F176" s="10" t="s">
         <v>364</v>
       </c>
       <c r="G176" s="8">
         <v>925931</v>
       </c>
-      <c r="H176" s="165" t="s">
+      <c r="H176" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I176" s="166"/>
-      <c r="J176" s="166"/>
-      <c r="K176" s="166"/>
-      <c r="L176" s="166"/>
-      <c r="M176" s="166"/>
-      <c r="N176" s="166"/>
-      <c r="O176" s="166"/>
-      <c r="P176" s="166"/>
+      <c r="I176" s="182"/>
+      <c r="J176" s="182"/>
+      <c r="K176" s="182"/>
+      <c r="L176" s="182"/>
+      <c r="M176" s="182"/>
+      <c r="N176" s="182"/>
+      <c r="O176" s="182"/>
+      <c r="P176" s="182"/>
       <c r="Q176" s="130"/>
       <c r="R176" s="131"/>
     </row>
     <row r="177" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="242"/>
-      <c r="B177" s="245"/>
-      <c r="C177" s="205"/>
-      <c r="D177" s="266"/>
-      <c r="E177" s="225"/>
+      <c r="A177" s="230"/>
+      <c r="B177" s="233"/>
+      <c r="C177" s="219"/>
+      <c r="D177" s="201"/>
+      <c r="E177" s="222"/>
       <c r="F177" s="10" t="s">
         <v>365</v>
       </c>
       <c r="G177" s="8">
         <v>926150</v>
       </c>
-      <c r="H177" s="165" t="s">
+      <c r="H177" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I177" s="166"/>
-      <c r="J177" s="166"/>
-      <c r="K177" s="166"/>
-      <c r="L177" s="166"/>
-      <c r="M177" s="166"/>
-      <c r="N177" s="166"/>
-      <c r="O177" s="166"/>
-      <c r="P177" s="166"/>
+      <c r="I177" s="182"/>
+      <c r="J177" s="182"/>
+      <c r="K177" s="182"/>
+      <c r="L177" s="182"/>
+      <c r="M177" s="182"/>
+      <c r="N177" s="182"/>
+      <c r="O177" s="182"/>
+      <c r="P177" s="182"/>
       <c r="Q177" s="102"/>
       <c r="R177" s="93"/>
     </row>
@@ -8483,31 +8496,31 @@
       <c r="G178" s="138" t="s">
         <v>135</v>
       </c>
-      <c r="H178" s="246" t="s">
+      <c r="H178" s="204" t="s">
         <v>197</v>
       </c>
-      <c r="I178" s="247"/>
-      <c r="J178" s="247"/>
-      <c r="K178" s="247"/>
-      <c r="L178" s="247"/>
-      <c r="M178" s="247"/>
-      <c r="N178" s="247"/>
-      <c r="O178" s="247"/>
-      <c r="P178" s="248"/>
+      <c r="I178" s="205"/>
+      <c r="J178" s="205"/>
+      <c r="K178" s="205"/>
+      <c r="L178" s="205"/>
+      <c r="M178" s="205"/>
+      <c r="N178" s="205"/>
+      <c r="O178" s="205"/>
+      <c r="P178" s="234"/>
       <c r="Q178" s="123"/>
       <c r="R178" s="124"/>
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A179" s="196" t="s">
+      <c r="A179" s="211" t="s">
         <v>80</v>
       </c>
-      <c r="B179" s="199" t="s">
+      <c r="B179" s="214" t="s">
         <v>197</v>
       </c>
-      <c r="C179" s="275" t="s">
+      <c r="C179" s="199" t="s">
         <v>81</v>
       </c>
-      <c r="D179" s="264">
+      <c r="D179" s="198">
         <v>130</v>
       </c>
       <c r="E179" s="158">
@@ -8519,25 +8532,25 @@
       <c r="G179" s="133" t="s">
         <v>136</v>
       </c>
-      <c r="H179" s="262" t="s">
+      <c r="H179" s="179" t="s">
         <v>197</v>
       </c>
-      <c r="I179" s="263"/>
-      <c r="J179" s="263"/>
-      <c r="K179" s="263"/>
-      <c r="L179" s="263"/>
-      <c r="M179" s="263"/>
-      <c r="N179" s="263"/>
-      <c r="O179" s="263"/>
-      <c r="P179" s="263"/>
+      <c r="I179" s="180"/>
+      <c r="J179" s="180"/>
+      <c r="K179" s="180"/>
+      <c r="L179" s="180"/>
+      <c r="M179" s="180"/>
+      <c r="N179" s="180"/>
+      <c r="O179" s="180"/>
+      <c r="P179" s="180"/>
       <c r="Q179" s="88"/>
       <c r="R179" s="89"/>
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A180" s="256"/>
-      <c r="B180" s="257"/>
-      <c r="C180" s="184"/>
-      <c r="D180" s="186"/>
+      <c r="A180" s="226"/>
+      <c r="B180" s="167"/>
+      <c r="C180" s="196"/>
+      <c r="D180" s="175"/>
       <c r="E180" s="156">
         <v>513026484</v>
       </c>
@@ -8547,25 +8560,25 @@
       <c r="G180" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="H180" s="165" t="s">
+      <c r="H180" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I180" s="166"/>
-      <c r="J180" s="166"/>
-      <c r="K180" s="166"/>
-      <c r="L180" s="166"/>
-      <c r="M180" s="166"/>
-      <c r="N180" s="166"/>
-      <c r="O180" s="166"/>
-      <c r="P180" s="166"/>
+      <c r="I180" s="182"/>
+      <c r="J180" s="182"/>
+      <c r="K180" s="182"/>
+      <c r="L180" s="182"/>
+      <c r="M180" s="182"/>
+      <c r="N180" s="182"/>
+      <c r="O180" s="182"/>
+      <c r="P180" s="182"/>
       <c r="Q180" s="85"/>
       <c r="R180" s="116"/>
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A181" s="256"/>
-      <c r="B181" s="257"/>
-      <c r="C181" s="184"/>
-      <c r="D181" s="186"/>
+      <c r="A181" s="226"/>
+      <c r="B181" s="167"/>
+      <c r="C181" s="196"/>
+      <c r="D181" s="175"/>
       <c r="E181" s="156">
         <v>520017450</v>
       </c>
@@ -8575,25 +8588,25 @@
       <c r="G181" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="H181" s="165" t="s">
+      <c r="H181" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I181" s="166"/>
-      <c r="J181" s="166"/>
-      <c r="K181" s="166"/>
-      <c r="L181" s="166"/>
-      <c r="M181" s="166"/>
-      <c r="N181" s="166"/>
-      <c r="O181" s="166"/>
-      <c r="P181" s="166"/>
+      <c r="I181" s="182"/>
+      <c r="J181" s="182"/>
+      <c r="K181" s="182"/>
+      <c r="L181" s="182"/>
+      <c r="M181" s="182"/>
+      <c r="N181" s="182"/>
+      <c r="O181" s="182"/>
+      <c r="P181" s="182"/>
       <c r="Q181" s="85"/>
       <c r="R181" s="116"/>
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A182" s="256"/>
-      <c r="B182" s="257"/>
-      <c r="C182" s="185"/>
-      <c r="D182" s="187"/>
+      <c r="A182" s="226"/>
+      <c r="B182" s="167"/>
+      <c r="C182" s="194"/>
+      <c r="D182" s="176"/>
       <c r="E182" s="156">
         <v>520023185</v>
       </c>
@@ -8603,27 +8616,27 @@
       <c r="G182" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="H182" s="165" t="s">
+      <c r="H182" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I182" s="166"/>
-      <c r="J182" s="166"/>
-      <c r="K182" s="166"/>
-      <c r="L182" s="166"/>
-      <c r="M182" s="166"/>
-      <c r="N182" s="166"/>
-      <c r="O182" s="166"/>
-      <c r="P182" s="166"/>
+      <c r="I182" s="182"/>
+      <c r="J182" s="182"/>
+      <c r="K182" s="182"/>
+      <c r="L182" s="182"/>
+      <c r="M182" s="182"/>
+      <c r="N182" s="182"/>
+      <c r="O182" s="182"/>
+      <c r="P182" s="182"/>
       <c r="Q182" s="85"/>
       <c r="R182" s="116"/>
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A183" s="256"/>
-      <c r="B183" s="257"/>
-      <c r="C183" s="273" t="s">
+      <c r="A183" s="226"/>
+      <c r="B183" s="167"/>
+      <c r="C183" s="193" t="s">
         <v>82</v>
       </c>
-      <c r="D183" s="188">
+      <c r="D183" s="184">
         <v>1165</v>
       </c>
       <c r="E183" s="156">
@@ -8635,25 +8648,25 @@
       <c r="G183" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="H183" s="165" t="s">
+      <c r="H183" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I183" s="166"/>
-      <c r="J183" s="166"/>
-      <c r="K183" s="166"/>
-      <c r="L183" s="166"/>
-      <c r="M183" s="166"/>
-      <c r="N183" s="166"/>
-      <c r="O183" s="166"/>
-      <c r="P183" s="166"/>
+      <c r="I183" s="182"/>
+      <c r="J183" s="182"/>
+      <c r="K183" s="182"/>
+      <c r="L183" s="182"/>
+      <c r="M183" s="182"/>
+      <c r="N183" s="182"/>
+      <c r="O183" s="182"/>
+      <c r="P183" s="182"/>
       <c r="Q183" s="85"/>
       <c r="R183" s="116"/>
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A184" s="256"/>
-      <c r="B184" s="257"/>
-      <c r="C184" s="184"/>
-      <c r="D184" s="186"/>
+      <c r="A184" s="226"/>
+      <c r="B184" s="167"/>
+      <c r="C184" s="196"/>
+      <c r="D184" s="175"/>
       <c r="E184" s="156">
         <v>540300019</v>
       </c>
@@ -8663,25 +8676,25 @@
       <c r="G184" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="H184" s="165" t="s">
+      <c r="H184" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I184" s="166"/>
-      <c r="J184" s="166"/>
-      <c r="K184" s="166"/>
-      <c r="L184" s="166"/>
-      <c r="M184" s="166"/>
-      <c r="N184" s="166"/>
-      <c r="O184" s="166"/>
-      <c r="P184" s="166"/>
+      <c r="I184" s="182"/>
+      <c r="J184" s="182"/>
+      <c r="K184" s="182"/>
+      <c r="L184" s="182"/>
+      <c r="M184" s="182"/>
+      <c r="N184" s="182"/>
+      <c r="O184" s="182"/>
+      <c r="P184" s="182"/>
       <c r="Q184" s="85"/>
       <c r="R184" s="116"/>
     </row>
     <row r="185" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A185" s="256"/>
-      <c r="B185" s="257"/>
-      <c r="C185" s="184"/>
-      <c r="D185" s="186"/>
+      <c r="A185" s="226"/>
+      <c r="B185" s="167"/>
+      <c r="C185" s="196"/>
+      <c r="D185" s="175"/>
       <c r="E185" s="156">
         <v>540253267</v>
       </c>
@@ -8691,25 +8704,25 @@
       <c r="G185" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="H185" s="165" t="s">
+      <c r="H185" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I185" s="166"/>
-      <c r="J185" s="166"/>
-      <c r="K185" s="166"/>
-      <c r="L185" s="166"/>
-      <c r="M185" s="166"/>
-      <c r="N185" s="166"/>
-      <c r="O185" s="166"/>
-      <c r="P185" s="166"/>
+      <c r="I185" s="182"/>
+      <c r="J185" s="182"/>
+      <c r="K185" s="182"/>
+      <c r="L185" s="182"/>
+      <c r="M185" s="182"/>
+      <c r="N185" s="182"/>
+      <c r="O185" s="182"/>
+      <c r="P185" s="182"/>
       <c r="Q185" s="85"/>
       <c r="R185" s="116"/>
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A186" s="256"/>
-      <c r="B186" s="257"/>
-      <c r="C186" s="184"/>
-      <c r="D186" s="186"/>
+      <c r="A186" s="226"/>
+      <c r="B186" s="167"/>
+      <c r="C186" s="196"/>
+      <c r="D186" s="175"/>
       <c r="E186" s="156">
         <v>540263498</v>
       </c>
@@ -8719,25 +8732,25 @@
       <c r="G186" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="H186" s="165" t="s">
+      <c r="H186" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I186" s="166"/>
-      <c r="J186" s="166"/>
-      <c r="K186" s="166"/>
-      <c r="L186" s="166"/>
-      <c r="M186" s="166"/>
-      <c r="N186" s="166"/>
-      <c r="O186" s="166"/>
-      <c r="P186" s="166"/>
+      <c r="I186" s="182"/>
+      <c r="J186" s="182"/>
+      <c r="K186" s="182"/>
+      <c r="L186" s="182"/>
+      <c r="M186" s="182"/>
+      <c r="N186" s="182"/>
+      <c r="O186" s="182"/>
+      <c r="P186" s="182"/>
       <c r="Q186" s="85"/>
       <c r="R186" s="116"/>
     </row>
     <row r="187" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A187" s="256"/>
-      <c r="B187" s="257"/>
-      <c r="C187" s="184"/>
-      <c r="D187" s="186"/>
+      <c r="A187" s="226"/>
+      <c r="B187" s="167"/>
+      <c r="C187" s="196"/>
+      <c r="D187" s="175"/>
       <c r="E187" s="156">
         <v>540265600</v>
       </c>
@@ -8760,10 +8773,10 @@
       <c r="R187" s="116"/>
     </row>
     <row r="188" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A188" s="256"/>
-      <c r="B188" s="257"/>
-      <c r="C188" s="184"/>
-      <c r="D188" s="186"/>
+      <c r="A188" s="226"/>
+      <c r="B188" s="167"/>
+      <c r="C188" s="196"/>
+      <c r="D188" s="175"/>
       <c r="E188" s="156">
         <v>540265568</v>
       </c>
@@ -8782,40 +8795,40 @@
       <c r="R188" s="116"/>
     </row>
     <row r="189" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="197"/>
-      <c r="B189" s="200"/>
-      <c r="C189" s="274"/>
-      <c r="D189" s="265"/>
+      <c r="A189" s="212"/>
+      <c r="B189" s="215"/>
+      <c r="C189" s="197"/>
+      <c r="D189" s="195"/>
       <c r="E189" s="159">
         <v>517030094</v>
       </c>
       <c r="F189" s="148"/>
       <c r="G189" s="149"/>
-      <c r="H189" s="165" t="s">
+      <c r="H189" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I189" s="166"/>
-      <c r="J189" s="166"/>
-      <c r="K189" s="166"/>
-      <c r="L189" s="166"/>
-      <c r="M189" s="166"/>
-      <c r="N189" s="166"/>
-      <c r="O189" s="166"/>
-      <c r="P189" s="166"/>
+      <c r="I189" s="182"/>
+      <c r="J189" s="182"/>
+      <c r="K189" s="182"/>
+      <c r="L189" s="182"/>
+      <c r="M189" s="182"/>
+      <c r="N189" s="182"/>
+      <c r="O189" s="182"/>
+      <c r="P189" s="182"/>
       <c r="Q189" s="6"/>
       <c r="R189" s="90"/>
     </row>
     <row r="190" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A190" s="196" t="s">
+      <c r="A190" s="211" t="s">
         <v>83</v>
       </c>
       <c r="B190" s="83" t="s">
         <v>197</v>
       </c>
-      <c r="C190" s="275" t="s">
+      <c r="C190" s="199" t="s">
         <v>84</v>
       </c>
-      <c r="D190" s="264">
+      <c r="D190" s="198">
         <v>132</v>
       </c>
       <c r="E190" s="158">
@@ -8827,25 +8840,25 @@
       <c r="G190" s="134" t="s">
         <v>145</v>
       </c>
-      <c r="H190" s="238" t="s">
+      <c r="H190" s="206" t="s">
         <v>197</v>
       </c>
-      <c r="I190" s="239"/>
-      <c r="J190" s="239"/>
-      <c r="K190" s="239"/>
-      <c r="L190" s="239"/>
-      <c r="M190" s="239"/>
-      <c r="N190" s="239"/>
-      <c r="O190" s="239"/>
-      <c r="P190" s="239"/>
+      <c r="I190" s="207"/>
+      <c r="J190" s="207"/>
+      <c r="K190" s="207"/>
+      <c r="L190" s="207"/>
+      <c r="M190" s="207"/>
+      <c r="N190" s="207"/>
+      <c r="O190" s="207"/>
+      <c r="P190" s="207"/>
       <c r="Q190" s="88"/>
       <c r="R190" s="89"/>
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A191" s="197"/>
+      <c r="A191" s="212"/>
       <c r="B191" s="1"/>
-      <c r="C191" s="184"/>
-      <c r="D191" s="186"/>
+      <c r="C191" s="196"/>
+      <c r="D191" s="175"/>
       <c r="E191" s="156">
         <v>540320306</v>
       </c>
@@ -8855,25 +8868,25 @@
       <c r="G191" s="135" t="s">
         <v>146</v>
       </c>
-      <c r="H191" s="165" t="s">
+      <c r="H191" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I191" s="166"/>
-      <c r="J191" s="166"/>
-      <c r="K191" s="166"/>
-      <c r="L191" s="166"/>
-      <c r="M191" s="166"/>
-      <c r="N191" s="166"/>
-      <c r="O191" s="166"/>
-      <c r="P191" s="166"/>
+      <c r="I191" s="182"/>
+      <c r="J191" s="182"/>
+      <c r="K191" s="182"/>
+      <c r="L191" s="182"/>
+      <c r="M191" s="182"/>
+      <c r="N191" s="182"/>
+      <c r="O191" s="182"/>
+      <c r="P191" s="182"/>
       <c r="Q191" s="6"/>
       <c r="R191" s="90"/>
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A192" s="197"/>
+      <c r="A192" s="212"/>
       <c r="B192" s="1"/>
-      <c r="C192" s="184"/>
-      <c r="D192" s="186"/>
+      <c r="C192" s="196"/>
+      <c r="D192" s="175"/>
       <c r="E192" s="156">
         <v>540271947</v>
       </c>
@@ -8892,10 +8905,10 @@
       <c r="R192" s="90"/>
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A193" s="197"/>
+      <c r="A193" s="212"/>
       <c r="B193" s="1"/>
-      <c r="C193" s="184"/>
-      <c r="D193" s="186"/>
+      <c r="C193" s="196"/>
+      <c r="D193" s="175"/>
       <c r="E193" s="156">
         <v>540271491</v>
       </c>
@@ -8914,10 +8927,10 @@
       <c r="R193" s="90"/>
     </row>
     <row r="194" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A194" s="197"/>
+      <c r="A194" s="212"/>
       <c r="B194" s="1"/>
-      <c r="C194" s="184"/>
-      <c r="D194" s="186"/>
+      <c r="C194" s="196"/>
+      <c r="D194" s="175"/>
       <c r="E194" s="156">
         <v>512244146</v>
       </c>
@@ -8936,10 +8949,10 @@
       <c r="R194" s="90"/>
     </row>
     <row r="195" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A195" s="197"/>
+      <c r="A195" s="212"/>
       <c r="B195" s="1"/>
-      <c r="C195" s="185"/>
-      <c r="D195" s="187"/>
+      <c r="C195" s="194"/>
+      <c r="D195" s="176"/>
       <c r="E195" s="156">
         <v>540340379</v>
       </c>
@@ -8958,7 +8971,7 @@
       <c r="R195" s="90"/>
     </row>
     <row r="196" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A196" s="197"/>
+      <c r="A196" s="212"/>
       <c r="B196" s="1" t="s">
         <v>197</v>
       </c>
@@ -8977,22 +8990,22 @@
       <c r="G196" s="135" t="s">
         <v>153</v>
       </c>
-      <c r="H196" s="165" t="s">
+      <c r="H196" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I196" s="166"/>
-      <c r="J196" s="166"/>
-      <c r="K196" s="166"/>
-      <c r="L196" s="166"/>
-      <c r="M196" s="166"/>
-      <c r="N196" s="166"/>
-      <c r="O196" s="166"/>
-      <c r="P196" s="166"/>
+      <c r="I196" s="182"/>
+      <c r="J196" s="182"/>
+      <c r="K196" s="182"/>
+      <c r="L196" s="182"/>
+      <c r="M196" s="182"/>
+      <c r="N196" s="182"/>
+      <c r="O196" s="182"/>
+      <c r="P196" s="182"/>
       <c r="Q196" s="6"/>
       <c r="R196" s="90"/>
     </row>
     <row r="197" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="208"/>
+      <c r="A197" s="227"/>
       <c r="B197" s="11" t="s">
         <v>197</v>
       </c>
@@ -9011,31 +9024,31 @@
       <c r="G197" s="136" t="s">
         <v>154</v>
       </c>
-      <c r="H197" s="194" t="s">
+      <c r="H197" s="186" t="s">
         <v>197</v>
       </c>
-      <c r="I197" s="195"/>
-      <c r="J197" s="195"/>
-      <c r="K197" s="195"/>
-      <c r="L197" s="195"/>
-      <c r="M197" s="195"/>
-      <c r="N197" s="195"/>
-      <c r="O197" s="195"/>
-      <c r="P197" s="195"/>
+      <c r="I197" s="187"/>
+      <c r="J197" s="187"/>
+      <c r="K197" s="187"/>
+      <c r="L197" s="187"/>
+      <c r="M197" s="187"/>
+      <c r="N197" s="187"/>
+      <c r="O197" s="187"/>
+      <c r="P197" s="187"/>
       <c r="Q197" s="96"/>
       <c r="R197" s="95"/>
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A198" s="196" t="s">
+      <c r="A198" s="211" t="s">
         <v>87</v>
       </c>
-      <c r="B198" s="199" t="s">
+      <c r="B198" s="214" t="s">
         <v>197</v>
       </c>
-      <c r="C198" s="202" t="s">
+      <c r="C198" s="225" t="s">
         <v>88</v>
       </c>
-      <c r="D198" s="264">
+      <c r="D198" s="198">
         <v>140</v>
       </c>
       <c r="E198" s="158">
@@ -9047,25 +9060,25 @@
       <c r="G198" s="125" t="s">
         <v>155</v>
       </c>
-      <c r="H198" s="238" t="s">
+      <c r="H198" s="206" t="s">
         <v>197</v>
       </c>
-      <c r="I198" s="239"/>
-      <c r="J198" s="239"/>
-      <c r="K198" s="239"/>
-      <c r="L198" s="239"/>
-      <c r="M198" s="239"/>
-      <c r="N198" s="239"/>
-      <c r="O198" s="239"/>
-      <c r="P198" s="239"/>
+      <c r="I198" s="207"/>
+      <c r="J198" s="207"/>
+      <c r="K198" s="207"/>
+      <c r="L198" s="207"/>
+      <c r="M198" s="207"/>
+      <c r="N198" s="207"/>
+      <c r="O198" s="207"/>
+      <c r="P198" s="207"/>
       <c r="Q198" s="88"/>
       <c r="R198" s="89"/>
     </row>
     <row r="199" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A199" s="197"/>
-      <c r="B199" s="200"/>
-      <c r="C199" s="168"/>
-      <c r="D199" s="186"/>
+      <c r="A199" s="212"/>
+      <c r="B199" s="215"/>
+      <c r="C199" s="173"/>
+      <c r="D199" s="175"/>
       <c r="E199" s="156">
         <v>520007469</v>
       </c>
@@ -9075,25 +9088,25 @@
       <c r="G199" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="H199" s="165" t="s">
+      <c r="H199" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I199" s="166"/>
-      <c r="J199" s="166"/>
-      <c r="K199" s="166"/>
-      <c r="L199" s="166"/>
-      <c r="M199" s="166"/>
-      <c r="N199" s="166"/>
-      <c r="O199" s="166"/>
-      <c r="P199" s="166"/>
+      <c r="I199" s="182"/>
+      <c r="J199" s="182"/>
+      <c r="K199" s="182"/>
+      <c r="L199" s="182"/>
+      <c r="M199" s="182"/>
+      <c r="N199" s="182"/>
+      <c r="O199" s="182"/>
+      <c r="P199" s="182"/>
       <c r="Q199" s="6"/>
       <c r="R199" s="90"/>
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A200" s="197"/>
-      <c r="B200" s="200"/>
-      <c r="C200" s="183"/>
-      <c r="D200" s="187"/>
+      <c r="A200" s="212"/>
+      <c r="B200" s="215"/>
+      <c r="C200" s="174"/>
+      <c r="D200" s="176"/>
       <c r="E200" s="156">
         <v>520027715</v>
       </c>
@@ -9103,22 +9116,22 @@
       <c r="G200" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="H200" s="165" t="s">
+      <c r="H200" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I200" s="166"/>
-      <c r="J200" s="166"/>
-      <c r="K200" s="166"/>
-      <c r="L200" s="166"/>
-      <c r="M200" s="166"/>
-      <c r="N200" s="166"/>
-      <c r="O200" s="166"/>
-      <c r="P200" s="166"/>
+      <c r="I200" s="182"/>
+      <c r="J200" s="182"/>
+      <c r="K200" s="182"/>
+      <c r="L200" s="182"/>
+      <c r="M200" s="182"/>
+      <c r="N200" s="182"/>
+      <c r="O200" s="182"/>
+      <c r="P200" s="182"/>
       <c r="Q200" s="6"/>
       <c r="R200" s="90"/>
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A201" s="208"/>
+      <c r="A201" s="227"/>
       <c r="B201" s="11"/>
       <c r="C201" s="143"/>
       <c r="D201" s="144"/>
@@ -9144,7 +9157,7 @@
       <c r="R201" s="95"/>
     </row>
     <row r="202" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="198"/>
+      <c r="A202" s="213"/>
       <c r="B202" s="101" t="s">
         <v>197</v>
       </c>
@@ -9159,31 +9172,31 @@
       </c>
       <c r="F202" s="150"/>
       <c r="G202" s="151"/>
-      <c r="H202" s="222" t="s">
+      <c r="H202" s="208" t="s">
         <v>197</v>
       </c>
-      <c r="I202" s="223"/>
-      <c r="J202" s="223"/>
-      <c r="K202" s="223"/>
-      <c r="L202" s="223"/>
-      <c r="M202" s="223"/>
-      <c r="N202" s="223"/>
-      <c r="O202" s="223"/>
-      <c r="P202" s="223"/>
+      <c r="I202" s="209"/>
+      <c r="J202" s="209"/>
+      <c r="K202" s="209"/>
+      <c r="L202" s="209"/>
+      <c r="M202" s="209"/>
+      <c r="N202" s="209"/>
+      <c r="O202" s="209"/>
+      <c r="P202" s="209"/>
       <c r="Q202" s="102"/>
       <c r="R202" s="93"/>
     </row>
     <row r="203" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A203" s="196" t="s">
+      <c r="A203" s="211" t="s">
         <v>92</v>
       </c>
-      <c r="B203" s="199" t="s">
+      <c r="B203" s="214" t="s">
         <v>197</v>
       </c>
-      <c r="C203" s="202" t="s">
+      <c r="C203" s="225" t="s">
         <v>93</v>
       </c>
-      <c r="D203" s="264">
+      <c r="D203" s="198">
         <v>1159</v>
       </c>
       <c r="E203" s="157">
@@ -9195,25 +9208,25 @@
       <c r="G203" s="134">
         <v>2</v>
       </c>
-      <c r="H203" s="238" t="s">
+      <c r="H203" s="206" t="s">
         <v>197</v>
       </c>
-      <c r="I203" s="239"/>
-      <c r="J203" s="239"/>
-      <c r="K203" s="239"/>
-      <c r="L203" s="239"/>
-      <c r="M203" s="239"/>
-      <c r="N203" s="239"/>
-      <c r="O203" s="239"/>
-      <c r="P203" s="239"/>
+      <c r="I203" s="207"/>
+      <c r="J203" s="207"/>
+      <c r="K203" s="207"/>
+      <c r="L203" s="207"/>
+      <c r="M203" s="207"/>
+      <c r="N203" s="207"/>
+      <c r="O203" s="207"/>
+      <c r="P203" s="207"/>
       <c r="Q203" s="88"/>
       <c r="R203" s="89"/>
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A204" s="197"/>
-      <c r="B204" s="200"/>
-      <c r="C204" s="168"/>
-      <c r="D204" s="186"/>
+      <c r="A204" s="212"/>
+      <c r="B204" s="215"/>
+      <c r="C204" s="173"/>
+      <c r="D204" s="175"/>
       <c r="E204" s="157">
         <v>570009852</v>
       </c>
@@ -9223,25 +9236,25 @@
       <c r="G204" s="135">
         <v>11</v>
       </c>
-      <c r="H204" s="165" t="s">
+      <c r="H204" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I204" s="166"/>
-      <c r="J204" s="166"/>
-      <c r="K204" s="166"/>
-      <c r="L204" s="166"/>
-      <c r="M204" s="166"/>
-      <c r="N204" s="166"/>
-      <c r="O204" s="166"/>
-      <c r="P204" s="166"/>
+      <c r="I204" s="182"/>
+      <c r="J204" s="182"/>
+      <c r="K204" s="182"/>
+      <c r="L204" s="182"/>
+      <c r="M204" s="182"/>
+      <c r="N204" s="182"/>
+      <c r="O204" s="182"/>
+      <c r="P204" s="182"/>
       <c r="Q204" s="6"/>
       <c r="R204" s="90"/>
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A205" s="197"/>
-      <c r="B205" s="200"/>
-      <c r="C205" s="168"/>
-      <c r="D205" s="186"/>
+      <c r="A205" s="212"/>
+      <c r="B205" s="215"/>
+      <c r="C205" s="173"/>
+      <c r="D205" s="175"/>
       <c r="E205" s="157">
         <v>570007476</v>
       </c>
@@ -9251,25 +9264,25 @@
       <c r="G205" s="135">
         <v>18</v>
       </c>
-      <c r="H205" s="165" t="s">
+      <c r="H205" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I205" s="166"/>
-      <c r="J205" s="166"/>
-      <c r="K205" s="166"/>
-      <c r="L205" s="166"/>
-      <c r="M205" s="166"/>
-      <c r="N205" s="166"/>
-      <c r="O205" s="166"/>
-      <c r="P205" s="166"/>
+      <c r="I205" s="182"/>
+      <c r="J205" s="182"/>
+      <c r="K205" s="182"/>
+      <c r="L205" s="182"/>
+      <c r="M205" s="182"/>
+      <c r="N205" s="182"/>
+      <c r="O205" s="182"/>
+      <c r="P205" s="182"/>
       <c r="Q205" s="6"/>
       <c r="R205" s="90"/>
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A206" s="197"/>
-      <c r="B206" s="200"/>
-      <c r="C206" s="183"/>
-      <c r="D206" s="187"/>
+      <c r="A206" s="212"/>
+      <c r="B206" s="215"/>
+      <c r="C206" s="174"/>
+      <c r="D206" s="176"/>
       <c r="E206" s="157">
         <v>570005850</v>
       </c>
@@ -9279,27 +9292,27 @@
       <c r="G206" s="135">
         <v>19</v>
       </c>
-      <c r="H206" s="165" t="s">
+      <c r="H206" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I206" s="166"/>
-      <c r="J206" s="166"/>
-      <c r="K206" s="166"/>
-      <c r="L206" s="166"/>
-      <c r="M206" s="166"/>
-      <c r="N206" s="166"/>
-      <c r="O206" s="166"/>
-      <c r="P206" s="166"/>
+      <c r="I206" s="182"/>
+      <c r="J206" s="182"/>
+      <c r="K206" s="182"/>
+      <c r="L206" s="182"/>
+      <c r="M206" s="182"/>
+      <c r="N206" s="182"/>
+      <c r="O206" s="182"/>
+      <c r="P206" s="182"/>
       <c r="Q206" s="6"/>
       <c r="R206" s="90"/>
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A207" s="197"/>
-      <c r="B207" s="200"/>
-      <c r="C207" s="167" t="s">
+      <c r="A207" s="212"/>
+      <c r="B207" s="215"/>
+      <c r="C207" s="183" t="s">
         <v>94</v>
       </c>
-      <c r="D207" s="188">
+      <c r="D207" s="184">
         <v>1160</v>
       </c>
       <c r="E207" s="157">
@@ -9311,25 +9324,25 @@
       <c r="G207" s="135">
         <v>10</v>
       </c>
-      <c r="H207" s="165" t="s">
+      <c r="H207" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I207" s="166"/>
-      <c r="J207" s="166"/>
-      <c r="K207" s="166"/>
-      <c r="L207" s="166"/>
-      <c r="M207" s="166"/>
-      <c r="N207" s="166"/>
-      <c r="O207" s="166"/>
-      <c r="P207" s="166"/>
+      <c r="I207" s="182"/>
+      <c r="J207" s="182"/>
+      <c r="K207" s="182"/>
+      <c r="L207" s="182"/>
+      <c r="M207" s="182"/>
+      <c r="N207" s="182"/>
+      <c r="O207" s="182"/>
+      <c r="P207" s="182"/>
       <c r="Q207" s="6"/>
       <c r="R207" s="90"/>
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A208" s="197"/>
-      <c r="B208" s="200"/>
-      <c r="C208" s="183"/>
-      <c r="D208" s="187"/>
+      <c r="A208" s="212"/>
+      <c r="B208" s="215"/>
+      <c r="C208" s="174"/>
+      <c r="D208" s="176"/>
       <c r="E208" s="157">
         <v>520020504</v>
       </c>
@@ -9339,27 +9352,27 @@
       <c r="G208" s="135">
         <v>12</v>
       </c>
-      <c r="H208" s="165" t="s">
+      <c r="H208" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I208" s="166"/>
-      <c r="J208" s="166"/>
-      <c r="K208" s="166"/>
-      <c r="L208" s="166"/>
-      <c r="M208" s="166"/>
-      <c r="N208" s="166"/>
-      <c r="O208" s="166"/>
-      <c r="P208" s="166"/>
+      <c r="I208" s="182"/>
+      <c r="J208" s="182"/>
+      <c r="K208" s="182"/>
+      <c r="L208" s="182"/>
+      <c r="M208" s="182"/>
+      <c r="N208" s="182"/>
+      <c r="O208" s="182"/>
+      <c r="P208" s="182"/>
       <c r="Q208" s="6"/>
       <c r="R208" s="90"/>
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A209" s="197"/>
-      <c r="B209" s="200"/>
-      <c r="C209" s="167" t="s">
+      <c r="A209" s="212"/>
+      <c r="B209" s="215"/>
+      <c r="C209" s="183" t="s">
         <v>95</v>
       </c>
-      <c r="D209" s="188">
+      <c r="D209" s="184">
         <v>1161</v>
       </c>
       <c r="E209" s="157">
@@ -9371,25 +9384,25 @@
       <c r="G209" s="135">
         <v>1</v>
       </c>
-      <c r="H209" s="165" t="s">
+      <c r="H209" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I209" s="166"/>
-      <c r="J209" s="166"/>
-      <c r="K209" s="166"/>
-      <c r="L209" s="166"/>
-      <c r="M209" s="166"/>
-      <c r="N209" s="166"/>
-      <c r="O209" s="166"/>
-      <c r="P209" s="166"/>
+      <c r="I209" s="182"/>
+      <c r="J209" s="182"/>
+      <c r="K209" s="182"/>
+      <c r="L209" s="182"/>
+      <c r="M209" s="182"/>
+      <c r="N209" s="182"/>
+      <c r="O209" s="182"/>
+      <c r="P209" s="182"/>
       <c r="Q209" s="6"/>
       <c r="R209" s="90"/>
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A210" s="197"/>
-      <c r="B210" s="200"/>
-      <c r="C210" s="168"/>
-      <c r="D210" s="186"/>
+      <c r="A210" s="212"/>
+      <c r="B210" s="215"/>
+      <c r="C210" s="173"/>
+      <c r="D210" s="175"/>
       <c r="E210" s="157">
         <v>520022963</v>
       </c>
@@ -9399,25 +9412,25 @@
       <c r="G210" s="135">
         <v>6</v>
       </c>
-      <c r="H210" s="165" t="s">
+      <c r="H210" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I210" s="166"/>
-      <c r="J210" s="166"/>
-      <c r="K210" s="166"/>
-      <c r="L210" s="166"/>
-      <c r="M210" s="166"/>
-      <c r="N210" s="166"/>
-      <c r="O210" s="166"/>
-      <c r="P210" s="166"/>
+      <c r="I210" s="182"/>
+      <c r="J210" s="182"/>
+      <c r="K210" s="182"/>
+      <c r="L210" s="182"/>
+      <c r="M210" s="182"/>
+      <c r="N210" s="182"/>
+      <c r="O210" s="182"/>
+      <c r="P210" s="182"/>
       <c r="Q210" s="6"/>
       <c r="R210" s="90"/>
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A211" s="197"/>
-      <c r="B211" s="200"/>
-      <c r="C211" s="168"/>
-      <c r="D211" s="186"/>
+      <c r="A211" s="212"/>
+      <c r="B211" s="215"/>
+      <c r="C211" s="173"/>
+      <c r="D211" s="175"/>
       <c r="E211" s="157">
         <v>520020447</v>
       </c>
@@ -9427,25 +9440,25 @@
       <c r="G211" s="135">
         <v>8</v>
       </c>
-      <c r="H211" s="165" t="s">
+      <c r="H211" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I211" s="166"/>
-      <c r="J211" s="166"/>
-      <c r="K211" s="166"/>
-      <c r="L211" s="166"/>
-      <c r="M211" s="166"/>
-      <c r="N211" s="166"/>
-      <c r="O211" s="166"/>
-      <c r="P211" s="166"/>
+      <c r="I211" s="182"/>
+      <c r="J211" s="182"/>
+      <c r="K211" s="182"/>
+      <c r="L211" s="182"/>
+      <c r="M211" s="182"/>
+      <c r="N211" s="182"/>
+      <c r="O211" s="182"/>
+      <c r="P211" s="182"/>
       <c r="Q211" s="6"/>
       <c r="R211" s="90"/>
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A212" s="197"/>
-      <c r="B212" s="200"/>
-      <c r="C212" s="168"/>
-      <c r="D212" s="186"/>
+      <c r="A212" s="212"/>
+      <c r="B212" s="215"/>
+      <c r="C212" s="173"/>
+      <c r="D212" s="175"/>
       <c r="E212" s="157">
         <v>570007476</v>
       </c>
@@ -9455,25 +9468,25 @@
       <c r="G212" s="135">
         <v>14</v>
       </c>
-      <c r="H212" s="165" t="s">
+      <c r="H212" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I212" s="166"/>
-      <c r="J212" s="166"/>
-      <c r="K212" s="166"/>
-      <c r="L212" s="166"/>
-      <c r="M212" s="166"/>
-      <c r="N212" s="166"/>
-      <c r="O212" s="166"/>
-      <c r="P212" s="259"/>
+      <c r="I212" s="182"/>
+      <c r="J212" s="182"/>
+      <c r="K212" s="182"/>
+      <c r="L212" s="182"/>
+      <c r="M212" s="182"/>
+      <c r="N212" s="182"/>
+      <c r="O212" s="182"/>
+      <c r="P212" s="224"/>
       <c r="Q212" s="6"/>
       <c r="R212" s="90"/>
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A213" s="197"/>
-      <c r="B213" s="200"/>
-      <c r="C213" s="168"/>
-      <c r="D213" s="186"/>
+      <c r="A213" s="212"/>
+      <c r="B213" s="215"/>
+      <c r="C213" s="173"/>
+      <c r="D213" s="175"/>
       <c r="E213" s="157">
         <v>570005850</v>
       </c>
@@ -9483,25 +9496,25 @@
       <c r="G213" s="135">
         <v>22</v>
       </c>
-      <c r="H213" s="165" t="s">
+      <c r="H213" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I213" s="166"/>
-      <c r="J213" s="166"/>
-      <c r="K213" s="166"/>
-      <c r="L213" s="166"/>
-      <c r="M213" s="166"/>
-      <c r="N213" s="166"/>
-      <c r="O213" s="166"/>
-      <c r="P213" s="259"/>
+      <c r="I213" s="182"/>
+      <c r="J213" s="182"/>
+      <c r="K213" s="182"/>
+      <c r="L213" s="182"/>
+      <c r="M213" s="182"/>
+      <c r="N213" s="182"/>
+      <c r="O213" s="182"/>
+      <c r="P213" s="224"/>
       <c r="Q213" s="6"/>
       <c r="R213" s="90"/>
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A214" s="197"/>
-      <c r="B214" s="200"/>
-      <c r="C214" s="168"/>
-      <c r="D214" s="186"/>
+      <c r="A214" s="212"/>
+      <c r="B214" s="215"/>
+      <c r="C214" s="173"/>
+      <c r="D214" s="175"/>
       <c r="E214" s="157">
         <v>520020447</v>
       </c>
@@ -9511,25 +9524,25 @@
       <c r="G214" s="135">
         <v>23</v>
       </c>
-      <c r="H214" s="165" t="s">
+      <c r="H214" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I214" s="166"/>
-      <c r="J214" s="166"/>
-      <c r="K214" s="166"/>
-      <c r="L214" s="166"/>
-      <c r="M214" s="166"/>
-      <c r="N214" s="166"/>
-      <c r="O214" s="166"/>
-      <c r="P214" s="259"/>
+      <c r="I214" s="182"/>
+      <c r="J214" s="182"/>
+      <c r="K214" s="182"/>
+      <c r="L214" s="182"/>
+      <c r="M214" s="182"/>
+      <c r="N214" s="182"/>
+      <c r="O214" s="182"/>
+      <c r="P214" s="224"/>
       <c r="Q214" s="6"/>
       <c r="R214" s="90"/>
     </row>
     <row r="215" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="198"/>
-      <c r="B215" s="201"/>
-      <c r="C215" s="254"/>
-      <c r="D215" s="265"/>
+      <c r="A215" s="213"/>
+      <c r="B215" s="216"/>
+      <c r="C215" s="223"/>
+      <c r="D215" s="195"/>
       <c r="E215" s="157">
         <v>520022351</v>
       </c>
@@ -9539,34 +9552,34 @@
       <c r="G215" s="137">
         <v>24</v>
       </c>
-      <c r="H215" s="222" t="s">
+      <c r="H215" s="208" t="s">
         <v>197</v>
       </c>
-      <c r="I215" s="223"/>
-      <c r="J215" s="223"/>
-      <c r="K215" s="223"/>
-      <c r="L215" s="223"/>
-      <c r="M215" s="223"/>
-      <c r="N215" s="223"/>
-      <c r="O215" s="223"/>
-      <c r="P215" s="223"/>
+      <c r="I215" s="209"/>
+      <c r="J215" s="209"/>
+      <c r="K215" s="209"/>
+      <c r="L215" s="209"/>
+      <c r="M215" s="209"/>
+      <c r="N215" s="209"/>
+      <c r="O215" s="209"/>
+      <c r="P215" s="209"/>
       <c r="Q215" s="102"/>
       <c r="R215" s="93"/>
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A216" s="196" t="s">
+      <c r="A216" s="211" t="s">
         <v>197</v>
       </c>
-      <c r="B216" s="199" t="s">
+      <c r="B216" s="214" t="s">
         <v>197</v>
       </c>
-      <c r="C216" s="237" t="s">
+      <c r="C216" s="217" t="s">
         <v>97</v>
       </c>
-      <c r="D216" s="267">
+      <c r="D216" s="210">
         <v>128</v>
       </c>
-      <c r="E216" s="258">
+      <c r="E216" s="220">
         <v>500500376</v>
       </c>
       <c r="F216" s="126" t="s">
@@ -9575,341 +9588,468 @@
       <c r="G216" s="134" t="s">
         <v>166</v>
       </c>
-      <c r="H216" s="238" t="s">
+      <c r="H216" s="206" t="s">
         <v>197</v>
       </c>
-      <c r="I216" s="239"/>
-      <c r="J216" s="239"/>
-      <c r="K216" s="239"/>
-      <c r="L216" s="239"/>
-      <c r="M216" s="239"/>
-      <c r="N216" s="239"/>
-      <c r="O216" s="239"/>
-      <c r="P216" s="239"/>
+      <c r="I216" s="207"/>
+      <c r="J216" s="207"/>
+      <c r="K216" s="207"/>
+      <c r="L216" s="207"/>
+      <c r="M216" s="207"/>
+      <c r="N216" s="207"/>
+      <c r="O216" s="207"/>
+      <c r="P216" s="207"/>
       <c r="Q216" s="88"/>
       <c r="R216" s="89"/>
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A217" s="197"/>
-      <c r="B217" s="200"/>
-      <c r="C217" s="192"/>
-      <c r="D217" s="191"/>
-      <c r="E217" s="193"/>
+      <c r="A217" s="212"/>
+      <c r="B217" s="215"/>
+      <c r="C217" s="218"/>
+      <c r="D217" s="200"/>
+      <c r="E217" s="221"/>
       <c r="F217" s="75" t="s">
         <v>336</v>
       </c>
       <c r="G217" s="135" t="s">
         <v>167</v>
       </c>
-      <c r="H217" s="165" t="s">
+      <c r="H217" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I217" s="166"/>
-      <c r="J217" s="166"/>
-      <c r="K217" s="166"/>
-      <c r="L217" s="166"/>
-      <c r="M217" s="166"/>
-      <c r="N217" s="166"/>
-      <c r="O217" s="166"/>
-      <c r="P217" s="166"/>
+      <c r="I217" s="182"/>
+      <c r="J217" s="182"/>
+      <c r="K217" s="182"/>
+      <c r="L217" s="182"/>
+      <c r="M217" s="182"/>
+      <c r="N217" s="182"/>
+      <c r="O217" s="182"/>
+      <c r="P217" s="182"/>
       <c r="Q217" s="6"/>
       <c r="R217" s="90"/>
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A218" s="197"/>
-      <c r="B218" s="200"/>
-      <c r="C218" s="192"/>
-      <c r="D218" s="191"/>
-      <c r="E218" s="193"/>
+      <c r="A218" s="212"/>
+      <c r="B218" s="215"/>
+      <c r="C218" s="218"/>
+      <c r="D218" s="200"/>
+      <c r="E218" s="221"/>
       <c r="F218" s="75" t="s">
         <v>337</v>
       </c>
       <c r="G218" s="135" t="s">
         <v>168</v>
       </c>
-      <c r="H218" s="165" t="s">
+      <c r="H218" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I218" s="166"/>
-      <c r="J218" s="166"/>
-      <c r="K218" s="166"/>
-      <c r="L218" s="166"/>
-      <c r="M218" s="166"/>
-      <c r="N218" s="166"/>
-      <c r="O218" s="166"/>
-      <c r="P218" s="166"/>
+      <c r="I218" s="182"/>
+      <c r="J218" s="182"/>
+      <c r="K218" s="182"/>
+      <c r="L218" s="182"/>
+      <c r="M218" s="182"/>
+      <c r="N218" s="182"/>
+      <c r="O218" s="182"/>
+      <c r="P218" s="182"/>
       <c r="Q218" s="6"/>
       <c r="R218" s="90"/>
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A219" s="197"/>
-      <c r="B219" s="200"/>
-      <c r="C219" s="192"/>
-      <c r="D219" s="191"/>
-      <c r="E219" s="193"/>
+      <c r="A219" s="212"/>
+      <c r="B219" s="215"/>
+      <c r="C219" s="218"/>
+      <c r="D219" s="200"/>
+      <c r="E219" s="221"/>
       <c r="F219" s="75" t="s">
         <v>337</v>
       </c>
       <c r="G219" s="135" t="s">
         <v>169</v>
       </c>
-      <c r="H219" s="165" t="s">
+      <c r="H219" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I219" s="166"/>
-      <c r="J219" s="166"/>
-      <c r="K219" s="166"/>
-      <c r="L219" s="166"/>
-      <c r="M219" s="166"/>
-      <c r="N219" s="166"/>
-      <c r="O219" s="166"/>
-      <c r="P219" s="166"/>
+      <c r="I219" s="182"/>
+      <c r="J219" s="182"/>
+      <c r="K219" s="182"/>
+      <c r="L219" s="182"/>
+      <c r="M219" s="182"/>
+      <c r="N219" s="182"/>
+      <c r="O219" s="182"/>
+      <c r="P219" s="182"/>
       <c r="Q219" s="6"/>
       <c r="R219" s="90"/>
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A220" s="197"/>
-      <c r="B220" s="200"/>
-      <c r="C220" s="192"/>
-      <c r="D220" s="191"/>
-      <c r="E220" s="193"/>
+      <c r="A220" s="212"/>
+      <c r="B220" s="215"/>
+      <c r="C220" s="218"/>
+      <c r="D220" s="200"/>
+      <c r="E220" s="221"/>
       <c r="F220" s="75" t="s">
         <v>338</v>
       </c>
       <c r="G220" s="135" t="s">
         <v>170</v>
       </c>
-      <c r="H220" s="165" t="s">
+      <c r="H220" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I220" s="166"/>
-      <c r="J220" s="166"/>
-      <c r="K220" s="166"/>
-      <c r="L220" s="166"/>
-      <c r="M220" s="166"/>
-      <c r="N220" s="166"/>
-      <c r="O220" s="166"/>
-      <c r="P220" s="166"/>
+      <c r="I220" s="182"/>
+      <c r="J220" s="182"/>
+      <c r="K220" s="182"/>
+      <c r="L220" s="182"/>
+      <c r="M220" s="182"/>
+      <c r="N220" s="182"/>
+      <c r="O220" s="182"/>
+      <c r="P220" s="182"/>
       <c r="Q220" s="6"/>
       <c r="R220" s="90"/>
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A221" s="197"/>
-      <c r="B221" s="200"/>
-      <c r="C221" s="192"/>
-      <c r="D221" s="191"/>
-      <c r="E221" s="193"/>
+      <c r="A221" s="212"/>
+      <c r="B221" s="215"/>
+      <c r="C221" s="218"/>
+      <c r="D221" s="200"/>
+      <c r="E221" s="221"/>
       <c r="F221" s="75" t="s">
         <v>339</v>
       </c>
       <c r="G221" s="135" t="s">
         <v>171</v>
       </c>
-      <c r="H221" s="165" t="s">
+      <c r="H221" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I221" s="166"/>
-      <c r="J221" s="166"/>
-      <c r="K221" s="166"/>
-      <c r="L221" s="166"/>
-      <c r="M221" s="166"/>
-      <c r="N221" s="166"/>
-      <c r="O221" s="166"/>
-      <c r="P221" s="166"/>
+      <c r="I221" s="182"/>
+      <c r="J221" s="182"/>
+      <c r="K221" s="182"/>
+      <c r="L221" s="182"/>
+      <c r="M221" s="182"/>
+      <c r="N221" s="182"/>
+      <c r="O221" s="182"/>
+      <c r="P221" s="182"/>
       <c r="Q221" s="6"/>
       <c r="R221" s="90"/>
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A222" s="197"/>
-      <c r="B222" s="200"/>
-      <c r="C222" s="192"/>
-      <c r="D222" s="191"/>
-      <c r="E222" s="193"/>
+      <c r="A222" s="212"/>
+      <c r="B222" s="215"/>
+      <c r="C222" s="218"/>
+      <c r="D222" s="200"/>
+      <c r="E222" s="221"/>
       <c r="F222" s="75" t="s">
         <v>340</v>
       </c>
       <c r="G222" s="135" t="s">
         <v>172</v>
       </c>
-      <c r="H222" s="165" t="s">
+      <c r="H222" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I222" s="166"/>
-      <c r="J222" s="166"/>
-      <c r="K222" s="166"/>
-      <c r="L222" s="166"/>
-      <c r="M222" s="166"/>
-      <c r="N222" s="166"/>
-      <c r="O222" s="166"/>
-      <c r="P222" s="166"/>
+      <c r="I222" s="182"/>
+      <c r="J222" s="182"/>
+      <c r="K222" s="182"/>
+      <c r="L222" s="182"/>
+      <c r="M222" s="182"/>
+      <c r="N222" s="182"/>
+      <c r="O222" s="182"/>
+      <c r="P222" s="182"/>
       <c r="Q222" s="6"/>
       <c r="R222" s="90"/>
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A223" s="197"/>
-      <c r="B223" s="200"/>
-      <c r="C223" s="192"/>
-      <c r="D223" s="191"/>
-      <c r="E223" s="193"/>
+      <c r="A223" s="212"/>
+      <c r="B223" s="215"/>
+      <c r="C223" s="218"/>
+      <c r="D223" s="200"/>
+      <c r="E223" s="221"/>
       <c r="F223" s="75" t="s">
         <v>341</v>
       </c>
       <c r="G223" s="135" t="s">
         <v>173</v>
       </c>
-      <c r="H223" s="165" t="s">
+      <c r="H223" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I223" s="166"/>
-      <c r="J223" s="166"/>
-      <c r="K223" s="166"/>
-      <c r="L223" s="166"/>
-      <c r="M223" s="166"/>
-      <c r="N223" s="166"/>
-      <c r="O223" s="166"/>
-      <c r="P223" s="166"/>
+      <c r="I223" s="182"/>
+      <c r="J223" s="182"/>
+      <c r="K223" s="182"/>
+      <c r="L223" s="182"/>
+      <c r="M223" s="182"/>
+      <c r="N223" s="182"/>
+      <c r="O223" s="182"/>
+      <c r="P223" s="182"/>
       <c r="Q223" s="6"/>
       <c r="R223" s="90"/>
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A224" s="197"/>
-      <c r="B224" s="200"/>
-      <c r="C224" s="192"/>
-      <c r="D224" s="191"/>
-      <c r="E224" s="193"/>
+      <c r="A224" s="212"/>
+      <c r="B224" s="215"/>
+      <c r="C224" s="218"/>
+      <c r="D224" s="200"/>
+      <c r="E224" s="221"/>
       <c r="F224" s="75" t="s">
         <v>342</v>
       </c>
       <c r="G224" s="135" t="s">
         <v>174</v>
       </c>
-      <c r="H224" s="165" t="s">
+      <c r="H224" s="181" t="s">
         <v>197</v>
       </c>
-      <c r="I224" s="166"/>
-      <c r="J224" s="166"/>
-      <c r="K224" s="166"/>
-      <c r="L224" s="166"/>
-      <c r="M224" s="166"/>
-      <c r="N224" s="166"/>
-      <c r="O224" s="166"/>
-      <c r="P224" s="166"/>
+      <c r="I224" s="182"/>
+      <c r="J224" s="182"/>
+      <c r="K224" s="182"/>
+      <c r="L224" s="182"/>
+      <c r="M224" s="182"/>
+      <c r="N224" s="182"/>
+      <c r="O224" s="182"/>
+      <c r="P224" s="182"/>
       <c r="Q224" s="6"/>
       <c r="R224" s="90"/>
     </row>
     <row r="225" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A225" s="198"/>
-      <c r="B225" s="201"/>
-      <c r="C225" s="205"/>
-      <c r="D225" s="266"/>
-      <c r="E225" s="225"/>
+      <c r="A225" s="213"/>
+      <c r="B225" s="216"/>
+      <c r="C225" s="219"/>
+      <c r="D225" s="201"/>
+      <c r="E225" s="222"/>
       <c r="F225" s="115" t="s">
         <v>343</v>
       </c>
       <c r="G225" s="137" t="s">
         <v>175</v>
       </c>
-      <c r="H225" s="222" t="s">
+      <c r="H225" s="208" t="s">
         <v>197</v>
       </c>
-      <c r="I225" s="223"/>
-      <c r="J225" s="223"/>
-      <c r="K225" s="223"/>
-      <c r="L225" s="223"/>
-      <c r="M225" s="223"/>
-      <c r="N225" s="223"/>
-      <c r="O225" s="223"/>
-      <c r="P225" s="223"/>
+      <c r="I225" s="209"/>
+      <c r="J225" s="209"/>
+      <c r="K225" s="209"/>
+      <c r="L225" s="209"/>
+      <c r="M225" s="209"/>
+      <c r="N225" s="209"/>
+      <c r="O225" s="209"/>
+      <c r="P225" s="209"/>
       <c r="Q225" s="102"/>
       <c r="R225" s="93"/>
     </row>
   </sheetData>
-  <mergeCells count="323">
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="F71:F72"/>
-    <mergeCell ref="G71:G72"/>
-    <mergeCell ref="H61:P61"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="H62:P62"/>
-    <mergeCell ref="H63:P63"/>
-    <mergeCell ref="C64:C68"/>
-    <mergeCell ref="D64:D68"/>
-    <mergeCell ref="E64:E68"/>
-    <mergeCell ref="H64:P64"/>
-    <mergeCell ref="H65:P65"/>
-    <mergeCell ref="H66:P66"/>
-    <mergeCell ref="H67:P67"/>
-    <mergeCell ref="H68:P68"/>
-    <mergeCell ref="H72:P72"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="D183:D189"/>
-    <mergeCell ref="C183:C189"/>
-    <mergeCell ref="D179:D182"/>
-    <mergeCell ref="C179:C182"/>
-    <mergeCell ref="D34:D46"/>
-    <mergeCell ref="D56:D58"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="D73:D83"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="D87:D91"/>
-    <mergeCell ref="D93:D94"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="H75:P75"/>
-    <mergeCell ref="H76:P76"/>
-    <mergeCell ref="H77:P77"/>
-    <mergeCell ref="H78:P78"/>
-    <mergeCell ref="H79:P79"/>
-    <mergeCell ref="H80:P80"/>
-    <mergeCell ref="H81:P81"/>
-    <mergeCell ref="H92:P92"/>
-    <mergeCell ref="D117:D128"/>
-    <mergeCell ref="H100:P100"/>
-    <mergeCell ref="C161:C162"/>
-    <mergeCell ref="D161:D162"/>
-    <mergeCell ref="D166:D167"/>
-    <mergeCell ref="D168:D170"/>
-    <mergeCell ref="D173:D177"/>
-    <mergeCell ref="D95:D113"/>
-    <mergeCell ref="D114:D115"/>
-    <mergeCell ref="C155:C157"/>
-    <mergeCell ref="E155:E157"/>
-    <mergeCell ref="D129:D130"/>
-    <mergeCell ref="D131:D133"/>
-    <mergeCell ref="D135:D136"/>
-    <mergeCell ref="D139:D143"/>
-    <mergeCell ref="D155:D157"/>
-    <mergeCell ref="H150:P150"/>
-    <mergeCell ref="H186:P186"/>
-    <mergeCell ref="H189:P189"/>
-    <mergeCell ref="H13:P13"/>
-    <mergeCell ref="H14:P14"/>
-    <mergeCell ref="H15:P15"/>
-    <mergeCell ref="H16:P16"/>
-    <mergeCell ref="H17:P17"/>
-    <mergeCell ref="H18:P18"/>
-    <mergeCell ref="H22:P22"/>
-    <mergeCell ref="H21:P21"/>
-    <mergeCell ref="H159:P159"/>
-    <mergeCell ref="H160:P160"/>
-    <mergeCell ref="H161:P161"/>
-    <mergeCell ref="H162:P162"/>
-    <mergeCell ref="H151:P151"/>
-    <mergeCell ref="H152:P152"/>
-    <mergeCell ref="H153:P153"/>
-    <mergeCell ref="H154:P154"/>
-    <mergeCell ref="H155:P155"/>
-    <mergeCell ref="H156:P156"/>
-    <mergeCell ref="H157:P157"/>
-    <mergeCell ref="H84:P84"/>
-    <mergeCell ref="H85:P85"/>
+  <mergeCells count="322">
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C13:C18"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="D13:D18"/>
+    <mergeCell ref="D21:D26"/>
+    <mergeCell ref="D27:D32"/>
+    <mergeCell ref="C27:C32"/>
+    <mergeCell ref="E27:E32"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:P1"/>
+    <mergeCell ref="H2:P5"/>
+    <mergeCell ref="E34:E46"/>
+    <mergeCell ref="H34:P34"/>
+    <mergeCell ref="H35:P35"/>
+    <mergeCell ref="H36:P36"/>
+    <mergeCell ref="H37:P37"/>
+    <mergeCell ref="H38:P38"/>
+    <mergeCell ref="H39:P39"/>
+    <mergeCell ref="H40:P40"/>
+    <mergeCell ref="E13:E18"/>
+    <mergeCell ref="H27:P27"/>
+    <mergeCell ref="H29:P29"/>
+    <mergeCell ref="H30:P30"/>
+    <mergeCell ref="H31:P31"/>
+    <mergeCell ref="H32:P32"/>
+    <mergeCell ref="H6:P6"/>
+    <mergeCell ref="H8:P8"/>
+    <mergeCell ref="H9:P9"/>
+    <mergeCell ref="H10:P10"/>
+    <mergeCell ref="H11:P11"/>
+    <mergeCell ref="H12:P12"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="H50:P51"/>
+    <mergeCell ref="H52:P53"/>
+    <mergeCell ref="H41:P41"/>
+    <mergeCell ref="H42:P42"/>
+    <mergeCell ref="H43:P43"/>
+    <mergeCell ref="H44:P44"/>
+    <mergeCell ref="H45:P45"/>
+    <mergeCell ref="H46:P46"/>
+    <mergeCell ref="A2:A49"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B6:B49"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="H23:P23"/>
+    <mergeCell ref="H24:P24"/>
+    <mergeCell ref="H25:P25"/>
+    <mergeCell ref="H26:P26"/>
+    <mergeCell ref="H33:P33"/>
+    <mergeCell ref="H28:P28"/>
+    <mergeCell ref="C34:C46"/>
+    <mergeCell ref="A69:A83"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="H69:P70"/>
+    <mergeCell ref="Q69:Q83"/>
+    <mergeCell ref="C73:C83"/>
+    <mergeCell ref="A54:A68"/>
+    <mergeCell ref="H54:P54"/>
+    <mergeCell ref="H55:P55"/>
+    <mergeCell ref="C56:C58"/>
+    <mergeCell ref="E56:E58"/>
+    <mergeCell ref="H56:P56"/>
+    <mergeCell ref="H57:P57"/>
+    <mergeCell ref="H58:P58"/>
+    <mergeCell ref="H59:P59"/>
+    <mergeCell ref="H82:P82"/>
+    <mergeCell ref="H83:P83"/>
+    <mergeCell ref="B56:B68"/>
+    <mergeCell ref="E73:E83"/>
+    <mergeCell ref="H73:P73"/>
+    <mergeCell ref="H74:P74"/>
+    <mergeCell ref="H60:P60"/>
+    <mergeCell ref="B73:B83"/>
+    <mergeCell ref="A93:A113"/>
+    <mergeCell ref="B93:B113"/>
+    <mergeCell ref="C93:C94"/>
+    <mergeCell ref="E93:E94"/>
+    <mergeCell ref="H93:P94"/>
+    <mergeCell ref="C95:C113"/>
+    <mergeCell ref="C87:C91"/>
+    <mergeCell ref="E87:E91"/>
+    <mergeCell ref="H87:P87"/>
+    <mergeCell ref="H88:P88"/>
+    <mergeCell ref="H89:P89"/>
+    <mergeCell ref="H90:P90"/>
+    <mergeCell ref="H91:P91"/>
+    <mergeCell ref="A84:A91"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="B87:B91"/>
+    <mergeCell ref="H86:P86"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="Q114:Q128"/>
+    <mergeCell ref="H116:P116"/>
+    <mergeCell ref="B117:B128"/>
+    <mergeCell ref="C117:C128"/>
+    <mergeCell ref="H95:P95"/>
+    <mergeCell ref="H96:P96"/>
+    <mergeCell ref="H97:P97"/>
+    <mergeCell ref="H98:P98"/>
+    <mergeCell ref="H99:P99"/>
+    <mergeCell ref="H113:P113"/>
+    <mergeCell ref="E117:E128"/>
+    <mergeCell ref="A129:A134"/>
+    <mergeCell ref="B129:B134"/>
+    <mergeCell ref="C129:C130"/>
+    <mergeCell ref="E129:E130"/>
+    <mergeCell ref="H129:P130"/>
+    <mergeCell ref="C131:C133"/>
+    <mergeCell ref="H131:P131"/>
+    <mergeCell ref="A114:A128"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="E114:E115"/>
+    <mergeCell ref="H114:P115"/>
+    <mergeCell ref="H132:P132"/>
+    <mergeCell ref="H133:P133"/>
+    <mergeCell ref="H134:P134"/>
+    <mergeCell ref="A135:A137"/>
+    <mergeCell ref="B135:B137"/>
+    <mergeCell ref="C135:C136"/>
+    <mergeCell ref="E135:E136"/>
+    <mergeCell ref="H135:P135"/>
+    <mergeCell ref="H136:P136"/>
+    <mergeCell ref="H137:P137"/>
+    <mergeCell ref="A138:A163"/>
+    <mergeCell ref="H138:P138"/>
+    <mergeCell ref="B139:B143"/>
+    <mergeCell ref="C139:C143"/>
+    <mergeCell ref="H139:P139"/>
+    <mergeCell ref="H140:P140"/>
+    <mergeCell ref="H141:P141"/>
+    <mergeCell ref="H142:P142"/>
+    <mergeCell ref="H143:P143"/>
+    <mergeCell ref="B144:B163"/>
+    <mergeCell ref="H144:P144"/>
+    <mergeCell ref="H145:P145"/>
+    <mergeCell ref="H146:P146"/>
+    <mergeCell ref="H147:P147"/>
+    <mergeCell ref="H148:P148"/>
+    <mergeCell ref="H149:P149"/>
+    <mergeCell ref="H158:P158"/>
+    <mergeCell ref="A173:A177"/>
+    <mergeCell ref="B173:B177"/>
+    <mergeCell ref="C173:C177"/>
+    <mergeCell ref="E173:E177"/>
+    <mergeCell ref="H178:P178"/>
+    <mergeCell ref="H170:P170"/>
+    <mergeCell ref="H171:P171"/>
+    <mergeCell ref="H172:P172"/>
+    <mergeCell ref="A166:A170"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="C166:C167"/>
+    <mergeCell ref="E166:E167"/>
+    <mergeCell ref="H166:P167"/>
+    <mergeCell ref="B168:B170"/>
+    <mergeCell ref="C168:C170"/>
+    <mergeCell ref="E168:E170"/>
+    <mergeCell ref="H168:P168"/>
+    <mergeCell ref="H169:P169"/>
+    <mergeCell ref="H173:P173"/>
+    <mergeCell ref="H174:P174"/>
+    <mergeCell ref="H175:P175"/>
+    <mergeCell ref="H176:P176"/>
+    <mergeCell ref="H177:P177"/>
+    <mergeCell ref="A179:A189"/>
+    <mergeCell ref="B179:B189"/>
+    <mergeCell ref="A198:A202"/>
+    <mergeCell ref="B198:B200"/>
+    <mergeCell ref="C198:C200"/>
+    <mergeCell ref="H198:P198"/>
+    <mergeCell ref="H199:P199"/>
+    <mergeCell ref="H200:P200"/>
+    <mergeCell ref="H202:P202"/>
+    <mergeCell ref="A190:A197"/>
+    <mergeCell ref="H190:P190"/>
+    <mergeCell ref="H191:P191"/>
+    <mergeCell ref="H196:P196"/>
+    <mergeCell ref="H197:P197"/>
+    <mergeCell ref="C190:C195"/>
+    <mergeCell ref="A216:A225"/>
+    <mergeCell ref="B216:B225"/>
+    <mergeCell ref="C216:C225"/>
+    <mergeCell ref="E216:E225"/>
+    <mergeCell ref="H216:P216"/>
+    <mergeCell ref="H217:P217"/>
+    <mergeCell ref="H207:P207"/>
+    <mergeCell ref="H208:P208"/>
+    <mergeCell ref="C209:C215"/>
+    <mergeCell ref="H209:P209"/>
+    <mergeCell ref="H210:P210"/>
+    <mergeCell ref="H211:P211"/>
+    <mergeCell ref="H212:P212"/>
+    <mergeCell ref="H213:P213"/>
+    <mergeCell ref="H214:P214"/>
+    <mergeCell ref="A203:A215"/>
+    <mergeCell ref="B203:B215"/>
+    <mergeCell ref="C203:C206"/>
+    <mergeCell ref="H203:P203"/>
+    <mergeCell ref="H204:P204"/>
+    <mergeCell ref="H205:P205"/>
+    <mergeCell ref="H206:P206"/>
+    <mergeCell ref="H224:P224"/>
+    <mergeCell ref="H225:P225"/>
     <mergeCell ref="H218:P218"/>
     <mergeCell ref="H219:P219"/>
     <mergeCell ref="H220:P220"/>
@@ -9934,220 +10074,92 @@
     <mergeCell ref="D209:D215"/>
     <mergeCell ref="D216:D225"/>
     <mergeCell ref="D190:D195"/>
-    <mergeCell ref="A216:A225"/>
-    <mergeCell ref="B216:B225"/>
-    <mergeCell ref="C216:C225"/>
-    <mergeCell ref="E216:E225"/>
-    <mergeCell ref="H216:P216"/>
-    <mergeCell ref="H217:P217"/>
-    <mergeCell ref="H207:P207"/>
-    <mergeCell ref="H208:P208"/>
-    <mergeCell ref="C209:C215"/>
-    <mergeCell ref="H209:P209"/>
-    <mergeCell ref="H210:P210"/>
-    <mergeCell ref="H211:P211"/>
-    <mergeCell ref="H212:P212"/>
-    <mergeCell ref="H213:P213"/>
-    <mergeCell ref="H214:P214"/>
-    <mergeCell ref="A203:A215"/>
-    <mergeCell ref="B203:B215"/>
-    <mergeCell ref="C203:C206"/>
-    <mergeCell ref="H203:P203"/>
-    <mergeCell ref="H204:P204"/>
-    <mergeCell ref="H205:P205"/>
-    <mergeCell ref="H206:P206"/>
-    <mergeCell ref="H224:P224"/>
-    <mergeCell ref="H225:P225"/>
-    <mergeCell ref="A179:A189"/>
-    <mergeCell ref="B179:B189"/>
-    <mergeCell ref="A198:A202"/>
-    <mergeCell ref="B198:B200"/>
-    <mergeCell ref="C198:C200"/>
-    <mergeCell ref="H198:P198"/>
-    <mergeCell ref="H199:P199"/>
-    <mergeCell ref="H200:P200"/>
-    <mergeCell ref="H202:P202"/>
-    <mergeCell ref="A190:A197"/>
-    <mergeCell ref="H190:P190"/>
-    <mergeCell ref="H191:P191"/>
-    <mergeCell ref="H196:P196"/>
-    <mergeCell ref="H197:P197"/>
-    <mergeCell ref="C190:C195"/>
-    <mergeCell ref="A173:A177"/>
-    <mergeCell ref="B173:B177"/>
-    <mergeCell ref="C173:C177"/>
-    <mergeCell ref="E173:E177"/>
-    <mergeCell ref="H178:P178"/>
-    <mergeCell ref="H170:P170"/>
-    <mergeCell ref="H171:P171"/>
-    <mergeCell ref="H172:P172"/>
-    <mergeCell ref="A166:A170"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="C166:C167"/>
-    <mergeCell ref="E166:E167"/>
-    <mergeCell ref="H166:P167"/>
-    <mergeCell ref="B168:B170"/>
-    <mergeCell ref="C168:C170"/>
-    <mergeCell ref="E168:E170"/>
-    <mergeCell ref="H168:P168"/>
-    <mergeCell ref="H169:P169"/>
-    <mergeCell ref="H173:P173"/>
-    <mergeCell ref="H174:P174"/>
-    <mergeCell ref="H175:P175"/>
-    <mergeCell ref="H176:P176"/>
-    <mergeCell ref="H177:P177"/>
-    <mergeCell ref="A135:A137"/>
-    <mergeCell ref="B135:B137"/>
-    <mergeCell ref="C135:C136"/>
-    <mergeCell ref="E135:E136"/>
-    <mergeCell ref="H135:P135"/>
-    <mergeCell ref="H136:P136"/>
-    <mergeCell ref="H137:P137"/>
-    <mergeCell ref="A138:A163"/>
-    <mergeCell ref="H138:P138"/>
-    <mergeCell ref="B139:B143"/>
-    <mergeCell ref="C139:C143"/>
-    <mergeCell ref="H139:P139"/>
-    <mergeCell ref="H140:P140"/>
-    <mergeCell ref="H141:P141"/>
-    <mergeCell ref="H142:P142"/>
-    <mergeCell ref="H143:P143"/>
-    <mergeCell ref="B144:B163"/>
-    <mergeCell ref="H144:P144"/>
-    <mergeCell ref="H145:P145"/>
-    <mergeCell ref="H146:P146"/>
-    <mergeCell ref="H147:P147"/>
-    <mergeCell ref="H148:P148"/>
-    <mergeCell ref="H149:P149"/>
-    <mergeCell ref="H158:P158"/>
-    <mergeCell ref="A129:A134"/>
-    <mergeCell ref="B129:B134"/>
-    <mergeCell ref="C129:C130"/>
-    <mergeCell ref="E129:E130"/>
-    <mergeCell ref="H129:P130"/>
-    <mergeCell ref="C131:C133"/>
-    <mergeCell ref="H131:P131"/>
-    <mergeCell ref="A114:A128"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="E114:E115"/>
-    <mergeCell ref="H114:P115"/>
-    <mergeCell ref="H132:P132"/>
-    <mergeCell ref="H133:P133"/>
-    <mergeCell ref="H134:P134"/>
-    <mergeCell ref="Q114:Q128"/>
-    <mergeCell ref="H116:P116"/>
-    <mergeCell ref="B117:B128"/>
-    <mergeCell ref="C117:C128"/>
-    <mergeCell ref="H95:P95"/>
-    <mergeCell ref="H96:P96"/>
-    <mergeCell ref="H97:P97"/>
-    <mergeCell ref="H98:P98"/>
-    <mergeCell ref="H99:P99"/>
-    <mergeCell ref="H113:P113"/>
-    <mergeCell ref="E117:E128"/>
-    <mergeCell ref="A93:A113"/>
-    <mergeCell ref="B93:B113"/>
-    <mergeCell ref="C93:C94"/>
-    <mergeCell ref="E93:E94"/>
-    <mergeCell ref="H93:P94"/>
-    <mergeCell ref="C95:C113"/>
-    <mergeCell ref="C87:C91"/>
-    <mergeCell ref="E87:E91"/>
-    <mergeCell ref="H87:P87"/>
-    <mergeCell ref="H88:P88"/>
-    <mergeCell ref="H89:P89"/>
-    <mergeCell ref="H90:P90"/>
-    <mergeCell ref="H91:P91"/>
-    <mergeCell ref="A84:A91"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="B87:B91"/>
-    <mergeCell ref="H86:P86"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="A69:A83"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="H69:P70"/>
-    <mergeCell ref="Q69:Q83"/>
-    <mergeCell ref="C73:C83"/>
-    <mergeCell ref="A54:A68"/>
-    <mergeCell ref="H54:P54"/>
-    <mergeCell ref="H55:P55"/>
-    <mergeCell ref="C56:C58"/>
-    <mergeCell ref="E56:E58"/>
-    <mergeCell ref="H56:P56"/>
-    <mergeCell ref="H57:P57"/>
-    <mergeCell ref="H58:P58"/>
-    <mergeCell ref="H59:P59"/>
-    <mergeCell ref="H82:P82"/>
-    <mergeCell ref="H83:P83"/>
-    <mergeCell ref="B56:B68"/>
-    <mergeCell ref="E73:E83"/>
-    <mergeCell ref="H73:P73"/>
-    <mergeCell ref="H74:P74"/>
-    <mergeCell ref="H60:P60"/>
-    <mergeCell ref="B73:B83"/>
+    <mergeCell ref="H189:P189"/>
+    <mergeCell ref="H13:P13"/>
+    <mergeCell ref="H14:P14"/>
+    <mergeCell ref="H15:P15"/>
+    <mergeCell ref="H16:P16"/>
+    <mergeCell ref="H17:P17"/>
+    <mergeCell ref="H18:P18"/>
+    <mergeCell ref="H22:P22"/>
+    <mergeCell ref="H21:P21"/>
+    <mergeCell ref="H159:P159"/>
+    <mergeCell ref="H160:P160"/>
+    <mergeCell ref="H161:P161"/>
+    <mergeCell ref="H162:P162"/>
+    <mergeCell ref="H151:P151"/>
+    <mergeCell ref="H152:P152"/>
+    <mergeCell ref="H153:P153"/>
+    <mergeCell ref="H154:P154"/>
+    <mergeCell ref="H155:P155"/>
+    <mergeCell ref="H156:P156"/>
+    <mergeCell ref="H157:P157"/>
+    <mergeCell ref="H84:P84"/>
+    <mergeCell ref="H85:P85"/>
     <mergeCell ref="H49:P49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="B50:B53"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="H50:P51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="H52:P53"/>
-    <mergeCell ref="H41:P41"/>
-    <mergeCell ref="H42:P42"/>
-    <mergeCell ref="H43:P43"/>
-    <mergeCell ref="H44:P44"/>
-    <mergeCell ref="H45:P45"/>
-    <mergeCell ref="H46:P46"/>
-    <mergeCell ref="A2:A49"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B6:B49"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="H23:P23"/>
-    <mergeCell ref="H24:P24"/>
-    <mergeCell ref="H25:P25"/>
-    <mergeCell ref="H26:P26"/>
-    <mergeCell ref="H33:P33"/>
-    <mergeCell ref="H28:P28"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:P1"/>
-    <mergeCell ref="H2:P5"/>
-    <mergeCell ref="E34:E46"/>
-    <mergeCell ref="H34:P34"/>
-    <mergeCell ref="H35:P35"/>
-    <mergeCell ref="H36:P36"/>
-    <mergeCell ref="H37:P37"/>
-    <mergeCell ref="H38:P38"/>
-    <mergeCell ref="H39:P39"/>
-    <mergeCell ref="H40:P40"/>
-    <mergeCell ref="C34:C46"/>
-    <mergeCell ref="E13:E18"/>
-    <mergeCell ref="C13:C18"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="D13:D18"/>
-    <mergeCell ref="D21:D26"/>
-    <mergeCell ref="D27:D32"/>
-    <mergeCell ref="C27:C32"/>
-    <mergeCell ref="E27:E32"/>
-    <mergeCell ref="H27:P27"/>
-    <mergeCell ref="H29:P29"/>
-    <mergeCell ref="H30:P30"/>
-    <mergeCell ref="H31:P31"/>
-    <mergeCell ref="H32:P32"/>
-    <mergeCell ref="H6:P6"/>
-    <mergeCell ref="H8:P8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="H9:P9"/>
-    <mergeCell ref="H10:P10"/>
-    <mergeCell ref="H11:P11"/>
-    <mergeCell ref="H12:P12"/>
+    <mergeCell ref="C155:C157"/>
+    <mergeCell ref="E155:E157"/>
+    <mergeCell ref="D129:D130"/>
+    <mergeCell ref="D131:D133"/>
+    <mergeCell ref="D135:D136"/>
+    <mergeCell ref="D139:D143"/>
+    <mergeCell ref="D155:D157"/>
+    <mergeCell ref="H150:P150"/>
+    <mergeCell ref="H186:P186"/>
+    <mergeCell ref="H75:P75"/>
+    <mergeCell ref="H76:P76"/>
+    <mergeCell ref="H77:P77"/>
+    <mergeCell ref="H78:P78"/>
+    <mergeCell ref="H79:P79"/>
+    <mergeCell ref="H80:P80"/>
+    <mergeCell ref="H81:P81"/>
+    <mergeCell ref="H92:P92"/>
+    <mergeCell ref="D117:D128"/>
+    <mergeCell ref="H100:P100"/>
+    <mergeCell ref="D95:D113"/>
+    <mergeCell ref="D114:D115"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="D183:D189"/>
+    <mergeCell ref="C183:C189"/>
+    <mergeCell ref="D179:D182"/>
+    <mergeCell ref="C179:C182"/>
+    <mergeCell ref="D34:D46"/>
+    <mergeCell ref="D56:D58"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="D73:D83"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="D87:D91"/>
+    <mergeCell ref="D93:D94"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C161:C162"/>
+    <mergeCell ref="D161:D162"/>
+    <mergeCell ref="D166:D167"/>
+    <mergeCell ref="D168:D170"/>
+    <mergeCell ref="D173:D177"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="F71:F72"/>
+    <mergeCell ref="G71:G72"/>
+    <mergeCell ref="H61:P61"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="H62:P62"/>
+    <mergeCell ref="H63:P63"/>
+    <mergeCell ref="C64:C68"/>
+    <mergeCell ref="D64:D68"/>
+    <mergeCell ref="E64:E68"/>
+    <mergeCell ref="H64:P64"/>
+    <mergeCell ref="H65:P65"/>
+    <mergeCell ref="H66:P66"/>
+    <mergeCell ref="H67:P67"/>
+    <mergeCell ref="H68:P68"/>
+    <mergeCell ref="H72:P72"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H2:P5" location="'איביאי קרנות'!A1" display="לינק לטבלה" xr:uid="{90B1F86E-B428-41A8-AA38-26FE63806C91}"/>
@@ -15103,14 +15115,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="281" t="s">
+      <c r="A1" s="284" t="s">
         <v>206</v>
       </c>
-      <c r="B1" s="281"/>
-      <c r="D1" s="282" t="s">
+      <c r="B1" s="284"/>
+      <c r="D1" s="285" t="s">
         <v>201</v>
       </c>
-      <c r="E1" s="282"/>
+      <c r="E1" s="285"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
@@ -17505,11 +17517,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="283" t="s">
+      <c r="A1" s="286" t="s">
         <v>225</v>
       </c>
-      <c r="B1" s="283"/>
-      <c r="C1" s="283"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="34" t="s">
@@ -18186,11 +18198,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="287" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
+      <c r="B1" s="287"/>
+      <c r="C1" s="287"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
